--- a/reportOKSanaliza.xlsx
+++ b/reportOKSanaliza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojan\Documents\GitHub\ReportOKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785D18C7-D0DB-45E0-A1B9-6B10CB636E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91B08E1-5FE9-4FCA-BEDA-E59738725DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="12" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,15 +45,40 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={405F762F-FEDE-4B39-BCD0-72D378326FD0}</author>
+    <author>tc={F4841313-2AC6-4AB8-9D8D-A918BDBEDA73}</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{405F762F-FEDE-4B39-BCD0-72D378326FD0}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{F4841313-2AC6-4AB8-9D8D-A918BDBEDA73}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Stat po regijah:
+    --statistike meritve (centili, cone) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
+--BL, 2026-04-01
+--centili Slovenija
+SELECT 'Slovenija' as Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev         -- &lt;--- dodano
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)   -- &lt;--- dodan pogoj
+GROUP BY 
+    t.Ime
+--ORDER BY     t.Ime
+UNION ALL
+-- centili regije
 SELECT
     rgn.Name AS Regija,
     t.Ime AS Test,
@@ -66,6 +91,8 @@
     ON r.IdTest = t.ID
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev     -- &lt;--- dodan povezovalni JOIN
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 JOIN Uporabnik u
@@ -76,38 +103,14 @@
     ON rgn.ID = pc.RegionID
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND tv.IdBaterija = 20   -- vključi samo teste baterije 20
+  AND tv.IdBaterija IN (18, 19, 20, 21, 25, 26)    -- testi iz teh baterij
+  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26) -- meritve morajo biti v teh baterijah
 GROUP BY 
     rgn.Name,
-    t.Ime,
-    tv.PrioritetaPrikaza
+    t.Ime
 ORDER BY 
-    rgn.Name ASC,
-    tv.PrioritetaPrikaza ASC;
-Reply:
-    --statistike meritve (centili) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
---BL, 2026-04-01
---centili Slovenija
-SELECT
-    t.Ime AS Test,
-    AVG(r.CentilniRang1) AS CentilXA,
-    COUNT(r.CentilniRang1) AS N --,
-    --tv.PrioritetaPrikaza
-FROM TestVbateriji tv
-JOIN Test t 
-    ON t.ID = tv.IdTest
-JOIN Rezultat r
-    ON r.IdTest = t.ID
-JOIN Merjenec m 
-    ON m.ID = r.IdMerjenec
-JOIN DostopUporabnikaDoClana du
-    ON du.IdClan = m.IdClan
-WHERE --tv.IdBaterija = 20  AND          -- testi iz baterije 20
-   du.IdVloga = 10               -- samo merjenci z vlogo 10
-  AND r.CentilniRang1 IS NOT NULL   -- samo veljavni centili
-GROUP BY 
-    t.Ime  --,     tv.PrioritetaPrikaza
-ORDER BY t.ime --  tv.PrioritetaPrikaza ASC;</t>
+    Regija ASC,
+    t.Ime ASC;</t>
       </text>
     </comment>
   </commentList>
@@ -150,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="533">
   <si>
     <t>ID</t>
   </si>
@@ -1709,43 +1712,16 @@
     <t>Dotikanje plošč z roko</t>
   </si>
   <si>
-    <t>Dviganje trupa</t>
-  </si>
-  <si>
-    <t>Indeks telesne zmogljivosti</t>
-  </si>
-  <si>
-    <t>Kožna guba nadlahti</t>
-  </si>
-  <si>
     <t>Navpični skok</t>
   </si>
   <si>
     <t>Obseg pasu</t>
   </si>
   <si>
-    <t>Poligon nazaj</t>
-  </si>
-  <si>
-    <t>Predklon na klopci</t>
-  </si>
-  <si>
     <t>Predklon sede</t>
   </si>
   <si>
-    <t>Skok v daljino z mesta</t>
-  </si>
-  <si>
-    <t>Sorensenov test</t>
-  </si>
-  <si>
     <t>Stisk pesti</t>
-  </si>
-  <si>
-    <t>T-test</t>
-  </si>
-  <si>
-    <t>Tek na 60 m</t>
   </si>
   <si>
     <t>Tek na 600 m</t>
@@ -1783,7 +1759,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1818,7 +1794,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1828,6 +1804,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1861,16 +1843,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1910,34 +1893,15 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Povprečni</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> centil 6-minutni test hoje</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Centili!$I$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>6-minutni test hoje</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2016,7 +1980,7 @@
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2025,6 +1989,18 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2038,7 +2014,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Centili!$I$4</c:f>
+              <c:f>Centili!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2057,9 +2033,85 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-2671-4D7C-9A62-B8B24505F2C5}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-SI"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Centili!$H$5:$H$18</c:f>
+              <c:f>Centili!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
@@ -2106,48 +2158,48 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Centili!$I$5:$I$18</c:f>
+              <c:f>Centili!$I$2</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>47.403438483789401</c:v>
+                  <c:v>47.213545978669501</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49.549960943097801</c:v>
+                  <c:v>49.2759144449562</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45.468040441577102</c:v>
+                  <c:v>45.754394202086303</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39.985276858955302</c:v>
+                  <c:v>38.9408789570046</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>42.328426016957202</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44.7408214844612</c:v>
+                  <c:v>43.466271724748701</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>58.041481211427403</c:v>
+                  <c:v>56.857993241955697</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>57.547824248004297</c:v>
+                  <c:v>56.042456384092503</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>37.5728138326173</c:v>
+                  <c:v>37.202252778856902</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.707977329237202</c:v>
+                  <c:v>49.362621388214997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52.687803510197</c:v>
+                  <c:v>52.909444525207498</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>45.898605534257399</c:v>
+                  <c:v>44.1525868175721</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46.2503544661785</c:v>
+                  <c:v>47.4406647863958</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2244,6 +2296,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Povprečni centil</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-SI"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2893,14 +3000,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>449580</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
@@ -2937,9 +3044,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bojan Leskošek" refreshedDate="46114.798216782408" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="178" xr:uid="{595DB436-C5C2-41FC-8D84-021DB1358F00}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bojan Leskošek" refreshedDate="46115.26942384259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="171" xr:uid="{595DB436-C5C2-41FC-8D84-021DB1358F00}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D179" sheet="Centili"/>
+    <worksheetSource ref="A1:D172" sheet="Centili"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="Geo_enota" numFmtId="0">
@@ -2963,33 +3070,33 @@
       <sharedItems count="22">
         <s v="6-minutni test hoje"/>
         <s v="Dotikanje plošč z roko"/>
-        <s v="Dviganje trupa"/>
         <s v="Indeks telesne mase"/>
-        <s v="Indeks telesne zmogljivosti"/>
-        <s v="Kožna guba nadlahti"/>
         <s v="Navpični skok"/>
         <s v="Obseg pasu"/>
-        <s v="Poligon nazaj"/>
-        <s v="Predklon na klopci"/>
         <s v="Predklon sede"/>
-        <s v="Skok v daljino z mesta"/>
-        <s v="Sorensenov test"/>
         <s v="Stisk pesti"/>
-        <s v="Tek na 60 m"/>
         <s v="Tek na 600 m"/>
         <s v="Tek v osmici"/>
         <s v="Telesna masa"/>
         <s v="Telesna višina"/>
-        <s v="T-test"/>
         <s v="Upogibanje trupa"/>
         <s v="Vesa v zgibi"/>
+        <s v="Dviganje trupa" u="1"/>
+        <s v="Indeks telesne zmogljivosti" u="1"/>
+        <s v="Kožna guba nadlahti" u="1"/>
+        <s v="Poligon nazaj" u="1"/>
+        <s v="Predklon na klopci" u="1"/>
+        <s v="Skok v daljino z mesta" u="1"/>
+        <s v="Sorensenov test" u="1"/>
+        <s v="Tek na 60 m" u="1"/>
+        <s v="T-test" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="CentilXA" numFmtId="169">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="32.176286239259497" maxValue="87.685120282945505"/>
+    <cacheField name="CentilXA" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="23.9110197355899" maxValue="87.685120282945505"/>
     </cacheField>
     <cacheField name="N" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="24" maxValue="113463"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="42561"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -3001,1080 +3108,1038 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="178">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="171">
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="45.898605534257399"/>
-    <n v="19884"/>
+    <n v="44.1525868175721"/>
+    <n v="17658"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="66.618687603144096"/>
+    <n v="23142"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="56.0457133560095"/>
+    <n v="42291"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="53.941658365389102"/>
+    <n v="13896"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="33.554443752736603"/>
+    <n v="22698"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="42.063796955507797"/>
+    <n v="24795"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="49.446959302965503"/>
+    <n v="38129"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="45.5295653729886"/>
+    <n v="2664"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="50.282760555419898"/>
+    <n v="10698"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="48.127581426298804"/>
+    <n v="42345"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="60.016678297444301"/>
+    <n v="42561"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="79.423231204496801"/>
+    <n v="10983"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="54.874364979161598"/>
+    <n v="6324"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="79.469977064439007"/>
+    <n v="10902"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="64.907446013677202"/>
+    <n v="35468"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
-    <n v="47.403438483789401"/>
-    <n v="167"/>
+    <n v="47.213545978669501"/>
+    <n v="840"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="72.237031058870201"/>
+    <n v="978"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="54.762699953825198"/>
+    <n v="1840"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="52.853248619205502"/>
+    <n v="921"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="34.876460790062303"/>
+    <n v="915"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="40.964293248515702"/>
+    <n v="1640"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="55.165541594365003"/>
+    <n v="2235"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="46.878551800041599"/>
+    <n v="128"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="45.503812138950302"/>
+    <n v="894"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="49.966186886155199"/>
+    <n v="1840"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="62.248543180751497"/>
+    <n v="1870"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="78.480495039805305"/>
+    <n v="909"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="54.949695935723099"/>
+    <n v="384"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="49.549960943097801"/>
-    <n v="84"/>
+    <n v="49.2759144449562"/>
+    <n v="415"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="70.975397017767804"/>
+    <n v="276"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="55.587407278988202"/>
+    <n v="575"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="56.690009894014402"/>
+    <n v="258"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="37.2734520684483"/>
+    <n v="258"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="43.0866370327984"/>
+    <n v="612"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="54.269111627875297"/>
+    <n v="755"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="68.828051058530505"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="54.693854108682103"/>
+    <n v="255"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <n v="46.956681256753903"/>
+    <n v="580"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <n v="58.668474682236003"/>
+    <n v="575"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <n v="76.368802247026196"/>
+    <n v="252"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <n v="51.7422096683147"/>
+    <n v="40"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
-    <n v="45.468040441577102"/>
-    <n v="122"/>
+    <n v="45.754394202086303"/>
+    <n v="590"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="71.184738067510693"/>
+    <n v="444"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="53.701333135917402"/>
+    <n v="920"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="56.987303724214598"/>
+    <n v="411"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="37.658836041894801"/>
+    <n v="468"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="43.101509762305703"/>
+    <n v="832"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="54.225235787806398"/>
+    <n v="1095"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="55.855744430016898"/>
+    <n v="17"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="8"/>
+    <n v="49.241048177148102"/>
+    <n v="399"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="51.1351303542246"/>
+    <n v="925"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="60.637535532534201"/>
+    <n v="925"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="11"/>
+    <n v="80.654467056390601"/>
+    <n v="396"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="12"/>
+    <n v="55.135764595926503"/>
+    <n v="126"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
-    <n v="39.985276858955302"/>
-    <n v="41"/>
+    <n v="38.9408789570046"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="70.057030374454996"/>
+    <n v="207"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="52.6122557388966"/>
+    <n v="355"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="65.033722915759"/>
+    <n v="198"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="36.430440565737001"/>
+    <n v="195"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="35.735898379346096"/>
+    <n v="524"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="46.644270716914903"/>
+    <n v="655"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="44.300781408270602"/>
+    <n v="16"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="48.350288591756502"/>
+    <n v="192"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="9"/>
+    <n v="49.751047873951201"/>
+    <n v="355"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="10"/>
+    <n v="57.984895306193202"/>
+    <n v="355"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="11"/>
+    <n v="83.678824463860593"/>
+    <n v="192"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="12"/>
+    <n v="67.467260273972599"/>
+    <n v="26"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
     <n v="42.328426016957202"/>
-    <n v="70"/>
+    <n v="350"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="61.043720896928598"/>
+    <n v="330"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="55.019436804129903"/>
+    <n v="605"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="51.785195029806303"/>
+    <n v="312"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="33.630302898423999"/>
+    <n v="318"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="38.111316710960601"/>
+    <n v="748"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="51.1563808307668"/>
+    <n v="960"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="23.9110197355899"/>
+    <n v="32"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="51.731895651234403"/>
+    <n v="315"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="9"/>
+    <n v="49.281192589934903"/>
+    <n v="605"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="10"/>
+    <n v="60.861083064304097"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="11"/>
+    <n v="78.012845287857104"/>
+    <n v="315"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="12"/>
+    <n v="57.1861325060637"/>
+    <n v="58"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
-    <n v="44.7408214844612"/>
+    <n v="43.466271724748701"/>
+    <n v="7105"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="66.711032811852107"/>
+    <n v="4899"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="57.326881783318299"/>
+    <n v="10745"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="53.652763584566699"/>
+    <n v="4461"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="32.1759976944467"/>
+    <n v="4818"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="43.384586076587397"/>
+    <n v="7504"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="47.6011199004273"/>
+    <n v="11190"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="7"/>
+    <n v="45.857690190700701"/>
+    <n v="478"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <n v="50.996130380926203"/>
+    <n v="4572"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="9"/>
+    <n v="46.354303783372302"/>
+    <n v="10755"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="10"/>
+    <n v="59.714905194425199"/>
+    <n v="10810"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="78.635559108774302"/>
+    <n v="4755"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="12"/>
+    <n v="55.304076490640703"/>
+    <n v="1630"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="56.857993241955697"/>
+    <n v="325"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="68.738460654889295"/>
+    <n v="420"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="53.404921575059703"/>
+    <n v="765"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="57.589612189216098"/>
+    <n v="375"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="34.737484915038898"/>
+    <n v="390"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="38.4177673141144"/>
+    <n v="1156"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="6"/>
+    <n v="44.900865274460202"/>
     <n v="1530"/>
   </r>
   <r>
     <x v="7"/>
-    <x v="0"/>
-    <n v="58.041481211427403"/>
-    <n v="69"/>
+    <x v="7"/>
+    <n v="38.557905710710898"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="8"/>
+    <n v="45.708521393594602"/>
+    <n v="381"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="9"/>
+    <n v="52.833180305912599"/>
+    <n v="770"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="10"/>
+    <n v="61.990040685703804"/>
+    <n v="765"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="11"/>
+    <n v="86.268103073859095"/>
+    <n v="375"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="12"/>
+    <n v="59.295677965594301"/>
+    <n v="120"/>
   </r>
   <r>
     <x v="8"/>
     <x v="0"/>
-    <n v="57.547824248004297"/>
-    <n v="44"/>
+    <n v="56.042456384092503"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="65.336499507476404"/>
+    <n v="171"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="53.183321861665497"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="64.457040261692001"/>
+    <n v="147"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="35.212465185146499"/>
+    <n v="159"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="40.305966477996598"/>
+    <n v="440"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="6"/>
+    <n v="48.340017743508497"/>
+    <n v="565"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="7"/>
+    <n v="34.167808219178099"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="39.482199972128001"/>
+    <n v="153"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="9"/>
+    <n v="48.401398822631101"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="10"/>
+    <n v="54.857734034872301"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="11"/>
+    <n v="87.418371681557602"/>
+    <n v="162"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="12"/>
+    <n v="62.184325823616"/>
+    <n v="22"/>
   </r>
   <r>
     <x v="9"/>
     <x v="0"/>
-    <n v="37.5728138326173"/>
-    <n v="172"/>
+    <n v="37.202252778856902"/>
+    <n v="830"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="66.070177130148707"/>
+    <n v="573"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="45.595635374632003"/>
+    <n v="975"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="41.434926065303202"/>
+    <n v="516"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="45.288270970867202"/>
+    <n v="552"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="40.877592695778702"/>
+    <n v="820"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="6"/>
+    <n v="53.715552900404397"/>
+    <n v="1050"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="7"/>
+    <n v="51.573505692886599"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="8"/>
+    <n v="49.622762230433402"/>
+    <n v="516"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="54.853125986850202"/>
+    <n v="975"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="10"/>
+    <n v="55.0259532581182"/>
+    <n v="980"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="11"/>
+    <n v="87.685120282945505"/>
+    <n v="543"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="12"/>
+    <n v="75.550156712903998"/>
+    <n v="28"/>
   </r>
   <r>
     <x v="10"/>
     <x v="0"/>
-    <n v="48.707977329237202"/>
-    <n v="37"/>
+    <n v="49.362621388214997"/>
+    <n v="175"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="71.358198340472995"/>
+    <n v="141"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="56.086290475249001"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="52.379372389788401"/>
+    <n v="132"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="32.309971435168798"/>
+    <n v="144"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="38.650156761510601"/>
+    <n v="392"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="53.5680054443377"/>
+    <n v="505"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="7"/>
+    <n v="52.500265675663499"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="8"/>
+    <n v="51.4226483777068"/>
+    <n v="141"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="9"/>
+    <n v="50.730495365464499"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="61.037819309723602"/>
+    <n v="270"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="11"/>
+    <n v="79.530469753445104"/>
+    <n v="138"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="12"/>
+    <n v="53.215858971269299"/>
+    <n v="34"/>
   </r>
   <r>
     <x v="11"/>
     <x v="0"/>
-    <n v="52.687803510197"/>
-    <n v="203"/>
+    <n v="52.909444525207498"/>
+    <n v="990"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="67.9869163465019"/>
+    <n v="930"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="56.084077908785503"/>
+    <n v="1665"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="57.765195138154702"/>
+    <n v="876"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="33.385990565389399"/>
+    <n v="915"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="38.447821604168901"/>
+    <n v="1716"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="50.046469590881301"/>
+    <n v="2205"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="44.502390416945097"/>
+    <n v="86"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="8"/>
+    <n v="53.088177215239199"/>
+    <n v="867"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="9"/>
+    <n v="49.275810712721501"/>
+    <n v="1670"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="10"/>
+    <n v="62.118327659585702"/>
+    <n v="1665"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="82.454129926923997"/>
+    <n v="870"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="12"/>
+    <n v="50.638366816528297"/>
+    <n v="382"/>
   </r>
   <r>
     <x v="12"/>
     <x v="0"/>
-    <n v="46.2503544661785"/>
-    <n v="26"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="61.859425770594299"/>
-    <n v="69456"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="64.448408615517494"/>
-    <n v="1010"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="1"/>
-    <n v="68.243981227685396"/>
-    <n v="241"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <n v="63.138306574372798"/>
-    <n v="516"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="1"/>
-    <n v="61.650970704337603"/>
-    <n v="151"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="1"/>
-    <n v="59.389565108445503"/>
-    <n v="325"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="1"/>
-    <n v="61.2586151987609"/>
-    <n v="4895"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="1"/>
-    <n v="63.5095650083449"/>
-    <n v="468"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="1"/>
-    <n v="69.4869477721941"/>
-    <n v="172"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="1"/>
-    <n v="67.441745285494903"/>
-    <n v="229"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="1"/>
-    <n v="65.998355987718696"/>
-    <n v="105"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="1"/>
-    <n v="59.1261023499139"/>
-    <n v="1449"/>
+    <n v="47.4406647863958"/>
+    <n v="120"/>
   </r>
   <r>
     <x v="12"/>
     <x v="1"/>
-    <n v="65.849143997583596"/>
-    <n v="56"/>
+    <n v="70.0407360789264"/>
+    <n v="93"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="12"/>
     <x v="2"/>
-    <n v="55.661144882087001"/>
-    <n v="14414"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <n v="63.4012882175344"/>
-    <n v="112680"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="3"/>
-    <n v="65.530243828187807"/>
-    <n v="1066"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="3"/>
-    <n v="64.179445006669596"/>
-    <n v="268"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-    <n v="61.726062333311603"/>
-    <n v="552"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="3"/>
-    <n v="64.408793384751206"/>
-    <n v="156"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="3"/>
-    <n v="52.365209085664198"/>
-    <n v="340"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="3"/>
-    <n v="64.889610353808095"/>
-    <n v="5435"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="3"/>
-    <n v="61.977832811772402"/>
-    <n v="483"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="3"/>
-    <n v="65.2944828417792"/>
-    <n v="176"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="3"/>
-    <n v="46.998091475705202"/>
-    <n v="236"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="3"/>
-    <n v="57.772054341643098"/>
-    <n v="112"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="3"/>
-    <n v="59.433243297663203"/>
-    <n v="1483"/>
+    <n v="57.134981854646"/>
+    <n v="170"/>
   </r>
   <r>
     <x v="12"/>
     <x v="3"/>
-    <n v="58.112522389522098"/>
-    <n v="59"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <n v="68.326974225841994"/>
-    <n v="6129"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="5"/>
-    <n v="64.015389907808895"/>
-    <n v="14244"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="6"/>
-    <n v="53.697158157179103"/>
-    <n v="15292"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="6"/>
-    <n v="52.570898919692397"/>
-    <n v="306"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="6"/>
-    <n v="56.2000095402095"/>
+    <n v="40.235331058226301"/>
     <n v="87"/>
   </r>
   <r>
-    <x v="3"/>
-    <x v="6"/>
-    <n v="56.639997361358503"/>
-    <n v="141"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="37.0825579071889"/>
+    <n v="93"/>
   </r>
   <r>
-    <x v="4"/>
-    <x v="6"/>
-    <n v="65.273677127912805"/>
-    <n v="67"/>
-  </r>
-  <r>
+    <x v="12"/>
     <x v="5"/>
-    <x v="6"/>
-    <n v="51.785195029806303"/>
-    <n v="104"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="6"/>
-    <n v="53.765226633869098"/>
-    <n v="1595"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="6"/>
-    <n v="56.957425172463999"/>
-    <n v="129"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="6"/>
-    <n v="66.126187877309903"/>
-    <n v="53"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="6"/>
-    <n v="42.040155333313997"/>
-    <n v="178"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="6"/>
-    <n v="52.1139427828059"/>
-    <n v="46"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="6"/>
-    <n v="57.719228367273402"/>
-    <n v="297"/>
+    <n v="40.162955620652703"/>
+    <n v="192"/>
   </r>
   <r>
     <x v="12"/>
     <x v="6"/>
-    <n v="38.480238583292397"/>
-    <n v="31"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="7"/>
-    <n v="33.533826370018403"/>
-    <n v="24948"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-    <n v="34.725366328251503"/>
-    <n v="307"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="7"/>
-    <n v="37.3124829898603"/>
-    <n v="87"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="7"/>
-    <n v="37.540867499998598"/>
-    <n v="160"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="7"/>
-    <n v="36.128660189547801"/>
-    <n v="66"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="7"/>
-    <n v="33.630302898423999"/>
-    <n v="106"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="7"/>
-    <n v="32.176286239259497"/>
-    <n v="1716"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="7"/>
-    <n v="34.930081172059801"/>
-    <n v="134"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="7"/>
-    <n v="33.8697091929373"/>
-    <n v="57"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="7"/>
-    <n v="45.330007201012101"/>
-    <n v="190"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="7"/>
-    <n v="33.654954772795698"/>
-    <n v="50"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="7"/>
-    <n v="33.332790420978696"/>
-    <n v="310"/>
+    <n v="39.365431517519703"/>
+    <n v="255"/>
   </r>
   <r>
     <x v="12"/>
     <x v="7"/>
-    <n v="37.565077958014598"/>
-    <n v="33"/>
+    <n v="60.513242009132398"/>
+    <n v="3"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="12"/>
     <x v="8"/>
-    <n v="65.466843015554005"/>
-    <n v="14284"/>
+    <n v="53.4277275613317"/>
+    <n v="84"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="12"/>
     <x v="9"/>
-    <n v="61.351768828458802"/>
-    <n v="14548"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="10"/>
-    <n v="42.712666945560002"/>
-    <n v="26625"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="10"/>
-    <n v="40.736015184493397"/>
-    <n v="407"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="10"/>
-    <n v="43.219114083155397"/>
-    <n v="154"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="10"/>
-    <n v="43.450132359176799"/>
-    <n v="211"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="10"/>
-    <n v="36.092427793259397"/>
-    <n v="132"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="10"/>
-    <n v="38.111316710960601"/>
-    <n v="187"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="10"/>
-    <n v="43.764208355606797"/>
-    <n v="1986"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="10"/>
-    <n v="38.252192028693599"/>
-    <n v="293"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="10"/>
-    <n v="40.466069288879297"/>
-    <n v="114"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="10"/>
-    <n v="40.8892282486676"/>
-    <n v="211"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="10"/>
-    <n v="38.403917916557504"/>
-    <n v="100"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="10"/>
-    <n v="38.654035245688199"/>
-    <n v="434"/>
+    <n v="55.634664925787099"/>
+    <n v="170"/>
   </r>
   <r>
     <x v="12"/>
     <x v="10"/>
-    <n v="40.682511076372201"/>
-    <n v="50"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="11"/>
-    <n v="73.081544716928903"/>
-    <n v="21858"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="12"/>
-    <n v="55.066957784531802"/>
-    <n v="333"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="13"/>
-    <n v="49.248488611347398"/>
-    <n v="40677"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="13"/>
-    <n v="54.609639948049903"/>
-    <n v="444"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="13"/>
-    <n v="54.405738377296203"/>
-    <n v="152"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="13"/>
-    <n v="53.665815840539501"/>
-    <n v="222"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="13"/>
-    <n v="46.796221411784998"/>
-    <n v="132"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="13"/>
-    <n v="51.1563808307668"/>
-    <n v="192"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="13"/>
-    <n v="47.5824975087639"/>
-    <n v="2348"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="13"/>
-    <n v="44.907350299407902"/>
-    <n v="310"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="13"/>
-    <n v="48.126693616174599"/>
-    <n v="117"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="13"/>
-    <n v="53.5830090690432"/>
-    <n v="216"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="13"/>
-    <n v="53.885315181876202"/>
-    <n v="103"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="13"/>
-    <n v="50.1052555793894"/>
-    <n v="446"/>
+    <n v="74.347564566117597"/>
+    <n v="170"/>
   </r>
   <r>
     <x v="12"/>
-    <x v="13"/>
-    <n v="39.1252950567835"/>
-    <n v="53"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="14"/>
-    <n v="62.736846697140599"/>
-    <n v="13378"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="15"/>
-    <n v="65.092210365558898"/>
-    <n v="22815"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="15"/>
-    <n v="69.613924753165406"/>
-    <n v="739"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="15"/>
-    <n v="79.164705551931604"/>
-    <n v="150"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="15"/>
-    <n v="68.985699389225204"/>
-    <n v="351"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="15"/>
-    <n v="69.329477258665406"/>
-    <n v="88"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="15"/>
-    <n v="56.405542703648798"/>
-    <n v="228"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="15"/>
-    <n v="63.6609159465944"/>
-    <n v="3365"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="15"/>
-    <n v="64.824228635389204"/>
-    <n v="290"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="15"/>
-    <n v="74.5752238884495"/>
-    <n v="104"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="15"/>
-    <n v="69.185630328958197"/>
-    <n v="40"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="15"/>
-    <n v="57.006471496012701"/>
-    <n v="65"/>
-  </r>
-  <r>
     <x v="11"/>
-    <x v="15"/>
-    <n v="62.959805682643903"/>
-    <n v="1137"/>
+    <n v="80.527480916363103"/>
+    <n v="81"/>
   </r>
   <r>
     <x v="12"/>
-    <x v="15"/>
-    <n v="67.195871385083706"/>
-    <n v="24"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="16"/>
-    <n v="50.3155339173992"/>
-    <n v="10623"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="16"/>
-    <n v="45.396404940776002"/>
-    <n v="293"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="16"/>
-    <n v="54.693854108682103"/>
-    <n v="85"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="16"/>
-    <n v="49.241048177148102"/>
-    <n v="133"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="16"/>
-    <n v="48.350288591756502"/>
-    <n v="64"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="16"/>
-    <n v="51.731895651234503"/>
-    <n v="105"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="16"/>
-    <n v="50.985012106276301"/>
-    <n v="1523"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="16"/>
-    <n v="45.708521393594602"/>
-    <n v="127"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="16"/>
-    <n v="39.482199972128001"/>
-    <n v="51"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="16"/>
-    <n v="49.622762230433402"/>
-    <n v="172"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="16"/>
-    <n v="51.4226483777068"/>
-    <n v="47"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="16"/>
-    <n v="53.088177215239199"/>
-    <n v="289"/>
-  </r>
-  <r>
     <x v="12"/>
-    <x v="16"/>
-    <n v="53.4277275613317"/>
-    <n v="28"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="17"/>
-    <n v="44.956695934961999"/>
-    <n v="112905"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="17"/>
-    <n v="46.943455913511002"/>
-    <n v="1066"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="17"/>
-    <n v="51.437575148050101"/>
-    <n v="271"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="17"/>
-    <n v="40.901873821008699"/>
-    <n v="553"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="17"/>
-    <n v="38.463718117236098"/>
-    <n v="156"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="17"/>
-    <n v="52.095844174479403"/>
-    <n v="340"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="17"/>
-    <n v="43.678887486846101"/>
-    <n v="5445"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="17"/>
-    <n v="44.768540984547897"/>
-    <n v="485"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="17"/>
-    <n v="44.797959464613001"/>
-    <n v="176"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="17"/>
-    <n v="55.559813900528603"/>
-    <n v="236"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="17"/>
-    <n v="48.122130899420803"/>
-    <n v="112"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="17"/>
-    <n v="43.1003679458912"/>
-    <n v="1486"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="17"/>
-    <n v="55.625432064830299"/>
-    <n v="59"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="18"/>
-    <n v="54.946662756617499"/>
-    <n v="113463"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="18"/>
-    <n v="55.246125221465398"/>
-    <n v="1074"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="18"/>
-    <n v="65.188198007966406"/>
-    <n v="268"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="18"/>
-    <n v="50.191012036541601"/>
-    <n v="555"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="18"/>
-    <n v="49.149086397040001"/>
-    <n v="157"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="18"/>
-    <n v="57.304594707692303"/>
-    <n v="344"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="18"/>
-    <n v="54.641579877167104"/>
-    <n v="5468"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="18"/>
-    <n v="52.559995728543903"/>
-    <n v="487"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="18"/>
-    <n v="56.244790507030999"/>
-    <n v="176"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="18"/>
-    <n v="56.870412978426899"/>
-    <n v="238"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="18"/>
-    <n v="54.543950468841601"/>
-    <n v="112"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="18"/>
-    <n v="49.698293084649599"/>
-    <n v="1488"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="18"/>
-    <n v="72.2022490289486"/>
-    <n v="59"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="19"/>
-    <n v="53.933019078220802"/>
-    <n v="333"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="20"/>
-    <n v="79.469977064439007"/>
-    <n v="10902"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="20"/>
-    <n v="78.572536587415797"/>
-    <n v="296"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="20"/>
-    <n v="76.368802247026196"/>
-    <n v="84"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="20"/>
-    <n v="80.654467056390601"/>
-    <n v="132"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="20"/>
-    <n v="83.678824463860593"/>
-    <n v="64"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="20"/>
-    <n v="78.012845287857104"/>
-    <n v="105"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="20"/>
-    <n v="78.637959870888693"/>
-    <n v="1584"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="20"/>
-    <n v="86.268103073859095"/>
-    <n v="125"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="20"/>
-    <n v="87.418371681557602"/>
-    <n v="54"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="20"/>
-    <n v="87.685120282945505"/>
-    <n v="181"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="20"/>
-    <n v="79.530469753445004"/>
-    <n v="46"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="20"/>
-    <n v="82.454129926923997"/>
-    <n v="290"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="20"/>
-    <n v="80.527480916363103"/>
-    <n v="27"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="21"/>
-    <n v="64.907446013677202"/>
-    <n v="35468"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="21"/>
-    <n v="69.1612064638703"/>
-    <n v="867"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="21"/>
-    <n v="69.913780496033397"/>
-    <n v="165"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="21"/>
-    <n v="71.259451314633495"/>
-    <n v="424"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="21"/>
-    <n v="69.8794925707234"/>
-    <n v="92"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="21"/>
-    <n v="57.828688718751799"/>
-    <n v="243"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="21"/>
-    <n v="64.367633164262301"/>
-    <n v="3944"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="21"/>
-    <n v="64.614934175024999"/>
-    <n v="372"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="21"/>
-    <n v="70.011570596232602"/>
-    <n v="122"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="21"/>
-    <n v="69.405836775045401"/>
-    <n v="45"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <x v="21"/>
-    <n v="57.411509270515502"/>
-    <n v="75"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <x v="21"/>
-    <n v="61.177828407118199"/>
-    <n v="1301"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="21"/>
-    <n v="53.021613534499103"/>
-    <n v="35"/>
+    <n v="39.431534969670203"/>
+    <n v="22"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="H4:I18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -4099,30 +4164,30 @@
       <items count="23">
         <item x="0"/>
         <item x="1"/>
+        <item m="1" x="13"/>
         <item x="2"/>
+        <item m="1" x="14"/>
+        <item m="1" x="15"/>
         <item x="3"/>
         <item x="4"/>
+        <item m="1" x="16"/>
+        <item m="1" x="17"/>
         <item x="5"/>
+        <item m="1" x="18"/>
+        <item m="1" x="19"/>
         <item x="6"/>
+        <item m="1" x="20"/>
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
+        <item m="1" x="21"/>
         <item x="11"/>
         <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="169" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -4179,10 +4244,10 @@
     <pageField fld="1" item="0" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="169"/>
+    <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="2">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -4235,12 +4300,24 @@
       </pivotAreas>
     </conditionalFormat>
   </conditionalFormats>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
           </reference>
         </references>
       </pivotArea>
@@ -4575,8 +4652,33 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A1" dT="2026-04-02T17:04:45.13" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{405F762F-FEDE-4B39-BCD0-72D378326FD0}">
-    <text>Stat po regijah:
+  <threadedComment ref="A1" dT="2026-04-03T04:11:08.84" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{F4841313-2AC6-4AB8-9D8D-A918BDBEDA73}">
+    <text>--statistike meritve (centili, cone) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
+--BL, 2026-04-01
+--centili Slovenija
+SELECT 'Slovenija' as Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev         -- &lt;--- dodano
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)   -- &lt;--- dodan pogoj
+GROUP BY 
+    t.Ime
+--ORDER BY     t.Ime
+UNION ALL
+-- centili regije
 SELECT
     rgn.Name AS Regija,
     t.Ime AS Test,
@@ -4589,6 +4691,8 @@
     ON r.IdTest = t.ID
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev     -- &lt;--- dodan povezovalni JOIN
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 JOIN Uporabnik u
@@ -4599,39 +4703,14 @@
     ON rgn.ID = pc.RegionID
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND tv.IdBaterija = 20   -- vključi samo teste baterije 20
+  AND tv.IdBaterija IN (18, 19, 20, 21, 25, 26)    -- testi iz teh baterij
+  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26) -- meritve morajo biti v teh baterijah
 GROUP BY 
     rgn.Name,
-    t.Ime,
-    tv.PrioritetaPrikaza
+    t.Ime
 ORDER BY 
-    rgn.Name ASC,
-    tv.PrioritetaPrikaza ASC;</text>
-  </threadedComment>
-  <threadedComment ref="A1" dT="2026-04-02T17:05:30.68" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{E67D7697-B063-49FB-92B1-A3B7509C0A1B}" parentId="{405F762F-FEDE-4B39-BCD0-72D378326FD0}">
-    <text>--statistike meritve (centili) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
---BL, 2026-04-01
---centili Slovenija
-SELECT
-    t.Ime AS Test,
-    AVG(r.CentilniRang1) AS CentilXA,
-    COUNT(r.CentilniRang1) AS N --,
-    --tv.PrioritetaPrikaza
-FROM TestVbateriji tv
-JOIN Test t 
-    ON t.ID = tv.IdTest
-JOIN Rezultat r
-    ON r.IdTest = t.ID
-JOIN Merjenec m 
-    ON m.ID = r.IdMerjenec
-JOIN DostopUporabnikaDoClana du
-    ON du.IdClan = m.IdClan
-WHERE --tv.IdBaterija = 20  AND          -- testi iz baterije 20
-   du.IdVloga = 10               -- samo merjenci z vlogo 10
-  AND r.CentilniRang1 IS NOT NULL   -- samo veljavni centili
-GROUP BY 
-    t.Ime  --,     tv.PrioritetaPrikaza
-ORDER BY t.ime --  tv.PrioritetaPrikaza ASC;</text>
+    Regija ASC,
+    t.Ime ASC;</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -4706,7 +4785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9739FDDB-4B6F-4B7B-90FA-3D344ADEA498}">
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
@@ -4737,11 +4816,11 @@
       <c r="B2" t="s">
         <v>517</v>
       </c>
-      <c r="C2" s="4">
-        <v>45.898605534257399</v>
+      <c r="C2">
+        <v>44.1525868175721</v>
       </c>
       <c r="D2">
-        <v>19884</v>
+        <v>17658</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>506</v>
@@ -4752,130 +4831,130 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="B3" t="s">
-        <v>517</v>
-      </c>
-      <c r="C3" s="4">
-        <v>47.403438483789401</v>
+        <v>518</v>
+      </c>
+      <c r="C3">
+        <v>66.618687603144096</v>
       </c>
       <c r="D3">
-        <v>167</v>
+        <v>23142</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>505</v>
       </c>
       <c r="B4" t="s">
-        <v>517</v>
-      </c>
-      <c r="C4" s="4">
-        <v>49.549960943097801</v>
+        <v>510</v>
+      </c>
+      <c r="C4">
+        <v>56.0457133560095</v>
       </c>
       <c r="D4">
-        <v>84</v>
+        <v>42291</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="I4" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>505</v>
       </c>
       <c r="B5" t="s">
-        <v>517</v>
-      </c>
-      <c r="C5" s="4">
-        <v>45.468040441577102</v>
+        <v>519</v>
+      </c>
+      <c r="C5">
+        <v>53.941658365389102</v>
       </c>
       <c r="D5">
-        <v>122</v>
+        <v>13896</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <v>47.403438483789401</v>
+        <v>47.213545978669501</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>505</v>
       </c>
       <c r="B6" t="s">
-        <v>517</v>
-      </c>
-      <c r="C6" s="4">
-        <v>39.985276858955302</v>
+        <v>520</v>
+      </c>
+      <c r="C6">
+        <v>33.554443752736603</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>22698</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="4">
-        <v>49.549960943097801</v>
+        <v>49.2759144449562</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>505</v>
       </c>
       <c r="B7" t="s">
-        <v>517</v>
-      </c>
-      <c r="C7" s="4">
-        <v>42.328426016957202</v>
+        <v>521</v>
+      </c>
+      <c r="C7">
+        <v>42.063796955507797</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>24795</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>96</v>
       </c>
       <c r="I7" s="4">
-        <v>45.468040441577102</v>
+        <v>45.754394202086303</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>505</v>
       </c>
       <c r="B8" t="s">
-        <v>517</v>
-      </c>
-      <c r="C8" s="4">
-        <v>44.7408214844612</v>
+        <v>522</v>
+      </c>
+      <c r="C8">
+        <v>49.446959302965503</v>
       </c>
       <c r="D8">
-        <v>1530</v>
+        <v>38129</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>143</v>
       </c>
       <c r="I8" s="4">
-        <v>39.985276858955302</v>
+        <v>38.9408789570046</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>505</v>
       </c>
       <c r="B9" t="s">
-        <v>517</v>
-      </c>
-      <c r="C9" s="4">
-        <v>58.041481211427403</v>
+        <v>523</v>
+      </c>
+      <c r="C9">
+        <v>45.5295653729886</v>
       </c>
       <c r="D9">
-        <v>69</v>
+        <v>2664</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>163</v>
@@ -4886,102 +4965,102 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>505</v>
       </c>
       <c r="B10" t="s">
-        <v>517</v>
-      </c>
-      <c r="C10" s="4">
-        <v>57.547824248004297</v>
+        <v>524</v>
+      </c>
+      <c r="C10">
+        <v>50.282760555419898</v>
       </c>
       <c r="D10">
-        <v>44</v>
+        <v>10698</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>191</v>
       </c>
       <c r="I10" s="4">
-        <v>44.7408214844612</v>
+        <v>43.466271724748701</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>505</v>
       </c>
       <c r="B11" t="s">
-        <v>517</v>
-      </c>
-      <c r="C11" s="4">
-        <v>37.5728138326173</v>
+        <v>525</v>
+      </c>
+      <c r="C11">
+        <v>48.127581426298804</v>
       </c>
       <c r="D11">
-        <v>172</v>
+        <v>42345</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>253</v>
       </c>
       <c r="I11" s="4">
-        <v>58.041481211427403</v>
+        <v>56.857993241955697</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>402</v>
+        <v>505</v>
       </c>
       <c r="B12" t="s">
-        <v>517</v>
-      </c>
-      <c r="C12" s="4">
-        <v>48.707977329237202</v>
+        <v>526</v>
+      </c>
+      <c r="C12">
+        <v>60.016678297444301</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>42561</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>333</v>
       </c>
       <c r="I12" s="4">
-        <v>57.547824248004297</v>
+        <v>56.042456384092503</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="B13" t="s">
-        <v>517</v>
-      </c>
-      <c r="C13" s="4">
-        <v>52.687803510197</v>
+        <v>527</v>
+      </c>
+      <c r="C13">
+        <v>79.423231204496801</v>
       </c>
       <c r="D13">
-        <v>203</v>
+        <v>10983</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>371</v>
       </c>
       <c r="I13" s="4">
-        <v>37.5728138326173</v>
+        <v>37.202252778856902</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="B14" t="s">
-        <v>517</v>
-      </c>
-      <c r="C14" s="4">
-        <v>46.2503544661785</v>
+        <v>528</v>
+      </c>
+      <c r="C14">
+        <v>54.874364979161598</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>6324</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I14" s="4">
-        <v>48.707977329237202</v>
+        <v>49.362621388214997</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -4989,247 +5068,247 @@
         <v>505</v>
       </c>
       <c r="B15" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C15" s="4">
-        <v>61.859425770594299</v>
+        <v>79.469977064439007</v>
       </c>
       <c r="D15">
-        <v>69456</v>
+        <v>10902</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>420</v>
       </c>
       <c r="I15" s="4">
-        <v>52.687803510197</v>
+        <v>52.909444525207498</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="B16" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="C16" s="4">
-        <v>64.448408615517494</v>
+        <v>64.907446013677202</v>
       </c>
       <c r="D16">
-        <v>1010</v>
+        <v>35468</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>505</v>
       </c>
       <c r="I16" s="4">
-        <v>45.898605534257399</v>
+        <v>44.1525868175721</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>518</v>
-      </c>
-      <c r="C17" s="4">
-        <v>68.243981227685396</v>
+        <v>517</v>
+      </c>
+      <c r="C17">
+        <v>47.213545978669501</v>
       </c>
       <c r="D17">
-        <v>241</v>
+        <v>840</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>491</v>
       </c>
       <c r="I17" s="4">
-        <v>46.2503544661785</v>
+        <v>47.4406647863958</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
         <v>518</v>
       </c>
-      <c r="C18" s="4">
-        <v>63.138306574372798</v>
+      <c r="C18">
+        <v>72.237031058870201</v>
       </c>
       <c r="D18">
-        <v>516</v>
+        <v>978</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="I18" s="4">
-        <v>47.398678796981315</v>
+        <v>46.995957788209083</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>518</v>
-      </c>
-      <c r="C19" s="4">
-        <v>61.650970704337603</v>
+        <v>510</v>
+      </c>
+      <c r="C19">
+        <v>54.762699953825198</v>
       </c>
       <c r="D19">
-        <v>151</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>518</v>
-      </c>
-      <c r="C20" s="4">
-        <v>59.389565108445503</v>
+        <v>519</v>
+      </c>
+      <c r="C20">
+        <v>52.853248619205502</v>
       </c>
       <c r="D20">
-        <v>325</v>
+        <v>921</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>518</v>
-      </c>
-      <c r="C21" s="4">
-        <v>61.2586151987609</v>
+        <v>520</v>
+      </c>
+      <c r="C21">
+        <v>34.876460790062303</v>
       </c>
       <c r="D21">
-        <v>4895</v>
+        <v>915</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>253</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>518</v>
-      </c>
-      <c r="C22" s="4">
-        <v>63.5095650083449</v>
+        <v>521</v>
+      </c>
+      <c r="C22">
+        <v>40.964293248515702</v>
       </c>
       <c r="D22">
-        <v>468</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>518</v>
-      </c>
-      <c r="C23" s="4">
-        <v>69.4869477721941</v>
+        <v>522</v>
+      </c>
+      <c r="C23">
+        <v>55.165541594365003</v>
       </c>
       <c r="D23">
-        <v>172</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>518</v>
-      </c>
-      <c r="C24" s="4">
-        <v>67.441745285494903</v>
+        <v>523</v>
+      </c>
+      <c r="C24">
+        <v>46.878551800041599</v>
       </c>
       <c r="D24">
-        <v>229</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>402</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>518</v>
-      </c>
-      <c r="C25" s="4">
-        <v>65.998355987718696</v>
+        <v>524</v>
+      </c>
+      <c r="C25">
+        <v>45.503812138950302</v>
       </c>
       <c r="D25">
-        <v>105</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>420</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>518</v>
-      </c>
-      <c r="C26" s="4">
-        <v>59.1261023499139</v>
+        <v>525</v>
+      </c>
+      <c r="C26">
+        <v>49.966186886155199</v>
       </c>
       <c r="D26">
-        <v>1449</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>491</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>518</v>
-      </c>
-      <c r="C27" s="4">
-        <v>65.849143997583596</v>
+        <v>526</v>
+      </c>
+      <c r="C27">
+        <v>62.248543180751497</v>
       </c>
       <c r="D27">
-        <v>56</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>505</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>519</v>
-      </c>
-      <c r="C28" s="4">
-        <v>55.661144882087001</v>
+        <v>527</v>
+      </c>
+      <c r="C28">
+        <v>78.480495039805305</v>
       </c>
       <c r="D28">
-        <v>14414</v>
+        <v>909</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>505</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>510</v>
-      </c>
-      <c r="C29" s="4">
-        <v>63.4012882175344</v>
+        <v>528</v>
+      </c>
+      <c r="C29">
+        <v>54.949695935723099</v>
       </c>
       <c r="D29">
-        <v>112680</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>510</v>
-      </c>
-      <c r="C30" s="4">
-        <v>65.530243828187807</v>
+        <v>517</v>
+      </c>
+      <c r="C30">
+        <v>49.2759144449562</v>
       </c>
       <c r="D30">
-        <v>1066</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -5237,223 +5316,223 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>510</v>
-      </c>
-      <c r="C31" s="4">
-        <v>64.179445006669596</v>
+        <v>518</v>
+      </c>
+      <c r="C31">
+        <v>70.975397017767804</v>
       </c>
       <c r="D31">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>510</v>
       </c>
-      <c r="C32" s="4">
-        <v>61.726062333311603</v>
+      <c r="C32">
+        <v>55.587407278988202</v>
       </c>
       <c r="D32">
-        <v>552</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>510</v>
-      </c>
-      <c r="C33" s="4">
-        <v>64.408793384751206</v>
+        <v>519</v>
+      </c>
+      <c r="C33">
+        <v>56.690009894014402</v>
       </c>
       <c r="D33">
-        <v>156</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>510</v>
-      </c>
-      <c r="C34" s="4">
-        <v>52.365209085664198</v>
+        <v>520</v>
+      </c>
+      <c r="C34">
+        <v>37.2734520684483</v>
       </c>
       <c r="D34">
-        <v>340</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>510</v>
-      </c>
-      <c r="C35" s="4">
-        <v>64.889610353808095</v>
+        <v>521</v>
+      </c>
+      <c r="C35">
+        <v>43.0866370327984</v>
       </c>
       <c r="D35">
-        <v>5435</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>253</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
-        <v>510</v>
-      </c>
-      <c r="C36" s="4">
-        <v>61.977832811772402</v>
+        <v>522</v>
+      </c>
+      <c r="C36">
+        <v>54.269111627875297</v>
       </c>
       <c r="D36">
-        <v>483</v>
+        <v>755</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>333</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
-        <v>510</v>
-      </c>
-      <c r="C37" s="4">
-        <v>65.2944828417792</v>
+        <v>523</v>
+      </c>
+      <c r="C37">
+        <v>68.828051058530505</v>
       </c>
       <c r="D37">
-        <v>176</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>371</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>510</v>
-      </c>
-      <c r="C38" s="4">
-        <v>46.998091475705202</v>
+        <v>524</v>
+      </c>
+      <c r="C38">
+        <v>54.693854108682103</v>
       </c>
       <c r="D38">
-        <v>236</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>402</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>510</v>
-      </c>
-      <c r="C39" s="4">
-        <v>57.772054341643098</v>
+        <v>525</v>
+      </c>
+      <c r="C39">
+        <v>46.956681256753903</v>
       </c>
       <c r="D39">
-        <v>112</v>
+        <v>580</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>420</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>510</v>
-      </c>
-      <c r="C40" s="4">
-        <v>59.433243297663203</v>
+        <v>526</v>
+      </c>
+      <c r="C40">
+        <v>58.668474682236003</v>
       </c>
       <c r="D40">
-        <v>1483</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>491</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>510</v>
-      </c>
-      <c r="C41" s="4">
-        <v>58.112522389522098</v>
+        <v>527</v>
+      </c>
+      <c r="C41">
+        <v>76.368802247026196</v>
       </c>
       <c r="D41">
-        <v>59</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>505</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>520</v>
-      </c>
-      <c r="C42" s="4">
-        <v>68.326974225841994</v>
+        <v>528</v>
+      </c>
+      <c r="C42">
+        <v>51.7422096683147</v>
       </c>
       <c r="D42">
-        <v>6129</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>505</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>521</v>
-      </c>
-      <c r="C43" s="4">
-        <v>64.015389907808895</v>
+        <v>517</v>
+      </c>
+      <c r="C43">
+        <v>45.754394202086303</v>
       </c>
       <c r="D43">
-        <v>14244</v>
+        <v>590</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>505</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>522</v>
-      </c>
-      <c r="C44" s="4">
-        <v>53.697158157179103</v>
+        <v>518</v>
+      </c>
+      <c r="C44">
+        <v>71.184738067510693</v>
       </c>
       <c r="D44">
-        <v>15292</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>522</v>
-      </c>
-      <c r="C45" s="4">
-        <v>52.570898919692397</v>
+        <v>510</v>
+      </c>
+      <c r="C45">
+        <v>53.701333135917402</v>
       </c>
       <c r="D45">
-        <v>306</v>
+        <v>920</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B46" t="s">
-        <v>522</v>
-      </c>
-      <c r="C46" s="4">
-        <v>56.2000095402095</v>
+        <v>519</v>
+      </c>
+      <c r="C46">
+        <v>56.987303724214598</v>
       </c>
       <c r="D46">
-        <v>87</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -5461,195 +5540,195 @@
         <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C47" s="4">
-        <v>56.639997361358503</v>
+        <v>520</v>
+      </c>
+      <c r="C47">
+        <v>37.658836041894801</v>
       </c>
       <c r="D47">
-        <v>141</v>
+        <v>468</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>522</v>
-      </c>
-      <c r="C48" s="4">
-        <v>65.273677127912805</v>
+        <v>521</v>
+      </c>
+      <c r="C48">
+        <v>43.101509762305703</v>
       </c>
       <c r="D48">
-        <v>67</v>
+        <v>832</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
         <v>522</v>
       </c>
-      <c r="C49" s="4">
-        <v>51.785195029806303</v>
+      <c r="C49">
+        <v>54.225235787806398</v>
       </c>
       <c r="D49">
-        <v>104</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>522</v>
-      </c>
-      <c r="C50" s="4">
-        <v>53.765226633869098</v>
+        <v>523</v>
+      </c>
+      <c r="C50">
+        <v>55.855744430016898</v>
       </c>
       <c r="D50">
-        <v>1595</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>253</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>522</v>
-      </c>
-      <c r="C51" s="4">
-        <v>56.957425172463999</v>
+        <v>524</v>
+      </c>
+      <c r="C51">
+        <v>49.241048177148102</v>
       </c>
       <c r="D51">
-        <v>129</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>333</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>522</v>
-      </c>
-      <c r="C52" s="4">
-        <v>66.126187877309903</v>
+        <v>525</v>
+      </c>
+      <c r="C52">
+        <v>51.1351303542246</v>
       </c>
       <c r="D52">
-        <v>53</v>
+        <v>925</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>371</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>522</v>
-      </c>
-      <c r="C53" s="4">
-        <v>42.040155333313997</v>
+        <v>526</v>
+      </c>
+      <c r="C53">
+        <v>60.637535532534201</v>
       </c>
       <c r="D53">
-        <v>178</v>
+        <v>925</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>402</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>522</v>
-      </c>
-      <c r="C54" s="4">
-        <v>52.1139427828059</v>
+        <v>527</v>
+      </c>
+      <c r="C54">
+        <v>80.654467056390601</v>
       </c>
       <c r="D54">
-        <v>46</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>420</v>
+        <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>522</v>
-      </c>
-      <c r="C55" s="4">
-        <v>57.719228367273402</v>
+        <v>528</v>
+      </c>
+      <c r="C55">
+        <v>55.135764595926503</v>
       </c>
       <c r="D55">
-        <v>297</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>491</v>
+        <v>143</v>
       </c>
       <c r="B56" t="s">
-        <v>522</v>
-      </c>
-      <c r="C56" s="4">
-        <v>38.480238583292397</v>
+        <v>517</v>
+      </c>
+      <c r="C56">
+        <v>38.9408789570046</v>
       </c>
       <c r="D56">
-        <v>31</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>505</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>523</v>
-      </c>
-      <c r="C57" s="4">
-        <v>33.533826370018403</v>
+        <v>518</v>
+      </c>
+      <c r="C57">
+        <v>70.057030374454996</v>
       </c>
       <c r="D57">
-        <v>24948</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
-        <v>523</v>
-      </c>
-      <c r="C58" s="4">
-        <v>34.725366328251503</v>
+        <v>510</v>
+      </c>
+      <c r="C58">
+        <v>52.6122557388966</v>
       </c>
       <c r="D58">
-        <v>307</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>523</v>
-      </c>
-      <c r="C59" s="4">
-        <v>37.3124829898603</v>
+        <v>519</v>
+      </c>
+      <c r="C59">
+        <v>65.033722915759</v>
       </c>
       <c r="D59">
-        <v>87</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="B60" t="s">
-        <v>523</v>
-      </c>
-      <c r="C60" s="4">
-        <v>37.540867499998598</v>
+        <v>520</v>
+      </c>
+      <c r="C60">
+        <v>36.430440565737001</v>
       </c>
       <c r="D60">
-        <v>160</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -5657,223 +5736,223 @@
         <v>143</v>
       </c>
       <c r="B61" t="s">
-        <v>523</v>
-      </c>
-      <c r="C61" s="4">
-        <v>36.128660189547801</v>
+        <v>521</v>
+      </c>
+      <c r="C61">
+        <v>35.735898379346096</v>
       </c>
       <c r="D61">
-        <v>66</v>
+        <v>524</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B62" t="s">
-        <v>523</v>
-      </c>
-      <c r="C62" s="4">
-        <v>33.630302898423999</v>
+        <v>522</v>
+      </c>
+      <c r="C62">
+        <v>46.644270716914903</v>
       </c>
       <c r="D62">
-        <v>106</v>
+        <v>655</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="B63" t="s">
         <v>523</v>
       </c>
-      <c r="C63" s="4">
-        <v>32.176286239259497</v>
+      <c r="C63">
+        <v>44.300781408270602</v>
       </c>
       <c r="D63">
-        <v>1716</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>253</v>
+        <v>143</v>
       </c>
       <c r="B64" t="s">
-        <v>523</v>
-      </c>
-      <c r="C64" s="4">
-        <v>34.930081172059801</v>
+        <v>524</v>
+      </c>
+      <c r="C64">
+        <v>48.350288591756502</v>
       </c>
       <c r="D64">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>333</v>
+        <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>523</v>
-      </c>
-      <c r="C65" s="4">
-        <v>33.8697091929373</v>
+        <v>525</v>
+      </c>
+      <c r="C65">
+        <v>49.751047873951201</v>
       </c>
       <c r="D65">
-        <v>57</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>371</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>523</v>
-      </c>
-      <c r="C66" s="4">
-        <v>45.330007201012101</v>
+        <v>526</v>
+      </c>
+      <c r="C66">
+        <v>57.984895306193202</v>
       </c>
       <c r="D66">
-        <v>190</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>402</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>523</v>
-      </c>
-      <c r="C67" s="4">
-        <v>33.654954772795698</v>
+        <v>527</v>
+      </c>
+      <c r="C67">
+        <v>83.678824463860593</v>
       </c>
       <c r="D67">
-        <v>50</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>420</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s">
-        <v>523</v>
-      </c>
-      <c r="C68" s="4">
-        <v>33.332790420978696</v>
+        <v>528</v>
+      </c>
+      <c r="C68">
+        <v>67.467260273972599</v>
       </c>
       <c r="D68">
-        <v>310</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>491</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s">
-        <v>523</v>
-      </c>
-      <c r="C69" s="4">
-        <v>37.565077958014598</v>
+        <v>517</v>
+      </c>
+      <c r="C69">
+        <v>42.328426016957202</v>
       </c>
       <c r="D69">
-        <v>33</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>505</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s">
-        <v>524</v>
-      </c>
-      <c r="C70" s="4">
-        <v>65.466843015554005</v>
+        <v>518</v>
+      </c>
+      <c r="C70">
+        <v>61.043720896928598</v>
       </c>
       <c r="D70">
-        <v>14284</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>505</v>
+        <v>163</v>
       </c>
       <c r="B71" t="s">
-        <v>525</v>
-      </c>
-      <c r="C71" s="4">
-        <v>61.351768828458802</v>
+        <v>510</v>
+      </c>
+      <c r="C71">
+        <v>55.019436804129903</v>
       </c>
       <c r="D71">
-        <v>14548</v>
+        <v>605</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>505</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>526</v>
-      </c>
-      <c r="C72" s="4">
-        <v>42.712666945560002</v>
+        <v>519</v>
+      </c>
+      <c r="C72">
+        <v>51.785195029806303</v>
       </c>
       <c r="D72">
-        <v>26625</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
-        <v>526</v>
-      </c>
-      <c r="C73" s="4">
-        <v>40.736015184493397</v>
+        <v>520</v>
+      </c>
+      <c r="C73">
+        <v>33.630302898423999</v>
       </c>
       <c r="D73">
-        <v>407</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>526</v>
-      </c>
-      <c r="C74" s="4">
-        <v>43.219114083155397</v>
+        <v>521</v>
+      </c>
+      <c r="C74">
+        <v>38.111316710960601</v>
       </c>
       <c r="D74">
-        <v>154</v>
+        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>526</v>
-      </c>
-      <c r="C75" s="4">
-        <v>43.450132359176799</v>
+        <v>522</v>
+      </c>
+      <c r="C75">
+        <v>51.1563808307668</v>
       </c>
       <c r="D75">
-        <v>211</v>
+        <v>960</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>526</v>
-      </c>
-      <c r="C76" s="4">
-        <v>36.092427793259397</v>
+        <v>523</v>
+      </c>
+      <c r="C76">
+        <v>23.9110197355899</v>
       </c>
       <c r="D76">
-        <v>132</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -5881,223 +5960,223 @@
         <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>526</v>
-      </c>
-      <c r="C77" s="4">
-        <v>38.111316710960601</v>
+        <v>524</v>
+      </c>
+      <c r="C77">
+        <v>51.731895651234403</v>
       </c>
       <c r="D77">
-        <v>187</v>
+        <v>315</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="B78" t="s">
-        <v>526</v>
-      </c>
-      <c r="C78" s="4">
-        <v>43.764208355606797</v>
+        <v>525</v>
+      </c>
+      <c r="C78">
+        <v>49.281192589934903</v>
       </c>
       <c r="D78">
-        <v>1986</v>
+        <v>605</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>253</v>
+        <v>163</v>
       </c>
       <c r="B79" t="s">
         <v>526</v>
       </c>
-      <c r="C79" s="4">
-        <v>38.252192028693599</v>
+      <c r="C79">
+        <v>60.861083064304097</v>
       </c>
       <c r="D79">
-        <v>293</v>
+        <v>610</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>333</v>
+        <v>163</v>
       </c>
       <c r="B80" t="s">
-        <v>526</v>
-      </c>
-      <c r="C80" s="4">
-        <v>40.466069288879297</v>
+        <v>527</v>
+      </c>
+      <c r="C80">
+        <v>78.012845287857104</v>
       </c>
       <c r="D80">
-        <v>114</v>
+        <v>315</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>371</v>
+        <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>526</v>
-      </c>
-      <c r="C81" s="4">
-        <v>40.8892282486676</v>
+        <v>528</v>
+      </c>
+      <c r="C81">
+        <v>57.1861325060637</v>
       </c>
       <c r="D81">
-        <v>211</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>402</v>
+        <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>526</v>
-      </c>
-      <c r="C82" s="4">
-        <v>38.403917916557504</v>
+        <v>517</v>
+      </c>
+      <c r="C82">
+        <v>43.466271724748701</v>
       </c>
       <c r="D82">
-        <v>100</v>
+        <v>7105</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>420</v>
+        <v>191</v>
       </c>
       <c r="B83" t="s">
-        <v>526</v>
-      </c>
-      <c r="C83" s="4">
-        <v>38.654035245688199</v>
+        <v>518</v>
+      </c>
+      <c r="C83">
+        <v>66.711032811852107</v>
       </c>
       <c r="D83">
-        <v>434</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>491</v>
+        <v>191</v>
       </c>
       <c r="B84" t="s">
-        <v>526</v>
-      </c>
-      <c r="C84" s="4">
-        <v>40.682511076372201</v>
+        <v>510</v>
+      </c>
+      <c r="C84">
+        <v>57.326881783318299</v>
       </c>
       <c r="D84">
-        <v>50</v>
+        <v>10745</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>505</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
-        <v>527</v>
-      </c>
-      <c r="C85" s="4">
-        <v>73.081544716928903</v>
+        <v>519</v>
+      </c>
+      <c r="C85">
+        <v>53.652763584566699</v>
       </c>
       <c r="D85">
-        <v>21858</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>505</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>528</v>
-      </c>
-      <c r="C86" s="4">
-        <v>55.066957784531802</v>
+        <v>520</v>
+      </c>
+      <c r="C86">
+        <v>32.1759976944467</v>
       </c>
       <c r="D86">
-        <v>333</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>505</v>
+        <v>191</v>
       </c>
       <c r="B87" t="s">
-        <v>529</v>
-      </c>
-      <c r="C87" s="4">
-        <v>49.248488611347398</v>
+        <v>521</v>
+      </c>
+      <c r="C87">
+        <v>43.384586076587397</v>
       </c>
       <c r="D87">
-        <v>40677</v>
+        <v>7504</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="B88" t="s">
-        <v>529</v>
-      </c>
-      <c r="C88" s="4">
-        <v>54.609639948049903</v>
+        <v>522</v>
+      </c>
+      <c r="C88">
+        <v>47.6011199004273</v>
       </c>
       <c r="D88">
-        <v>444</v>
+        <v>11190</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>529</v>
-      </c>
-      <c r="C89" s="4">
-        <v>54.405738377296203</v>
+        <v>523</v>
+      </c>
+      <c r="C89">
+        <v>45.857690190700701</v>
       </c>
       <c r="D89">
-        <v>152</v>
+        <v>478</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>529</v>
-      </c>
-      <c r="C90" s="4">
-        <v>53.665815840539501</v>
+        <v>524</v>
+      </c>
+      <c r="C90">
+        <v>50.996130380926203</v>
       </c>
       <c r="D90">
-        <v>222</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="B91" t="s">
-        <v>529</v>
-      </c>
-      <c r="C91" s="4">
-        <v>46.796221411784998</v>
+        <v>525</v>
+      </c>
+      <c r="C91">
+        <v>46.354303783372302</v>
       </c>
       <c r="D91">
-        <v>132</v>
+        <v>10755</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>529</v>
-      </c>
-      <c r="C92" s="4">
-        <v>51.1563808307668</v>
+        <v>526</v>
+      </c>
+      <c r="C92">
+        <v>59.714905194425199</v>
       </c>
       <c r="D92">
-        <v>192</v>
+        <v>10810</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -6105,223 +6184,223 @@
         <v>191</v>
       </c>
       <c r="B93" t="s">
-        <v>529</v>
-      </c>
-      <c r="C93" s="4">
-        <v>47.5824975087639</v>
+        <v>527</v>
+      </c>
+      <c r="C93">
+        <v>78.635559108774302</v>
       </c>
       <c r="D93">
-        <v>2348</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="B94" t="s">
-        <v>529</v>
-      </c>
-      <c r="C94" s="4">
-        <v>44.907350299407902</v>
+        <v>528</v>
+      </c>
+      <c r="C94">
+        <v>55.304076490640703</v>
       </c>
       <c r="D94">
-        <v>310</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>333</v>
+        <v>253</v>
       </c>
       <c r="B95" t="s">
-        <v>529</v>
-      </c>
-      <c r="C95" s="4">
-        <v>48.126693616174599</v>
+        <v>517</v>
+      </c>
+      <c r="C95">
+        <v>56.857993241955697</v>
       </c>
       <c r="D95">
-        <v>117</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>371</v>
+        <v>253</v>
       </c>
       <c r="B96" t="s">
-        <v>529</v>
-      </c>
-      <c r="C96" s="4">
-        <v>53.5830090690432</v>
+        <v>518</v>
+      </c>
+      <c r="C96">
+        <v>68.738460654889295</v>
       </c>
       <c r="D96">
-        <v>216</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>402</v>
+        <v>253</v>
       </c>
       <c r="B97" t="s">
-        <v>529</v>
-      </c>
-      <c r="C97" s="4">
-        <v>53.885315181876202</v>
+        <v>510</v>
+      </c>
+      <c r="C97">
+        <v>53.404921575059703</v>
       </c>
       <c r="D97">
-        <v>103</v>
+        <v>765</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>420</v>
+        <v>253</v>
       </c>
       <c r="B98" t="s">
-        <v>529</v>
-      </c>
-      <c r="C98" s="4">
-        <v>50.1052555793894</v>
+        <v>519</v>
+      </c>
+      <c r="C98">
+        <v>57.589612189216098</v>
       </c>
       <c r="D98">
-        <v>446</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>491</v>
+        <v>253</v>
       </c>
       <c r="B99" t="s">
-        <v>529</v>
-      </c>
-      <c r="C99" s="4">
-        <v>39.1252950567835</v>
+        <v>520</v>
+      </c>
+      <c r="C99">
+        <v>34.737484915038898</v>
       </c>
       <c r="D99">
-        <v>53</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>505</v>
+        <v>253</v>
       </c>
       <c r="B100" t="s">
-        <v>531</v>
-      </c>
-      <c r="C100" s="4">
-        <v>62.736846697140599</v>
+        <v>521</v>
+      </c>
+      <c r="C100">
+        <v>38.4177673141144</v>
       </c>
       <c r="D100">
-        <v>13378</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>505</v>
+        <v>253</v>
       </c>
       <c r="B101" t="s">
-        <v>532</v>
-      </c>
-      <c r="C101" s="4">
-        <v>65.092210365558898</v>
+        <v>522</v>
+      </c>
+      <c r="C101">
+        <v>44.900865274460202</v>
       </c>
       <c r="D101">
-        <v>22815</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>6</v>
+        <v>253</v>
       </c>
       <c r="B102" t="s">
-        <v>532</v>
-      </c>
-      <c r="C102" s="4">
-        <v>69.613924753165406</v>
+        <v>523</v>
+      </c>
+      <c r="C102">
+        <v>38.557905710710898</v>
       </c>
       <c r="D102">
-        <v>739</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>52</v>
+        <v>253</v>
       </c>
       <c r="B103" t="s">
-        <v>532</v>
-      </c>
-      <c r="C103" s="4">
-        <v>79.164705551931604</v>
+        <v>524</v>
+      </c>
+      <c r="C103">
+        <v>45.708521393594602</v>
       </c>
       <c r="D103">
-        <v>150</v>
+        <v>381</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>253</v>
       </c>
       <c r="B104" t="s">
-        <v>532</v>
-      </c>
-      <c r="C104" s="4">
-        <v>68.985699389225204</v>
+        <v>525</v>
+      </c>
+      <c r="C104">
+        <v>52.833180305912599</v>
       </c>
       <c r="D104">
-        <v>351</v>
+        <v>770</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="B105" t="s">
-        <v>532</v>
-      </c>
-      <c r="C105" s="4">
-        <v>69.329477258665406</v>
+        <v>526</v>
+      </c>
+      <c r="C105">
+        <v>61.990040685703804</v>
       </c>
       <c r="D105">
-        <v>88</v>
+        <v>765</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="B106" t="s">
-        <v>532</v>
-      </c>
-      <c r="C106" s="4">
-        <v>56.405542703648798</v>
+        <v>527</v>
+      </c>
+      <c r="C106">
+        <v>86.268103073859095</v>
       </c>
       <c r="D106">
-        <v>228</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>532</v>
-      </c>
-      <c r="C107" s="4">
-        <v>63.6609159465944</v>
+        <v>528</v>
+      </c>
+      <c r="C107">
+        <v>59.295677965594301</v>
       </c>
       <c r="D107">
-        <v>3365</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>253</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s">
-        <v>532</v>
-      </c>
-      <c r="C108" s="4">
-        <v>64.824228635389204</v>
+        <v>517</v>
+      </c>
+      <c r="C108">
+        <v>56.042456384092503</v>
       </c>
       <c r="D108">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -6329,195 +6408,195 @@
         <v>333</v>
       </c>
       <c r="B109" t="s">
-        <v>532</v>
-      </c>
-      <c r="C109" s="4">
-        <v>74.5752238884495</v>
+        <v>518</v>
+      </c>
+      <c r="C109">
+        <v>65.336499507476404</v>
       </c>
       <c r="D109">
-        <v>104</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="B110" t="s">
-        <v>532</v>
-      </c>
-      <c r="C110" s="4">
-        <v>69.185630328958197</v>
+        <v>510</v>
+      </c>
+      <c r="C110">
+        <v>53.183321861665497</v>
       </c>
       <c r="D110">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="B111" t="s">
-        <v>532</v>
-      </c>
-      <c r="C111" s="4">
-        <v>57.006471496012701</v>
+        <v>519</v>
+      </c>
+      <c r="C111">
+        <v>64.457040261692001</v>
       </c>
       <c r="D111">
-        <v>65</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>420</v>
+        <v>333</v>
       </c>
       <c r="B112" t="s">
-        <v>532</v>
-      </c>
-      <c r="C112" s="4">
-        <v>62.959805682643903</v>
+        <v>520</v>
+      </c>
+      <c r="C112">
+        <v>35.212465185146499</v>
       </c>
       <c r="D112">
-        <v>1137</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>491</v>
+        <v>333</v>
       </c>
       <c r="B113" t="s">
-        <v>532</v>
-      </c>
-      <c r="C113" s="4">
-        <v>67.195871385083706</v>
+        <v>521</v>
+      </c>
+      <c r="C113">
+        <v>40.305966477996598</v>
       </c>
       <c r="D113">
-        <v>24</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>505</v>
+        <v>333</v>
       </c>
       <c r="B114" t="s">
-        <v>533</v>
-      </c>
-      <c r="C114" s="4">
-        <v>50.3155339173992</v>
+        <v>522</v>
+      </c>
+      <c r="C114">
+        <v>48.340017743508497</v>
       </c>
       <c r="D114">
-        <v>10623</v>
+        <v>565</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>333</v>
       </c>
       <c r="B115" t="s">
-        <v>533</v>
-      </c>
-      <c r="C115" s="4">
-        <v>45.396404940776002</v>
+        <v>523</v>
+      </c>
+      <c r="C115">
+        <v>34.167808219178099</v>
       </c>
       <c r="D115">
-        <v>293</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>52</v>
+        <v>333</v>
       </c>
       <c r="B116" t="s">
-        <v>533</v>
-      </c>
-      <c r="C116" s="4">
-        <v>54.693854108682103</v>
+        <v>524</v>
+      </c>
+      <c r="C116">
+        <v>39.482199972128001</v>
       </c>
       <c r="D116">
-        <v>85</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>96</v>
+        <v>333</v>
       </c>
       <c r="B117" t="s">
-        <v>533</v>
-      </c>
-      <c r="C117" s="4">
-        <v>49.241048177148102</v>
+        <v>525</v>
+      </c>
+      <c r="C117">
+        <v>48.401398822631101</v>
       </c>
       <c r="D117">
-        <v>133</v>
+        <v>300</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>333</v>
       </c>
       <c r="B118" t="s">
-        <v>533</v>
-      </c>
-      <c r="C118" s="4">
-        <v>48.350288591756502</v>
+        <v>526</v>
+      </c>
+      <c r="C118">
+        <v>54.857734034872301</v>
       </c>
       <c r="D118">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>163</v>
+        <v>333</v>
       </c>
       <c r="B119" t="s">
-        <v>533</v>
-      </c>
-      <c r="C119" s="4">
-        <v>51.731895651234503</v>
+        <v>527</v>
+      </c>
+      <c r="C119">
+        <v>87.418371681557602</v>
       </c>
       <c r="D119">
-        <v>105</v>
+        <v>162</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="B120" t="s">
-        <v>533</v>
-      </c>
-      <c r="C120" s="4">
-        <v>50.985012106276301</v>
+        <v>528</v>
+      </c>
+      <c r="C120">
+        <v>62.184325823616</v>
       </c>
       <c r="D120">
-        <v>1523</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>253</v>
+        <v>371</v>
       </c>
       <c r="B121" t="s">
-        <v>533</v>
-      </c>
-      <c r="C121" s="4">
-        <v>45.708521393594602</v>
+        <v>517</v>
+      </c>
+      <c r="C121">
+        <v>37.202252778856902</v>
       </c>
       <c r="D121">
-        <v>127</v>
+        <v>830</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="B122" t="s">
-        <v>533</v>
-      </c>
-      <c r="C122" s="4">
-        <v>39.482199972128001</v>
+        <v>518</v>
+      </c>
+      <c r="C122">
+        <v>66.070177130148707</v>
       </c>
       <c r="D122">
-        <v>51</v>
+        <v>573</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -6525,195 +6604,195 @@
         <v>371</v>
       </c>
       <c r="B123" t="s">
-        <v>533</v>
-      </c>
-      <c r="C123" s="4">
-        <v>49.622762230433402</v>
+        <v>510</v>
+      </c>
+      <c r="C123">
+        <v>45.595635374632003</v>
       </c>
       <c r="D123">
-        <v>172</v>
+        <v>975</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="B124" t="s">
-        <v>533</v>
-      </c>
-      <c r="C124" s="4">
-        <v>51.4226483777068</v>
+        <v>519</v>
+      </c>
+      <c r="C124">
+        <v>41.434926065303202</v>
       </c>
       <c r="D124">
-        <v>47</v>
+        <v>516</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="B125" t="s">
-        <v>533</v>
-      </c>
-      <c r="C125" s="4">
-        <v>53.088177215239199</v>
+        <v>520</v>
+      </c>
+      <c r="C125">
+        <v>45.288270970867202</v>
       </c>
       <c r="D125">
-        <v>289</v>
+        <v>552</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>491</v>
+        <v>371</v>
       </c>
       <c r="B126" t="s">
-        <v>533</v>
-      </c>
-      <c r="C126" s="4">
-        <v>53.4277275613317</v>
+        <v>521</v>
+      </c>
+      <c r="C126">
+        <v>40.877592695778702</v>
       </c>
       <c r="D126">
-        <v>28</v>
+        <v>820</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>505</v>
+        <v>371</v>
       </c>
       <c r="B127" t="s">
-        <v>534</v>
-      </c>
-      <c r="C127" s="4">
-        <v>44.956695934961999</v>
+        <v>522</v>
+      </c>
+      <c r="C127">
+        <v>53.715552900404397</v>
       </c>
       <c r="D127">
-        <v>112905</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>371</v>
       </c>
       <c r="B128" t="s">
-        <v>534</v>
-      </c>
-      <c r="C128" s="4">
-        <v>46.943455913511002</v>
+        <v>523</v>
+      </c>
+      <c r="C128">
+        <v>51.573505692886599</v>
       </c>
       <c r="D128">
-        <v>1066</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>52</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s">
-        <v>534</v>
-      </c>
-      <c r="C129" s="4">
-        <v>51.437575148050101</v>
+        <v>524</v>
+      </c>
+      <c r="C129">
+        <v>49.622762230433402</v>
       </c>
       <c r="D129">
-        <v>271</v>
+        <v>516</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>96</v>
+        <v>371</v>
       </c>
       <c r="B130" t="s">
-        <v>534</v>
-      </c>
-      <c r="C130" s="4">
-        <v>40.901873821008699</v>
+        <v>525</v>
+      </c>
+      <c r="C130">
+        <v>54.853125986850202</v>
       </c>
       <c r="D130">
-        <v>553</v>
+        <v>975</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>371</v>
       </c>
       <c r="B131" t="s">
-        <v>534</v>
-      </c>
-      <c r="C131" s="4">
-        <v>38.463718117236098</v>
+        <v>526</v>
+      </c>
+      <c r="C131">
+        <v>55.0259532581182</v>
       </c>
       <c r="D131">
-        <v>156</v>
+        <v>980</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>371</v>
       </c>
       <c r="B132" t="s">
-        <v>534</v>
-      </c>
-      <c r="C132" s="4">
-        <v>52.095844174479403</v>
+        <v>527</v>
+      </c>
+      <c r="C132">
+        <v>87.685120282945505</v>
       </c>
       <c r="D132">
-        <v>340</v>
+        <v>543</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="B133" t="s">
-        <v>534</v>
-      </c>
-      <c r="C133" s="4">
-        <v>43.678887486846101</v>
+        <v>528</v>
+      </c>
+      <c r="C133">
+        <v>75.550156712903998</v>
       </c>
       <c r="D133">
-        <v>5445</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>253</v>
+        <v>402</v>
       </c>
       <c r="B134" t="s">
-        <v>534</v>
-      </c>
-      <c r="C134" s="4">
-        <v>44.768540984547897</v>
+        <v>517</v>
+      </c>
+      <c r="C134">
+        <v>49.362621388214997</v>
       </c>
       <c r="D134">
-        <v>485</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="B135" t="s">
-        <v>534</v>
-      </c>
-      <c r="C135" s="4">
-        <v>44.797959464613001</v>
+        <v>518</v>
+      </c>
+      <c r="C135">
+        <v>71.358198340472995</v>
       </c>
       <c r="D135">
-        <v>176</v>
+        <v>141</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="B136" t="s">
-        <v>534</v>
-      </c>
-      <c r="C136" s="4">
-        <v>55.559813900528603</v>
+        <v>510</v>
+      </c>
+      <c r="C136">
+        <v>56.086290475249001</v>
       </c>
       <c r="D136">
-        <v>236</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -6721,195 +6800,195 @@
         <v>402</v>
       </c>
       <c r="B137" t="s">
-        <v>534</v>
-      </c>
-      <c r="C137" s="4">
-        <v>48.122130899420803</v>
+        <v>519</v>
+      </c>
+      <c r="C137">
+        <v>52.379372389788401</v>
       </c>
       <c r="D137">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B138" t="s">
-        <v>534</v>
-      </c>
-      <c r="C138" s="4">
-        <v>43.1003679458912</v>
+        <v>520</v>
+      </c>
+      <c r="C138">
+        <v>32.309971435168798</v>
       </c>
       <c r="D138">
-        <v>1486</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>491</v>
+        <v>402</v>
       </c>
       <c r="B139" t="s">
-        <v>534</v>
-      </c>
-      <c r="C139" s="4">
-        <v>55.625432064830299</v>
+        <v>521</v>
+      </c>
+      <c r="C139">
+        <v>38.650156761510601</v>
       </c>
       <c r="D139">
-        <v>59</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>402</v>
+      </c>
+      <c r="B140" t="s">
+        <v>522</v>
+      </c>
+      <c r="C140">
+        <v>53.5680054443377</v>
+      </c>
+      <c r="D140">
         <v>505</v>
-      </c>
-      <c r="B140" t="s">
-        <v>535</v>
-      </c>
-      <c r="C140" s="4">
-        <v>54.946662756617499</v>
-      </c>
-      <c r="D140">
-        <v>113463</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>6</v>
+        <v>402</v>
       </c>
       <c r="B141" t="s">
-        <v>535</v>
-      </c>
-      <c r="C141" s="4">
-        <v>55.246125221465398</v>
+        <v>523</v>
+      </c>
+      <c r="C141">
+        <v>52.500265675663499</v>
       </c>
       <c r="D141">
-        <v>1074</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>52</v>
+        <v>402</v>
       </c>
       <c r="B142" t="s">
-        <v>535</v>
-      </c>
-      <c r="C142" s="4">
-        <v>65.188198007966406</v>
+        <v>524</v>
+      </c>
+      <c r="C142">
+        <v>51.4226483777068</v>
       </c>
       <c r="D142">
-        <v>268</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>96</v>
+        <v>402</v>
       </c>
       <c r="B143" t="s">
-        <v>535</v>
-      </c>
-      <c r="C143" s="4">
-        <v>50.191012036541601</v>
+        <v>525</v>
+      </c>
+      <c r="C143">
+        <v>50.730495365464499</v>
       </c>
       <c r="D143">
-        <v>555</v>
+        <v>270</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>143</v>
+        <v>402</v>
       </c>
       <c r="B144" t="s">
-        <v>535</v>
-      </c>
-      <c r="C144" s="4">
-        <v>49.149086397040001</v>
+        <v>526</v>
+      </c>
+      <c r="C144">
+        <v>61.037819309723602</v>
       </c>
       <c r="D144">
-        <v>157</v>
+        <v>270</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>402</v>
       </c>
       <c r="B145" t="s">
-        <v>535</v>
-      </c>
-      <c r="C145" s="4">
-        <v>57.304594707692303</v>
+        <v>527</v>
+      </c>
+      <c r="C145">
+        <v>79.530469753445104</v>
       </c>
       <c r="D145">
-        <v>344</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>191</v>
+        <v>402</v>
       </c>
       <c r="B146" t="s">
-        <v>535</v>
-      </c>
-      <c r="C146" s="4">
-        <v>54.641579877167104</v>
+        <v>528</v>
+      </c>
+      <c r="C146">
+        <v>53.215858971269299</v>
       </c>
       <c r="D146">
-        <v>5468</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>253</v>
+        <v>420</v>
       </c>
       <c r="B147" t="s">
-        <v>535</v>
-      </c>
-      <c r="C147" s="4">
-        <v>52.559995728543903</v>
+        <v>517</v>
+      </c>
+      <c r="C147">
+        <v>52.909444525207498</v>
       </c>
       <c r="D147">
-        <v>487</v>
+        <v>990</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>333</v>
+        <v>420</v>
       </c>
       <c r="B148" t="s">
-        <v>535</v>
-      </c>
-      <c r="C148" s="4">
-        <v>56.244790507030999</v>
+        <v>518</v>
+      </c>
+      <c r="C148">
+        <v>67.9869163465019</v>
       </c>
       <c r="D148">
-        <v>176</v>
+        <v>930</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>420</v>
       </c>
       <c r="B149" t="s">
-        <v>535</v>
-      </c>
-      <c r="C149" s="4">
-        <v>56.870412978426899</v>
+        <v>510</v>
+      </c>
+      <c r="C149">
+        <v>56.084077908785503</v>
       </c>
       <c r="D149">
-        <v>238</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="B150" t="s">
-        <v>535</v>
-      </c>
-      <c r="C150" s="4">
-        <v>54.543950468841601</v>
+        <v>519</v>
+      </c>
+      <c r="C150">
+        <v>57.765195138154702</v>
       </c>
       <c r="D150">
-        <v>112</v>
+        <v>876</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -6917,209 +6996,209 @@
         <v>420</v>
       </c>
       <c r="B151" t="s">
-        <v>535</v>
-      </c>
-      <c r="C151" s="4">
-        <v>49.698293084649599</v>
+        <v>520</v>
+      </c>
+      <c r="C151">
+        <v>33.385990565389399</v>
       </c>
       <c r="D151">
-        <v>1488</v>
+        <v>915</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>491</v>
+        <v>420</v>
       </c>
       <c r="B152" t="s">
-        <v>535</v>
-      </c>
-      <c r="C152" s="4">
-        <v>72.2022490289486</v>
+        <v>521</v>
+      </c>
+      <c r="C152">
+        <v>38.447821604168901</v>
       </c>
       <c r="D152">
-        <v>59</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="B153" t="s">
-        <v>530</v>
-      </c>
-      <c r="C153" s="4">
-        <v>53.933019078220802</v>
+        <v>522</v>
+      </c>
+      <c r="C153">
+        <v>50.046469590881301</v>
       </c>
       <c r="D153">
-        <v>333</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="B154" t="s">
-        <v>536</v>
-      </c>
-      <c r="C154" s="4">
-        <v>79.469977064439007</v>
+        <v>523</v>
+      </c>
+      <c r="C154">
+        <v>44.502390416945097</v>
       </c>
       <c r="D154">
-        <v>10902</v>
+        <v>86</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>6</v>
+        <v>420</v>
       </c>
       <c r="B155" t="s">
-        <v>536</v>
-      </c>
-      <c r="C155" s="4">
-        <v>78.572536587415797</v>
+        <v>524</v>
+      </c>
+      <c r="C155">
+        <v>53.088177215239199</v>
       </c>
       <c r="D155">
-        <v>296</v>
+        <v>867</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>52</v>
+        <v>420</v>
       </c>
       <c r="B156" t="s">
-        <v>536</v>
-      </c>
-      <c r="C156" s="4">
-        <v>76.368802247026196</v>
+        <v>525</v>
+      </c>
+      <c r="C156">
+        <v>49.275810712721501</v>
       </c>
       <c r="D156">
-        <v>84</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>96</v>
+        <v>420</v>
       </c>
       <c r="B157" t="s">
-        <v>536</v>
-      </c>
-      <c r="C157" s="4">
-        <v>80.654467056390601</v>
+        <v>526</v>
+      </c>
+      <c r="C157">
+        <v>62.118327659585702</v>
       </c>
       <c r="D157">
-        <v>132</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="B158" t="s">
-        <v>536</v>
-      </c>
-      <c r="C158" s="4">
-        <v>83.678824463860593</v>
+        <v>527</v>
+      </c>
+      <c r="C158">
+        <v>82.454129926923997</v>
       </c>
       <c r="D158">
-        <v>64</v>
+        <v>870</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>420</v>
       </c>
       <c r="B159" t="s">
-        <v>536</v>
-      </c>
-      <c r="C159" s="4">
-        <v>78.012845287857104</v>
+        <v>528</v>
+      </c>
+      <c r="C159">
+        <v>50.638366816528297</v>
       </c>
       <c r="D159">
-        <v>105</v>
+        <v>382</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>191</v>
+        <v>491</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
-      </c>
-      <c r="C160" s="4">
-        <v>78.637959870888693</v>
+        <v>517</v>
+      </c>
+      <c r="C160">
+        <v>47.4406647863958</v>
       </c>
       <c r="D160">
-        <v>1584</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>253</v>
+        <v>491</v>
       </c>
       <c r="B161" t="s">
-        <v>536</v>
-      </c>
-      <c r="C161" s="4">
-        <v>86.268103073859095</v>
+        <v>518</v>
+      </c>
+      <c r="C161">
+        <v>70.0407360789264</v>
       </c>
       <c r="D161">
-        <v>125</v>
+        <v>93</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>333</v>
+        <v>491</v>
       </c>
       <c r="B162" t="s">
-        <v>536</v>
-      </c>
-      <c r="C162" s="4">
-        <v>87.418371681557602</v>
+        <v>510</v>
+      </c>
+      <c r="C162">
+        <v>57.134981854646</v>
       </c>
       <c r="D162">
-        <v>54</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>371</v>
+        <v>491</v>
       </c>
       <c r="B163" t="s">
-        <v>536</v>
-      </c>
-      <c r="C163" s="4">
-        <v>87.685120282945505</v>
+        <v>519</v>
+      </c>
+      <c r="C163">
+        <v>40.235331058226301</v>
       </c>
       <c r="D163">
-        <v>181</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>402</v>
+        <v>491</v>
       </c>
       <c r="B164" t="s">
-        <v>536</v>
-      </c>
-      <c r="C164" s="4">
-        <v>79.530469753445004</v>
+        <v>520</v>
+      </c>
+      <c r="C164">
+        <v>37.0825579071889</v>
       </c>
       <c r="D164">
-        <v>46</v>
+        <v>93</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>536</v>
-      </c>
-      <c r="C165" s="4">
-        <v>82.454129926923997</v>
+        <v>521</v>
+      </c>
+      <c r="C165">
+        <v>40.162955620652703</v>
       </c>
       <c r="D165">
-        <v>290</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -7127,203 +7206,105 @@
         <v>491</v>
       </c>
       <c r="B166" t="s">
-        <v>536</v>
-      </c>
-      <c r="C166" s="4">
-        <v>80.527480916363103</v>
+        <v>522</v>
+      </c>
+      <c r="C166">
+        <v>39.365431517519703</v>
       </c>
       <c r="D166">
-        <v>27</v>
+        <v>255</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B167" t="s">
-        <v>537</v>
-      </c>
-      <c r="C167" s="4">
-        <v>64.907446013677202</v>
+        <v>523</v>
+      </c>
+      <c r="C167">
+        <v>60.513242009132398</v>
       </c>
       <c r="D167">
-        <v>35468</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>6</v>
+        <v>491</v>
       </c>
       <c r="B168" t="s">
-        <v>537</v>
-      </c>
-      <c r="C168" s="4">
-        <v>69.1612064638703</v>
+        <v>524</v>
+      </c>
+      <c r="C168">
+        <v>53.4277275613317</v>
       </c>
       <c r="D168">
-        <v>867</v>
+        <v>84</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>52</v>
+        <v>491</v>
       </c>
       <c r="B169" t="s">
-        <v>537</v>
-      </c>
-      <c r="C169" s="4">
-        <v>69.913780496033397</v>
+        <v>525</v>
+      </c>
+      <c r="C169">
+        <v>55.634664925787099</v>
       </c>
       <c r="D169">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>96</v>
+        <v>491</v>
       </c>
       <c r="B170" t="s">
-        <v>537</v>
-      </c>
-      <c r="C170" s="4">
-        <v>71.259451314633495</v>
+        <v>526</v>
+      </c>
+      <c r="C170">
+        <v>74.347564566117597</v>
       </c>
       <c r="D170">
-        <v>424</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>143</v>
+        <v>491</v>
       </c>
       <c r="B171" t="s">
-        <v>537</v>
-      </c>
-      <c r="C171" s="4">
-        <v>69.8794925707234</v>
+        <v>527</v>
+      </c>
+      <c r="C171">
+        <v>80.527480916363103</v>
       </c>
       <c r="D171">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>163</v>
+        <v>491</v>
       </c>
       <c r="B172" t="s">
-        <v>537</v>
-      </c>
-      <c r="C172" s="4">
-        <v>57.828688718751799</v>
+        <v>528</v>
+      </c>
+      <c r="C172">
+        <v>39.431534969670203</v>
       </c>
       <c r="D172">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>191</v>
-      </c>
-      <c r="B173" t="s">
-        <v>537</v>
-      </c>
-      <c r="C173" s="4">
-        <v>64.367633164262301</v>
-      </c>
-      <c r="D173">
-        <v>3944</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>253</v>
-      </c>
-      <c r="B174" t="s">
-        <v>537</v>
-      </c>
-      <c r="C174" s="4">
-        <v>64.614934175024999</v>
-      </c>
-      <c r="D174">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>333</v>
-      </c>
-      <c r="B175" t="s">
-        <v>537</v>
-      </c>
-      <c r="C175" s="4">
-        <v>70.011570596232602</v>
-      </c>
-      <c r="D175">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>371</v>
-      </c>
-      <c r="B176" t="s">
-        <v>537</v>
-      </c>
-      <c r="C176" s="4">
-        <v>69.405836775045401</v>
-      </c>
-      <c r="D176">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>402</v>
-      </c>
-      <c r="B177" t="s">
-        <v>537</v>
-      </c>
-      <c r="C177" s="4">
-        <v>57.411509270515502</v>
-      </c>
-      <c r="D177">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>420</v>
-      </c>
-      <c r="B178" t="s">
-        <v>537</v>
-      </c>
-      <c r="C178" s="4">
-        <v>61.177828407118199</v>
-      </c>
-      <c r="D178">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>491</v>
-      </c>
-      <c r="B179" t="s">
-        <v>537</v>
-      </c>
-      <c r="C179" s="4">
-        <v>53.021613534499103</v>
-      </c>
-      <c r="D179">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D179">
-    <sortCondition ref="B2:B179"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D172">
+    <sortCondition ref="A2:A172"/>
   </sortState>
   <conditionalFormatting pivot="1" sqref="I5:I17">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7342,9 +7323,9 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -7398,18 +7379,18 @@
       <c r="E1" t="s">
         <v>509</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" s="7" t="str">
         <f>C1&amp;"%"</f>
         <v>Zdravo%</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" s="7" t="str">
         <f t="shared" ref="H1:I1" si="0">D1&amp;"%"</f>
         <v>Mejno%</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Tvegano%</v>
       </c>
@@ -7511,7 +7492,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">

--- a/reportOKSanaliza.xlsx
+++ b/reportOKSanaliza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojan\Documents\GitHub\ReportOKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91B08E1-5FE9-4FCA-BEDA-E59738725DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A274C62-E0A4-4B79-A1B2-8B961B2310DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
   </bookViews>
   <sheets>
     <sheet name="Analize" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="10" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -120,6 +121,75 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={BFFC901B-821E-4A6C-8204-68AA98345E97}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BFFC901B-821E-4A6C-8204-68AA98345E97}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    SELECT 'Slovenija' as Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+  AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
+GROUP BY
+    te.Ime
+--ORDER BY     te.Ime
+UNION ALL
+SELECT
+    rgn.Name AS Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = c.ID
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+  AND du.IdVloga = 10
+  AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
+GROUP BY
+    rgn.Name,
+    te.Ime
+ORDER BY
+    Regija ASC,
+    te.Ime ASC;</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={27CA99E9-B9D0-4DB6-9B7E-D9517DFCF062}</author>
     <author>tc={FFBCDB00-2945-45C1-A471-2CFEEE31329C}</author>
   </authors>
@@ -153,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="535">
   <si>
     <t>ID</t>
   </si>
@@ -1752,14 +1822,21 @@
   </si>
   <si>
     <t>Average of CentilXA</t>
+  </si>
+  <si>
+    <t>Average of Mejno%</t>
+  </si>
+  <si>
+    <t>Average of Tvegano%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1843,7 +1920,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1854,13 +1931,28 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{BDBFD1E4-62EC-41BE-B39B-390F134CCF6B}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2453,6 +2545,798 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[reportOKSanaliza.xlsx]Cone!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>Cone!$L$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>6-minutni test hoje</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SI"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-SI"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-SI"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-SI"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-SI"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average of Tvegano%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="28575">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1264-454D-8BD1-543C87141A81}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>Gorenjska</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Goriška</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Jugovzhodna Slovenija</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Koroška</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Obalno-kraška</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Osrednjeslovenska</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Podravska</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Pomurska</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Posavska</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Primorsko-notranjska</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Savinjska</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Slovenija</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Zasavska</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1864406779661017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21794871794871795</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25490196078431371</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.39473684210526316</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.32307692307692309</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24878048780487805</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14516129032258066</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.23684210526315788</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.19379844961240311</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14285714285714285</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.203125</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.24783974862529459</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.22727272727272727</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1264-454D-8BD1-543C87141A81}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average of Mejno%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>Gorenjska</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Goriška</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Jugovzhodna Slovenija</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Koroška</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Obalno-kraška</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Osrednjeslovenska</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Podravska</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Pomurska</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Posavska</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Primorsko-notranjska</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Savinjska</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Slovenija</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Zasavska</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cone!$L$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.16949152542372881</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17948717948717949</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14705882352941177</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15789473684210525</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.2307692307692313E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2032520325203252</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.19354838709677419</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.21052631578947367</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.27906976744186046</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14285714285714285</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2109375</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.19285153181461115</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.31818181818181818</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1264-454D-8BD1-543C87141A81}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="100"/>
+        <c:axId val="1696995311"/>
+        <c:axId val="1696983311"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1696995311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-SI"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1696983311"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1696983311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-SI"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1696995311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SI"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-SI"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2493,7 +3377,550 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3037,6 +4464,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>156210</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2751ADB-F2A4-824B-DA81-780BDE6CAB70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Leskošek, Bojan" id="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" userId="S::Bojan.Leskosek@fsp.uni-lj.si::01467edb-a248-43f6-847c-bdc254055f4f" providerId="AD"/>
@@ -3107,6 +4575,74 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bojan Leskošek" refreshedDate="46115.336710532407" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="143" xr:uid="{62DBB8F1-B9CF-435A-A5F6-CE2D0CA1F5C6}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I144" sheet="Cone"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Geo_enota" numFmtId="0">
+      <sharedItems count="13">
+        <s v="Slovenija"/>
+        <s v="Gorenjska"/>
+        <s v="Goriška"/>
+        <s v="Jugovzhodna Slovenija"/>
+        <s v="Koroška"/>
+        <s v="Obalno-kraška"/>
+        <s v="Osrednjeslovenska"/>
+        <s v="Podravska"/>
+        <s v="Pomurska"/>
+        <s v="Posavska"/>
+        <s v="Primorsko-notranjska"/>
+        <s v="Savinjska"/>
+        <s v="Zasavska"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Test" numFmtId="0">
+      <sharedItems count="11">
+        <s v="6-minutni test hoje"/>
+        <s v="Dotikanje plošč z roko"/>
+        <s v="Indeks telesne mase"/>
+        <s v="Navpični skok"/>
+        <s v="Obseg pasu"/>
+        <s v="Predklon sede"/>
+        <s v="Stisk pesti"/>
+        <s v="Tek na 600 m"/>
+        <s v="Tek v osmici"/>
+        <s v="Upogibanje trupa"/>
+        <s v="Vesa v zgibi"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Zdravo" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3903"/>
+    </cacheField>
+    <cacheField name="Mejno" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1082"/>
+    </cacheField>
+    <cacheField name="Tvegano" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1709"/>
+    </cacheField>
+    <cacheField name="sum" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="4198"/>
+    </cacheField>
+    <cacheField name="Zdravo%" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.6774193548387094E-2" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Mejno%" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.5"/>
+    </cacheField>
+    <cacheField name="Tvegano%" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.80769230769230771"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="171">
   <r>
@@ -4138,8 +5674,1586 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="143">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1424"/>
+    <n v="491"/>
+    <n v="631"/>
+    <n v="2546"/>
+    <n v="0.55930871956009431"/>
+    <n v="0.19285153181461115"/>
+    <n v="0.24783974862529459"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="3050"/>
+    <n v="293"/>
+    <n v="107"/>
+    <n v="3450"/>
+    <n v="0.88405797101449279"/>
+    <n v="8.4927536231884052E-2"/>
+    <n v="3.1014492753623189E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1912"/>
+    <n v="915"/>
+    <n v="1332"/>
+    <n v="4159"/>
+    <n v="0.45972589564799232"/>
+    <n v="0.22000480884828083"/>
+    <n v="0.32026929550372685"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2274"/>
+    <n v="547"/>
+    <n v="236"/>
+    <n v="3057"/>
+    <n v="0.74386653581943085"/>
+    <n v="0.17893359502780504"/>
+    <n v="7.7199869152764153E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1280"/>
+    <n v="419"/>
+    <n v="1709"/>
+    <n v="3408"/>
+    <n v="0.37558685446009388"/>
+    <n v="0.12294600938967136"/>
+    <n v="0.50146713615023475"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="2105"/>
+    <n v="1082"/>
+    <n v="664"/>
+    <n v="3851"/>
+    <n v="0.54661126980005192"/>
+    <n v="0.28096598286159441"/>
+    <n v="0.17242274733835367"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="3903"/>
+    <n v="205"/>
+    <n v="90"/>
+    <n v="4198"/>
+    <n v="0.92972844211529304"/>
+    <n v="4.8832777513101479E-2"/>
+    <n v="2.1438780371605525E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="221"/>
+    <n v="116"/>
+    <n v="469"/>
+    <n v="806"/>
+    <n v="0.27419354838709675"/>
+    <n v="0.14392059553349876"/>
+    <n v="0.58188585607940446"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="1505"/>
+    <n v="308"/>
+    <n v="1347"/>
+    <n v="3160"/>
+    <n v="0.47626582278481011"/>
+    <n v="9.7468354430379753E-2"/>
+    <n v="0.42626582278481012"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="3005"/>
+    <n v="106"/>
+    <n v="158"/>
+    <n v="3269"/>
+    <n v="0.91924135821352093"/>
+    <n v="3.2425818293055977E-2"/>
+    <n v="4.8332823493423063E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="1051"/>
+    <n v="158"/>
+    <n v="105"/>
+    <n v="1314"/>
+    <n v="0.79984779299847797"/>
+    <n v="0.12024353120243531"/>
+    <n v="7.9908675799086754E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="76"/>
+    <n v="20"/>
+    <n v="22"/>
+    <n v="118"/>
+    <n v="0.64406779661016944"/>
+    <n v="0.16949152542372881"/>
+    <n v="0.1864406779661017"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="236"/>
+    <n v="22"/>
+    <n v="3"/>
+    <n v="261"/>
+    <n v="0.90421455938697315"/>
+    <n v="8.4291187739463605E-2"/>
+    <n v="1.1494252873563218E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="139"/>
+    <n v="65"/>
+    <n v="84"/>
+    <n v="288"/>
+    <n v="0.4826388888888889"/>
+    <n v="0.22569444444444445"/>
+    <n v="0.29166666666666669"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="173"/>
+    <n v="55"/>
+    <n v="16"/>
+    <n v="244"/>
+    <n v="0.70901639344262291"/>
+    <n v="0.22540983606557377"/>
+    <n v="6.5573770491803282E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="91"/>
+    <n v="38"/>
+    <n v="114"/>
+    <n v="243"/>
+    <n v="0.37448559670781895"/>
+    <n v="0.15637860082304528"/>
+    <n v="0.46913580246913578"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="145"/>
+    <n v="91"/>
+    <n v="63"/>
+    <n v="299"/>
+    <n v="0.48494983277591974"/>
+    <n v="0.30434782608695654"/>
+    <n v="0.21070234113712374"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="297"/>
+    <n v="14"/>
+    <n v="4"/>
+    <n v="315"/>
+    <n v="0.94285714285714284"/>
+    <n v="4.4444444444444446E-2"/>
+    <n v="1.2698412698412698E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="29"/>
+    <n v="10"/>
+    <n v="72"/>
+    <n v="111"/>
+    <n v="0.26126126126126126"/>
+    <n v="9.0090090090090086E-2"/>
+    <n v="0.64864864864864868"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="125"/>
+    <n v="29"/>
+    <n v="83"/>
+    <n v="237"/>
+    <n v="0.52742616033755274"/>
+    <n v="0.12236286919831224"/>
+    <n v="0.35021097046413502"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="225"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="243"/>
+    <n v="0.92592592592592593"/>
+    <n v="2.8806584362139918E-2"/>
+    <n v="4.5267489711934158E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="114"/>
+    <n v="12"/>
+    <n v="11"/>
+    <n v="137"/>
+    <n v="0.83211678832116787"/>
+    <n v="8.7591240875912413E-2"/>
+    <n v="8.0291970802919707E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="47"/>
+    <n v="14"/>
+    <n v="17"/>
+    <n v="78"/>
+    <n v="0.60256410256410253"/>
+    <n v="0.17948717948717949"/>
+    <n v="0.21794871794871795"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="73"/>
+    <n v="9"/>
+    <n v="1"/>
+    <n v="83"/>
+    <n v="0.87951807228915657"/>
+    <n v="0.10843373493975904"/>
+    <n v="1.2048192771084338E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="56"/>
+    <n v="19"/>
+    <n v="31"/>
+    <n v="106"/>
+    <n v="0.52830188679245282"/>
+    <n v="0.17924528301886791"/>
+    <n v="0.29245283018867924"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="60"/>
+    <n v="15"/>
+    <n v="2"/>
+    <n v="77"/>
+    <n v="0.77922077922077926"/>
+    <n v="0.19480519480519481"/>
+    <n v="2.5974025974025976E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="26"/>
+    <n v="10"/>
+    <n v="43"/>
+    <n v="79"/>
+    <n v="0.32911392405063289"/>
+    <n v="0.12658227848101267"/>
+    <n v="0.54430379746835444"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="69"/>
+    <n v="25"/>
+    <n v="27"/>
+    <n v="121"/>
+    <n v="0.57024793388429751"/>
+    <n v="0.20661157024793389"/>
+    <n v="0.2231404958677686"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="112"/>
+    <n v="6"/>
+    <n v="1"/>
+    <n v="119"/>
+    <n v="0.94117647058823528"/>
+    <n v="5.0420168067226892E-2"/>
+    <n v="8.4033613445378148E-3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="7"/>
+    <n v="0.42857142857142855"/>
+    <n v="0"/>
+    <n v="0.5714285714285714"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="33"/>
+    <n v="7"/>
+    <n v="34"/>
+    <n v="74"/>
+    <n v="0.44594594594594594"/>
+    <n v="9.45945945945946E-2"/>
+    <n v="0.45945945945945948"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <n v="69"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="76"/>
+    <n v="0.90789473684210531"/>
+    <n v="2.6315789473684209E-2"/>
+    <n v="6.5789473684210523E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <n v="10"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="15"/>
+    <n v="0.66666666666666663"/>
+    <n v="0.2"/>
+    <n v="0.13333333333333333"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="61"/>
+    <n v="15"/>
+    <n v="26"/>
+    <n v="102"/>
+    <n v="0.59803921568627449"/>
+    <n v="0.14705882352941177"/>
+    <n v="0.25490196078431371"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="114"/>
+    <n v="14"/>
+    <n v="1"/>
+    <n v="129"/>
+    <n v="0.88372093023255816"/>
+    <n v="0.10852713178294573"/>
+    <n v="7.7519379844961239E-3"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="86"/>
+    <n v="28"/>
+    <n v="51"/>
+    <n v="165"/>
+    <n v="0.52121212121212124"/>
+    <n v="0.16969696969696971"/>
+    <n v="0.30909090909090908"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="87"/>
+    <n v="21"/>
+    <n v="11"/>
+    <n v="119"/>
+    <n v="0.73109243697478987"/>
+    <n v="0.17647058823529413"/>
+    <n v="9.2436974789915971E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="52"/>
+    <n v="20"/>
+    <n v="68"/>
+    <n v="140"/>
+    <n v="0.37142857142857144"/>
+    <n v="0.14285714285714285"/>
+    <n v="0.48571428571428571"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="82"/>
+    <n v="41"/>
+    <n v="33"/>
+    <n v="156"/>
+    <n v="0.52564102564102566"/>
+    <n v="0.26282051282051283"/>
+    <n v="0.21153846153846154"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="152"/>
+    <n v="11"/>
+    <n v="3"/>
+    <n v="166"/>
+    <n v="0.91566265060240959"/>
+    <n v="6.6265060240963861E-2"/>
+    <n v="1.8072289156626505E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="13"/>
+    <n v="17"/>
+    <n v="0.17647058823529413"/>
+    <n v="5.8823529411764705E-2"/>
+    <n v="0.76470588235294112"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="8"/>
+    <n v="53"/>
+    <n v="14"/>
+    <n v="47"/>
+    <n v="114"/>
+    <n v="0.46491228070175439"/>
+    <n v="0.12280701754385964"/>
+    <n v="0.41228070175438597"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="106"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="116"/>
+    <n v="0.91379310344827591"/>
+    <n v="6.0344827586206899E-2"/>
+    <n v="2.5862068965517241E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="43"/>
+    <n v="12"/>
+    <n v="6"/>
+    <n v="61"/>
+    <n v="0.70491803278688525"/>
+    <n v="0.19672131147540983"/>
+    <n v="9.8360655737704916E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="17"/>
+    <n v="6"/>
+    <n v="15"/>
+    <n v="38"/>
+    <n v="0.44736842105263158"/>
+    <n v="0.15789473684210525"/>
+    <n v="0.39473684210526316"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="55"/>
+    <n v="6"/>
+    <n v="4"/>
+    <n v="65"/>
+    <n v="0.84615384615384615"/>
+    <n v="9.2307692307692313E-2"/>
+    <n v="6.1538461538461542E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="31"/>
+    <n v="15"/>
+    <n v="20"/>
+    <n v="66"/>
+    <n v="0.46969696969696972"/>
+    <n v="0.22727272727272727"/>
+    <n v="0.30303030303030304"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="51"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="62"/>
+    <n v="0.82258064516129037"/>
+    <n v="0.12903225806451613"/>
+    <n v="4.8387096774193547E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="17"/>
+    <n v="6"/>
+    <n v="38"/>
+    <n v="61"/>
+    <n v="0.27868852459016391"/>
+    <n v="9.8360655737704916E-2"/>
+    <n v="0.62295081967213117"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="41"/>
+    <n v="19"/>
+    <n v="11"/>
+    <n v="71"/>
+    <n v="0.57746478873239437"/>
+    <n v="0.26760563380281688"/>
+    <n v="0.15492957746478872"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="66"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="71"/>
+    <n v="0.92957746478873238"/>
+    <n v="4.2253521126760563E-2"/>
+    <n v="2.8169014084507043E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="12"/>
+    <n v="15"/>
+    <n v="0.2"/>
+    <n v="0"/>
+    <n v="0.8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="19"/>
+    <n v="7"/>
+    <n v="33"/>
+    <n v="59"/>
+    <n v="0.32203389830508472"/>
+    <n v="0.11864406779661017"/>
+    <n v="0.55932203389830504"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="9"/>
+    <n v="57"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="60"/>
+    <n v="0.95"/>
+    <n v="0"/>
+    <n v="0.05"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="10"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="38"/>
+    <n v="6"/>
+    <n v="21"/>
+    <n v="65"/>
+    <n v="0.58461538461538465"/>
+    <n v="9.2307692307692313E-2"/>
+    <n v="0.32307692307692309"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="89"/>
+    <n v="8"/>
+    <n v="6"/>
+    <n v="103"/>
+    <n v="0.86407766990291257"/>
+    <n v="7.7669902912621352E-2"/>
+    <n v="5.8252427184466021E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="53"/>
+    <n v="18"/>
+    <n v="43"/>
+    <n v="114"/>
+    <n v="0.46491228070175439"/>
+    <n v="0.15789473684210525"/>
+    <n v="0.37719298245614036"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="70"/>
+    <n v="19"/>
+    <n v="8"/>
+    <n v="97"/>
+    <n v="0.72164948453608246"/>
+    <n v="0.19587628865979381"/>
+    <n v="8.247422680412371E-2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="36"/>
+    <n v="9"/>
+    <n v="55"/>
+    <n v="100"/>
+    <n v="0.36"/>
+    <n v="0.09"/>
+    <n v="0.55000000000000004"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="60"/>
+    <n v="41"/>
+    <n v="28"/>
+    <n v="129"/>
+    <n v="0.46511627906976744"/>
+    <n v="0.31782945736434109"/>
+    <n v="0.21705426356589147"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="126"/>
+    <n v="10"/>
+    <n v="1"/>
+    <n v="137"/>
+    <n v="0.91970802919708028"/>
+    <n v="7.2992700729927001E-2"/>
+    <n v="7.2992700729927005E-3"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="25"/>
+    <n v="31"/>
+    <n v="9.6774193548387094E-2"/>
+    <n v="9.6774193548387094E-2"/>
+    <n v="0.80645161290322576"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="36"/>
+    <n v="17"/>
+    <n v="45"/>
+    <n v="98"/>
+    <n v="0.36734693877551022"/>
+    <n v="0.17346938775510204"/>
+    <n v="0.45918367346938777"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="9"/>
+    <n v="90"/>
+    <n v="2"/>
+    <n v="8"/>
+    <n v="100"/>
+    <n v="0.9"/>
+    <n v="0.02"/>
+    <n v="0.08"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="10"/>
+    <n v="20"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="26"/>
+    <n v="0.76923076923076927"/>
+    <n v="7.6923076923076927E-2"/>
+    <n v="0.15384615384615385"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="674"/>
+    <n v="250"/>
+    <n v="306"/>
+    <n v="1230"/>
+    <n v="0.54796747967479675"/>
+    <n v="0.2032520325203252"/>
+    <n v="0.24878048780487805"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="1298"/>
+    <n v="128"/>
+    <n v="56"/>
+    <n v="1482"/>
+    <n v="0.87584345479082326"/>
+    <n v="8.6369770580296892E-2"/>
+    <n v="3.7786774628879895E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="854"/>
+    <n v="441"/>
+    <n v="598"/>
+    <n v="1893"/>
+    <n v="0.45113576333861594"/>
+    <n v="0.23296354992076071"/>
+    <n v="0.31590068674062333"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="977"/>
+    <n v="233"/>
+    <n v="112"/>
+    <n v="1322"/>
+    <n v="0.73903177004538578"/>
+    <n v="0.1762481089258699"/>
+    <n v="8.4720121028744322E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="555"/>
+    <n v="177"/>
+    <n v="735"/>
+    <n v="1467"/>
+    <n v="0.3783231083844581"/>
+    <n v="0.12065439672801637"/>
+    <n v="0.50102249488752559"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="860"/>
+    <n v="455"/>
+    <n v="248"/>
+    <n v="1563"/>
+    <n v="0.55022392834293021"/>
+    <n v="0.29110684580934099"/>
+    <n v="0.15866922584772872"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="1679"/>
+    <n v="100"/>
+    <n v="49"/>
+    <n v="1828"/>
+    <n v="0.91849015317286653"/>
+    <n v="5.4704595185995623E-2"/>
+    <n v="2.6805251641137857E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="7"/>
+    <n v="119"/>
+    <n v="61"/>
+    <n v="260"/>
+    <n v="440"/>
+    <n v="0.27045454545454545"/>
+    <n v="0.13863636363636364"/>
+    <n v="0.59090909090909094"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <n v="626"/>
+    <n v="149"/>
+    <n v="591"/>
+    <n v="1366"/>
+    <n v="0.45827232796486089"/>
+    <n v="0.10907759882869693"/>
+    <n v="0.43265007320644217"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="9"/>
+    <n v="1301"/>
+    <n v="52"/>
+    <n v="78"/>
+    <n v="1431"/>
+    <n v="0.90915443745632429"/>
+    <n v="3.6338225017470298E-2"/>
+    <n v="5.450733752620545E-2"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="10"/>
+    <n v="575"/>
+    <n v="86"/>
+    <n v="53"/>
+    <n v="714"/>
+    <n v="0.80532212885154064"/>
+    <n v="0.12044817927170869"/>
+    <n v="7.42296918767507E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="41"/>
+    <n v="12"/>
+    <n v="9"/>
+    <n v="62"/>
+    <n v="0.66129032258064513"/>
+    <n v="0.19354838709677419"/>
+    <n v="0.14516129032258066"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="115"/>
+    <n v="9"/>
+    <n v="7"/>
+    <n v="131"/>
+    <n v="0.87786259541984735"/>
+    <n v="6.8702290076335881E-2"/>
+    <n v="5.3435114503816793E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="79"/>
+    <n v="32"/>
+    <n v="33"/>
+    <n v="144"/>
+    <n v="0.54861111111111116"/>
+    <n v="0.22222222222222221"/>
+    <n v="0.22916666666666666"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="86"/>
+    <n v="28"/>
+    <n v="2"/>
+    <n v="116"/>
+    <n v="0.74137931034482762"/>
+    <n v="0.2413793103448276"/>
+    <n v="1.7241379310344827E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="43"/>
+    <n v="12"/>
+    <n v="69"/>
+    <n v="124"/>
+    <n v="0.34677419354838712"/>
+    <n v="9.6774193548387094E-2"/>
+    <n v="0.55645161290322576"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="107"/>
+    <n v="38"/>
+    <n v="49"/>
+    <n v="194"/>
+    <n v="0.55154639175257736"/>
+    <n v="0.19587628865979381"/>
+    <n v="0.25257731958762886"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="6"/>
+    <n v="189"/>
+    <n v="13"/>
+    <n v="3"/>
+    <n v="205"/>
+    <n v="0.92195121951219516"/>
+    <n v="6.3414634146341464E-2"/>
+    <n v="1.4634146341463415E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="13"/>
+    <n v="21"/>
+    <n v="0.23809523809523808"/>
+    <n v="0.14285714285714285"/>
+    <n v="0.61904761904761907"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="8"/>
+    <n v="61"/>
+    <n v="9"/>
+    <n v="48"/>
+    <n v="118"/>
+    <n v="0.51694915254237284"/>
+    <n v="7.6271186440677971E-2"/>
+    <n v="0.40677966101694918"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="9"/>
+    <n v="113"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="118"/>
+    <n v="0.9576271186440678"/>
+    <n v="1.6949152542372881E-2"/>
+    <n v="2.5423728813559324E-2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="10"/>
+    <n v="48"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="56"/>
+    <n v="0.8571428571428571"/>
+    <n v="8.9285714285714288E-2"/>
+    <n v="5.3571428571428568E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="21"/>
+    <n v="8"/>
+    <n v="9"/>
+    <n v="38"/>
+    <n v="0.55263157894736847"/>
+    <n v="0.21052631578947367"/>
+    <n v="0.23684210526315788"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="50"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="55"/>
+    <n v="0.90909090909090906"/>
+    <n v="3.6363636363636362E-2"/>
+    <n v="5.4545454545454543E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="11"/>
+    <n v="8"/>
+    <n v="38"/>
+    <n v="57"/>
+    <n v="0.19298245614035087"/>
+    <n v="0.14035087719298245"/>
+    <n v="0.66666666666666663"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="39"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="47"/>
+    <n v="0.82978723404255317"/>
+    <n v="0.1276595744680851"/>
+    <n v="4.2553191489361701E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="42"/>
+    <n v="52"/>
+    <n v="0.19230769230769232"/>
+    <n v="0"/>
+    <n v="0.80769230769230771"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="34"/>
+    <n v="29"/>
+    <n v="17"/>
+    <n v="80"/>
+    <n v="0.42499999999999999"/>
+    <n v="0.36249999999999999"/>
+    <n v="0.21249999999999999"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="6"/>
+    <n v="76"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="82"/>
+    <n v="0.92682926829268297"/>
+    <n v="6.097560975609756E-2"/>
+    <n v="1.2195121951219513E-2"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0.25"/>
+    <n v="0.5"/>
+    <n v="0.25"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="11"/>
+    <n v="0"/>
+    <n v="38"/>
+    <n v="49"/>
+    <n v="0.22448979591836735"/>
+    <n v="0"/>
+    <n v="0.77551020408163263"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="9"/>
+    <n v="45"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="52"/>
+    <n v="0.86538461538461542"/>
+    <n v="0.13461538461538461"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="10"/>
+    <n v="7"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="0.77777777777777779"/>
+    <n v="0.22222222222222221"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="68"/>
+    <n v="36"/>
+    <n v="25"/>
+    <n v="129"/>
+    <n v="0.52713178294573648"/>
+    <n v="0.27906976744186046"/>
+    <n v="0.19379844961240311"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="149"/>
+    <n v="0.97315436241610742"/>
+    <n v="2.6845637583892617E-2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="48"/>
+    <n v="18"/>
+    <n v="87"/>
+    <n v="153"/>
+    <n v="0.31372549019607843"/>
+    <n v="0.11764705882352941"/>
+    <n v="0.56862745098039214"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="81"/>
+    <n v="33"/>
+    <n v="21"/>
+    <n v="135"/>
+    <n v="0.6"/>
+    <n v="0.24444444444444444"/>
+    <n v="0.15555555555555556"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="30"/>
+    <n v="16"/>
+    <n v="96"/>
+    <n v="142"/>
+    <n v="0.21126760563380281"/>
+    <n v="0.11267605633802817"/>
+    <n v="0.676056338028169"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="78"/>
+    <n v="57"/>
+    <n v="14"/>
+    <n v="149"/>
+    <n v="0.52348993288590606"/>
+    <n v="0.3825503355704698"/>
+    <n v="9.3959731543624164E-2"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="6"/>
+    <n v="151"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="152"/>
+    <n v="0.99342105263157898"/>
+    <n v="0"/>
+    <n v="6.5789473684210523E-3"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="7"/>
+    <n v="9"/>
+    <n v="0.1111111111111111"/>
+    <n v="0.1111111111111111"/>
+    <n v="0.77777777777777779"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="8"/>
+    <n v="54"/>
+    <n v="6"/>
+    <n v="77"/>
+    <n v="137"/>
+    <n v="0.39416058394160586"/>
+    <n v="4.3795620437956206E-2"/>
+    <n v="0.56204379562043794"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="139"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="142"/>
+    <n v="0.97887323943661975"/>
+    <n v="7.0422535211267607E-3"/>
+    <n v="1.4084507042253521E-2"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="10"/>
+    <n v="13"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="14"/>
+    <n v="0.9285714285714286"/>
+    <n v="7.1428571428571425E-2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="20"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="28"/>
+    <n v="0.7142857142857143"/>
+    <n v="0.14285714285714285"/>
+    <n v="0.14285714285714285"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="39"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="42"/>
+    <n v="0.9285714285714286"/>
+    <n v="7.1428571428571425E-2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="16"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="46"/>
+    <n v="0.34782608695652173"/>
+    <n v="0.32608695652173914"/>
+    <n v="0.32608695652173914"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="30"/>
+    <n v="5"/>
+    <n v="4"/>
+    <n v="39"/>
+    <n v="0.76923076923076927"/>
+    <n v="0.12820512820512819"/>
+    <n v="0.10256410256410256"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="18"/>
+    <n v="5"/>
+    <n v="20"/>
+    <n v="43"/>
+    <n v="0.41860465116279072"/>
+    <n v="0.11627906976744186"/>
+    <n v="0.46511627906976744"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="37"/>
+    <n v="6"/>
+    <n v="3"/>
+    <n v="46"/>
+    <n v="0.80434782608695654"/>
+    <n v="0.13043478260869565"/>
+    <n v="6.5217391304347824E-2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="44"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="46"/>
+    <n v="0.95652173913043481"/>
+    <n v="0"/>
+    <n v="4.3478260869565216E-2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="9"/>
+    <n v="0.33333333333333331"/>
+    <n v="0"/>
+    <n v="0.66666666666666663"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="8"/>
+    <n v="22"/>
+    <n v="2"/>
+    <n v="18"/>
+    <n v="42"/>
+    <n v="0.52380952380952384"/>
+    <n v="4.7619047619047616E-2"/>
+    <n v="0.42857142857142855"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="9"/>
+    <n v="38"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="41"/>
+    <n v="0.92682926829268297"/>
+    <n v="4.878048780487805E-2"/>
+    <n v="2.4390243902439025E-2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="11"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="14"/>
+    <n v="0.7857142857142857"/>
+    <n v="7.1428571428571425E-2"/>
+    <n v="0.14285714285714285"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="75"/>
+    <n v="27"/>
+    <n v="26"/>
+    <n v="128"/>
+    <n v="0.5859375"/>
+    <n v="0.2109375"/>
+    <n v="0.203125"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="210"/>
+    <n v="23"/>
+    <n v="1"/>
+    <n v="234"/>
+    <n v="0.89743589743589747"/>
+    <n v="9.8290598290598288E-2"/>
+    <n v="4.2735042735042739E-3"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="125"/>
+    <n v="58"/>
+    <n v="70"/>
+    <n v="253"/>
+    <n v="0.49407114624505927"/>
+    <n v="0.22924901185770752"/>
+    <n v="0.27667984189723321"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="170"/>
+    <n v="34"/>
+    <n v="13"/>
+    <n v="217"/>
+    <n v="0.78341013824884798"/>
+    <n v="0.15668202764976957"/>
+    <n v="5.9907834101382486E-2"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="89"/>
+    <n v="33"/>
+    <n v="110"/>
+    <n v="232"/>
+    <n v="0.38362068965517243"/>
+    <n v="0.14224137931034483"/>
+    <n v="0.47413793103448276"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="139"/>
+    <n v="85"/>
+    <n v="66"/>
+    <n v="290"/>
+    <n v="0.47931034482758622"/>
+    <n v="0.29310344827586204"/>
+    <n v="0.22758620689655173"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="263"/>
+    <n v="25"/>
+    <n v="10"/>
+    <n v="298"/>
+    <n v="0.8825503355704698"/>
+    <n v="8.3892617449664433E-2"/>
+    <n v="3.3557046979865772E-2"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="36"/>
+    <n v="23"/>
+    <n v="20"/>
+    <n v="79"/>
+    <n v="0.45569620253164556"/>
+    <n v="0.29113924050632911"/>
+    <n v="0.25316455696202533"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="8"/>
+    <n v="104"/>
+    <n v="35"/>
+    <n v="74"/>
+    <n v="213"/>
+    <n v="0.48826291079812206"/>
+    <n v="0.16431924882629109"/>
+    <n v="0.34741784037558687"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="9"/>
+    <n v="203"/>
+    <n v="5"/>
+    <n v="8"/>
+    <n v="216"/>
+    <n v="0.93981481481481477"/>
+    <n v="2.3148148148148147E-2"/>
+    <n v="3.7037037037037035E-2"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="10"/>
+    <n v="86"/>
+    <n v="22"/>
+    <n v="17"/>
+    <n v="125"/>
+    <n v="0.68799999999999994"/>
+    <n v="0.17599999999999999"/>
+    <n v="0.13600000000000001"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="7"/>
+    <n v="5"/>
+    <n v="22"/>
+    <n v="0.45454545454545453"/>
+    <n v="0.31818181818181818"/>
+    <n v="0.22727272727272727"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="26"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="30"/>
+    <n v="0.8666666666666667"/>
+    <n v="0.13333333333333333"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="11"/>
+    <n v="3"/>
+    <n v="18"/>
+    <n v="32"/>
+    <n v="0.34375"/>
+    <n v="9.375E-2"/>
+    <n v="0.5625"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="13"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="28"/>
+    <n v="0.4642857142857143"/>
+    <n v="0.35714285714285715"/>
+    <n v="0.17857142857142858"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="8"/>
+    <n v="2"/>
+    <n v="20"/>
+    <n v="30"/>
+    <n v="0.26666666666666666"/>
+    <n v="6.6666666666666666E-2"/>
+    <n v="0.66666666666666663"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="19"/>
+    <n v="14"/>
+    <n v="4"/>
+    <n v="37"/>
+    <n v="0.51351351351351349"/>
+    <n v="0.3783783783783784"/>
+    <n v="0.10810810810810811"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="36"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="39"/>
+    <n v="0.92307692307692313"/>
+    <n v="5.128205128205128E-2"/>
+    <n v="2.564102564102564E-2"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <n v="0"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="8"/>
+    <n v="9"/>
+    <n v="1"/>
+    <n v="17"/>
+    <n v="27"/>
+    <n v="0.33333333333333331"/>
+    <n v="3.7037037037037035E-2"/>
+    <n v="0.62962962962962965"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="9"/>
+    <n v="23"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="26"/>
+    <n v="0.88461538461538458"/>
+    <n v="7.6923076923076927E-2"/>
+    <n v="3.8461538461538464E-2"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="10"/>
+    <n v="8"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="10"/>
+    <n v="0.8"/>
+    <n v="0.1"/>
+    <n v="0.1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="H4:I18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -4247,7 +7361,7 @@
     <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -4273,7 +7387,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -4311,6 +7425,170 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED1F8AC9-8CC5-4E08-995C-C481136EF10E}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="K4:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" item="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Average of Tvegano%" fld="8" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of Mejno%" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4717,6 +7995,65 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-04-03T05:49:55.82" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{BFFC901B-821E-4A6C-8204-68AA98345E97}">
+    <text>SELECT 'Slovenija' as Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+  AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
+GROUP BY
+    te.Ime
+--ORDER BY     te.Ime
+UNION ALL
+SELECT
+    rgn.Name AS Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = c.ID
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+  AND du.IdVloga = 10
+  AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
+GROUP BY
+    rgn.Name,
+    te.Ime
+ORDER BY
+    Regija ASC,
+    te.Ime ASC;</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="A1" dT="2026-04-01T17:39:40.25" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{27CA99E9-B9D0-4DB6-9B7E-D9517DFCF062}">
     <text>SELECT TABLE_NAME FROM INFORMATION_SCHEMA.TABLES where TABLE_NAME like '%regi%'  --WHERE TABLE_TYPE='BASE TABLE'
 select top 945 * from FitnessMapStates --212 občin
@@ -7355,15 +10692,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5174BCBC-B217-4578-9C7C-78EA70EB9E43}">
-  <dimension ref="A1:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5174BCBC-B217-4578-9C7C-78EA70EB9E43}">
+  <dimension ref="A1:M144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="6.21875" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>512</v>
       </c>
@@ -7395,74 +10737,4870 @@
         <v>Tvegano%</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>505</v>
       </c>
       <c r="B2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C2">
-        <v>6666</v>
+        <v>1424</v>
       </c>
       <c r="D2">
-        <v>3333</v>
+        <v>491</v>
       </c>
       <c r="E2">
-        <v>1111</v>
+        <v>631</v>
       </c>
       <c r="F2">
         <f>SUM(C2:E2)</f>
-        <v>11110</v>
+        <v>2546</v>
       </c>
       <c r="G2" s="3">
         <f>C2/$F2</f>
+        <v>0.55930871956009431</v>
+      </c>
+      <c r="H2" s="3">
+        <f t="shared" ref="H2" si="1">D2/$F2</f>
+        <v>0.19285153181461115</v>
+      </c>
+      <c r="I2" s="3">
+        <f t="shared" ref="I2" si="2">E2/$F2</f>
+        <v>0.24783974862529459</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="L2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C3">
+        <v>3050</v>
+      </c>
+      <c r="D3">
+        <v>293</v>
+      </c>
+      <c r="E3">
+        <v>107</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="3">SUM(C3:E3)</f>
+        <v>3450</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G66" si="4">C3/$F3</f>
+        <v>0.88405797101449279</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H66" si="5">D3/$F3</f>
+        <v>8.4927536231884052E-2</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I66" si="6">E3/$F3</f>
+        <v>3.1014492753623189E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4">
+        <v>1912</v>
+      </c>
+      <c r="D4">
+        <v>915</v>
+      </c>
+      <c r="E4">
+        <v>1332</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="3"/>
+        <v>4159</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" si="4"/>
+        <v>0.45972589564799232</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" si="5"/>
+        <v>0.22000480884828083</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="6"/>
+        <v>0.32026929550372685</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="L4" t="s">
+        <v>534</v>
+      </c>
+      <c r="M4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5">
+        <v>2274</v>
+      </c>
+      <c r="D5">
+        <v>547</v>
+      </c>
+      <c r="E5">
+        <v>236</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="3"/>
+        <v>3057</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="4"/>
+        <v>0.74386653581943085</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17893359502780504</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="6"/>
+        <v>7.7199869152764153E-2</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0.1864406779661017</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0.16949152542372881</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C6">
+        <v>1280</v>
+      </c>
+      <c r="D6">
+        <v>419</v>
+      </c>
+      <c r="E6">
+        <v>1709</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>3408</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="4"/>
+        <v>0.37558685446009388</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12294600938967136</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="6"/>
+        <v>0.50146713615023475</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0.21794871794871795</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>505</v>
+      </c>
+      <c r="B7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C7">
+        <v>2105</v>
+      </c>
+      <c r="D7">
+        <v>1082</v>
+      </c>
+      <c r="E7">
+        <v>664</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>3851</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="4"/>
+        <v>0.54661126980005192</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="5"/>
+        <v>0.28096598286159441</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="6"/>
+        <v>0.17242274733835367</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0.25490196078431371</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0.14705882352941177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B8" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8">
+        <v>3903</v>
+      </c>
+      <c r="D8">
+        <v>205</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>4198</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="4"/>
+        <v>0.92972844211529304</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="5"/>
+        <v>4.8832777513101479E-2</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="6"/>
+        <v>2.1438780371605525E-2</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.39473684210526316</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0.15789473684210525</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B9" t="s">
+        <v>523</v>
+      </c>
+      <c r="C9">
+        <v>221</v>
+      </c>
+      <c r="D9">
+        <v>116</v>
+      </c>
+      <c r="E9">
+        <v>469</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="3"/>
+        <v>806</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="4"/>
+        <v>0.27419354838709675</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="5"/>
+        <v>0.14392059553349876</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="6"/>
+        <v>0.58188585607940446</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0.32307692307692309</v>
+      </c>
+      <c r="M9" s="9">
+        <v>9.2307692307692313E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>505</v>
+      </c>
+      <c r="B10" t="s">
+        <v>524</v>
+      </c>
+      <c r="C10">
+        <v>1505</v>
+      </c>
+      <c r="D10">
+        <v>308</v>
+      </c>
+      <c r="E10">
+        <v>1347</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>3160</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="4"/>
+        <v>0.47626582278481011</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="5"/>
+        <v>9.7468354430379753E-2</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="6"/>
+        <v>0.42626582278481012</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0.24878048780487805</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0.2032520325203252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>505</v>
+      </c>
+      <c r="B11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C11">
+        <v>3005</v>
+      </c>
+      <c r="D11">
+        <v>106</v>
+      </c>
+      <c r="E11">
+        <v>158</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="3"/>
+        <v>3269</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="4"/>
+        <v>0.91924135821352093</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="5"/>
+        <v>3.2425818293055977E-2</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="6"/>
+        <v>4.8332823493423063E-2</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0.14516129032258066</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0.19354838709677419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>505</v>
+      </c>
+      <c r="B12" t="s">
+        <v>528</v>
+      </c>
+      <c r="C12">
+        <v>1051</v>
+      </c>
+      <c r="D12">
+        <v>158</v>
+      </c>
+      <c r="E12">
+        <v>105</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>1314</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="4"/>
+        <v>0.79984779299847797</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12024353120243531</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="6"/>
+        <v>7.9908675799086754E-2</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0.23684210526315788</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>517</v>
+      </c>
+      <c r="C13">
+        <v>76</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>118</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="4"/>
+        <v>0.64406779661016944</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="5"/>
+        <v>0.16949152542372881</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="6"/>
+        <v>0.1864406779661017</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0.19379844961240311</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0.27906976744186046</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>518</v>
+      </c>
+      <c r="C14">
+        <v>236</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>261</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="4"/>
+        <v>0.90421455938697315</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="5"/>
+        <v>8.4291187739463605E-2</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1494252873563218E-2</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>510</v>
+      </c>
+      <c r="C15">
+        <v>139</v>
+      </c>
+      <c r="D15">
+        <v>65</v>
+      </c>
+      <c r="E15">
+        <v>84</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>288</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="4"/>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="5"/>
+        <v>0.22569444444444445</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="6"/>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0.203125</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0.2109375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>519</v>
+      </c>
+      <c r="C16">
+        <v>173</v>
+      </c>
+      <c r="D16">
+        <v>55</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>244</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="4"/>
+        <v>0.70901639344262291</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="5"/>
+        <v>0.22540983606557377</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="6"/>
+        <v>6.5573770491803282E-2</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0.24783974862529459</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0.19285153181461115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>520</v>
+      </c>
+      <c r="C17">
+        <v>91</v>
+      </c>
+      <c r="D17">
+        <v>38</v>
+      </c>
+      <c r="E17">
+        <v>114</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="4"/>
+        <v>0.37448559670781895</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="5"/>
+        <v>0.15637860082304528</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="6"/>
+        <v>0.46913580246913578</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0.31818181818181818</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>521</v>
+      </c>
+      <c r="C18">
+        <v>145</v>
+      </c>
+      <c r="D18">
+        <v>91</v>
+      </c>
+      <c r="E18">
+        <v>63</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>299</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="4"/>
+        <v>0.48494983277591974</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="5"/>
+        <v>0.30434782608695654</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="6"/>
+        <v>0.21070234113712374</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.23252169797226951</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0.19211265025324029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C19">
+        <v>297</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="4"/>
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="5"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="6"/>
+        <v>1.2698412698412698E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>523</v>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>72</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="4"/>
+        <v>0.26126126126126126</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="5"/>
+        <v>9.0090090090090086E-2</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="6"/>
+        <v>0.64864864864864868</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>524</v>
+      </c>
+      <c r="C21">
+        <v>125</v>
+      </c>
+      <c r="D21">
+        <v>29</v>
+      </c>
+      <c r="E21">
+        <v>83</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="4"/>
+        <v>0.52742616033755274</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12236286919831224</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="6"/>
+        <v>0.35021097046413502</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>527</v>
+      </c>
+      <c r="C22">
+        <v>225</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="4"/>
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="5"/>
+        <v>2.8806584362139918E-2</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="6"/>
+        <v>4.5267489711934158E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>528</v>
+      </c>
+      <c r="C23">
+        <v>114</v>
+      </c>
+      <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>137</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="4"/>
+        <v>0.83211678832116787</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="5"/>
+        <v>8.7591240875912413E-2</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="6"/>
+        <v>8.0291970802919707E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>517</v>
+      </c>
+      <c r="C24">
+        <v>47</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60256410256410253</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="6"/>
+        <v>0.21794871794871795</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>518</v>
+      </c>
+      <c r="C25">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="4"/>
+        <v>0.87951807228915657</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="5"/>
+        <v>0.10843373493975904</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="6"/>
+        <v>1.2048192771084338E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>510</v>
+      </c>
+      <c r="C26">
+        <v>56</v>
+      </c>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>31</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>106</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="4"/>
+        <v>0.52830188679245282</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17924528301886791</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="6"/>
+        <v>0.29245283018867924</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>519</v>
+      </c>
+      <c r="C27">
+        <v>60</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="4"/>
+        <v>0.77922077922077926</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="5"/>
+        <v>0.19480519480519481</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="6"/>
+        <v>2.5974025974025976E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>520</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>43</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>79</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="4"/>
+        <v>0.32911392405063289</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12658227848101267</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="6"/>
+        <v>0.54430379746835444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>521</v>
+      </c>
+      <c r="C29">
+        <v>69</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29">
+        <v>27</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>121</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="4"/>
+        <v>0.57024793388429751</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="5"/>
+        <v>0.20661157024793389</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="6"/>
+        <v>0.2231404958677686</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>522</v>
+      </c>
+      <c r="C30">
+        <v>112</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="4"/>
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="5"/>
+        <v>5.0420168067226892E-2</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="6"/>
+        <v>8.4033613445378148E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>523</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="4"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="6"/>
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>524</v>
+      </c>
+      <c r="C32">
+        <v>33</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>34</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="3"/>
+        <v>74</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="4"/>
+        <v>0.44594594594594594</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="5"/>
+        <v>9.45945945945946E-2</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="6"/>
+        <v>0.45945945945945948</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>527</v>
+      </c>
+      <c r="C33">
+        <v>69</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>76</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="4"/>
+        <v>0.90789473684210531</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="5"/>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="6"/>
+        <v>6.5789473684210523E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>528</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="6"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>517</v>
+      </c>
+      <c r="C35">
+        <v>61</v>
+      </c>
+      <c r="D35">
+        <v>15</v>
+      </c>
+      <c r="E35">
+        <v>26</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="4"/>
+        <v>0.59803921568627449</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="5"/>
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="6"/>
+        <v>0.25490196078431371</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
+        <v>518</v>
+      </c>
+      <c r="C36">
+        <v>114</v>
+      </c>
+      <c r="D36">
+        <v>14</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="4"/>
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="5"/>
+        <v>0.10852713178294573</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="6"/>
+        <v>7.7519379844961239E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
+        <v>510</v>
+      </c>
+      <c r="C37">
+        <v>86</v>
+      </c>
+      <c r="D37">
+        <v>28</v>
+      </c>
+      <c r="E37">
+        <v>51</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="4"/>
+        <v>0.52121212121212124</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="5"/>
+        <v>0.16969696969696971</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="6"/>
+        <v>0.30909090909090908</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>519</v>
+      </c>
+      <c r="C38">
+        <v>87</v>
+      </c>
+      <c r="D38">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>11</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="4"/>
+        <v>0.73109243697478987</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="6"/>
+        <v>9.2436974789915971E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39">
+        <v>52</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+      <c r="E39">
+        <v>68</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="4"/>
+        <v>0.37142857142857144</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="5"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="6"/>
+        <v>0.48571428571428571</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>521</v>
+      </c>
+      <c r="C40">
+        <v>82</v>
+      </c>
+      <c r="D40">
+        <v>41</v>
+      </c>
+      <c r="E40">
+        <v>33</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>156</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="4"/>
+        <v>0.52564102564102566</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="5"/>
+        <v>0.26282051282051283</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="6"/>
+        <v>0.21153846153846154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>522</v>
+      </c>
+      <c r="C41">
+        <v>152</v>
+      </c>
+      <c r="D41">
+        <v>11</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+      <c r="G41" s="3">
+        <f t="shared" si="4"/>
+        <v>0.91566265060240959</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="5"/>
+        <v>6.6265060240963861E-2</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8072289156626505E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" t="s">
+        <v>523</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="4"/>
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="5"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="6"/>
+        <v>0.76470588235294112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
+        <v>524</v>
+      </c>
+      <c r="C43">
+        <v>53</v>
+      </c>
+      <c r="D43">
+        <v>14</v>
+      </c>
+      <c r="E43">
+        <v>47</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>114</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="4"/>
+        <v>0.46491228070175439</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12280701754385964</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="6"/>
+        <v>0.41228070175438597</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>527</v>
+      </c>
+      <c r="C44">
+        <v>106</v>
+      </c>
+      <c r="D44">
+        <v>7</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>116</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" si="4"/>
+        <v>0.91379310344827591</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="5"/>
+        <v>6.0344827586206899E-2</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="6"/>
+        <v>2.5862068965517241E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>528</v>
+      </c>
+      <c r="C45">
+        <v>43</v>
+      </c>
+      <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" si="4"/>
+        <v>0.70491803278688525</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="5"/>
+        <v>0.19672131147540983</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="6"/>
+        <v>9.8360655737704916E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" t="s">
+        <v>517</v>
+      </c>
+      <c r="C46">
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="4"/>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="5"/>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="6"/>
+        <v>0.39473684210526316</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" t="s">
+        <v>518</v>
+      </c>
+      <c r="C47">
+        <v>55</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+      <c r="G47" s="3">
+        <f t="shared" si="4"/>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="5"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="6"/>
+        <v>6.1538461538461542E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" t="s">
+        <v>510</v>
+      </c>
+      <c r="C48">
+        <v>31</v>
+      </c>
+      <c r="D48">
+        <v>15</v>
+      </c>
+      <c r="E48">
+        <v>20</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" si="4"/>
+        <v>0.46969696969696972</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="5"/>
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="6"/>
+        <v>0.30303030303030304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" t="s">
+        <v>519</v>
+      </c>
+      <c r="C49">
+        <v>51</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="4"/>
+        <v>0.82258064516129037</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="5"/>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="I49" s="3">
+        <f t="shared" si="6"/>
+        <v>4.8387096774193547E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" t="s">
+        <v>520</v>
+      </c>
+      <c r="C50">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50">
+        <v>38</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="4"/>
+        <v>0.27868852459016391</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="5"/>
+        <v>9.8360655737704916E-2</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="6"/>
+        <v>0.62295081967213117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>143</v>
+      </c>
+      <c r="B51" t="s">
+        <v>521</v>
+      </c>
+      <c r="C51">
+        <v>41</v>
+      </c>
+      <c r="D51">
+        <v>19</v>
+      </c>
+      <c r="E51">
+        <v>11</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="4"/>
+        <v>0.57746478873239437</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" si="5"/>
+        <v>0.26760563380281688</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="6"/>
+        <v>0.15492957746478872</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" t="s">
+        <v>522</v>
+      </c>
+      <c r="C52">
+        <v>66</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="4"/>
+        <v>0.92957746478873238</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" si="5"/>
+        <v>4.2253521126760563E-2</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="6"/>
+        <v>2.8169014084507043E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" t="s">
+        <v>523</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>12</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="6"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" t="s">
+        <v>524</v>
+      </c>
+      <c r="C54">
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>33</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>59</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="4"/>
+        <v>0.32203389830508472</v>
+      </c>
+      <c r="H54" s="3">
+        <f t="shared" si="5"/>
+        <v>0.11864406779661017</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="6"/>
+        <v>0.55932203389830504</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" t="s">
+        <v>527</v>
+      </c>
+      <c r="C55">
+        <v>57</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="4"/>
+        <v>0.95</v>
+      </c>
+      <c r="H55" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" t="s">
+        <v>528</v>
+      </c>
+      <c r="C56">
+        <v>9</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" t="s">
+        <v>517</v>
+      </c>
+      <c r="C57">
+        <v>38</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>21</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+      <c r="G57" s="3">
+        <f t="shared" si="4"/>
+        <v>0.58461538461538465</v>
+      </c>
+      <c r="H57" s="3">
+        <f t="shared" si="5"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="6"/>
+        <v>0.32307692307692309</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" t="s">
+        <v>518</v>
+      </c>
+      <c r="C58">
+        <v>89</v>
+      </c>
+      <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="G58" s="3">
+        <f t="shared" si="4"/>
+        <v>0.86407766990291257</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" si="5"/>
+        <v>7.7669902912621352E-2</v>
+      </c>
+      <c r="I58" s="3">
+        <f t="shared" si="6"/>
+        <v>5.8252427184466021E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" t="s">
+        <v>510</v>
+      </c>
+      <c r="C59">
+        <v>53</v>
+      </c>
+      <c r="D59">
+        <v>18</v>
+      </c>
+      <c r="E59">
+        <v>43</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="3"/>
+        <v>114</v>
+      </c>
+      <c r="G59" s="3">
+        <f t="shared" si="4"/>
+        <v>0.46491228070175439</v>
+      </c>
+      <c r="H59" s="3">
+        <f t="shared" si="5"/>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="I59" s="3">
+        <f t="shared" si="6"/>
+        <v>0.37719298245614036</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" t="s">
+        <v>519</v>
+      </c>
+      <c r="C60">
+        <v>70</v>
+      </c>
+      <c r="D60">
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="3"/>
+        <v>97</v>
+      </c>
+      <c r="G60" s="3">
+        <f t="shared" si="4"/>
+        <v>0.72164948453608246</v>
+      </c>
+      <c r="H60" s="3">
+        <f t="shared" si="5"/>
+        <v>0.19587628865979381</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="6"/>
+        <v>8.247422680412371E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" t="s">
+        <v>520</v>
+      </c>
+      <c r="C61">
+        <v>36</v>
+      </c>
+      <c r="D61">
+        <v>9</v>
+      </c>
+      <c r="E61">
+        <v>55</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="G61" s="3">
+        <f t="shared" si="4"/>
+        <v>0.36</v>
+      </c>
+      <c r="H61" s="3">
+        <f t="shared" si="5"/>
+        <v>0.09</v>
+      </c>
+      <c r="I61" s="3">
+        <f t="shared" si="6"/>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" t="s">
+        <v>521</v>
+      </c>
+      <c r="C62">
+        <v>60</v>
+      </c>
+      <c r="D62">
+        <v>41</v>
+      </c>
+      <c r="E62">
+        <v>28</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+      <c r="G62" s="3">
+        <f t="shared" si="4"/>
+        <v>0.46511627906976744</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" si="5"/>
+        <v>0.31782945736434109</v>
+      </c>
+      <c r="I62" s="3">
+        <f t="shared" si="6"/>
+        <v>0.21705426356589147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" t="s">
+        <v>522</v>
+      </c>
+      <c r="C63">
+        <v>126</v>
+      </c>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="3"/>
+        <v>137</v>
+      </c>
+      <c r="G63" s="3">
+        <f t="shared" si="4"/>
+        <v>0.91970802919708028</v>
+      </c>
+      <c r="H63" s="3">
+        <f t="shared" si="5"/>
+        <v>7.2992700729927001E-2</v>
+      </c>
+      <c r="I63" s="3">
+        <f t="shared" si="6"/>
+        <v>7.2992700729927005E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" t="s">
+        <v>523</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>25</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G64" s="3">
+        <f t="shared" si="4"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="H64" s="3">
+        <f t="shared" si="5"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="I64" s="3">
+        <f t="shared" si="6"/>
+        <v>0.80645161290322576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>163</v>
+      </c>
+      <c r="B65" t="s">
+        <v>524</v>
+      </c>
+      <c r="C65">
+        <v>36</v>
+      </c>
+      <c r="D65">
+        <v>17</v>
+      </c>
+      <c r="E65">
+        <v>45</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+      <c r="G65" s="3">
+        <f t="shared" si="4"/>
+        <v>0.36734693877551022</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17346938775510204</v>
+      </c>
+      <c r="I65" s="3">
+        <f t="shared" si="6"/>
+        <v>0.45918367346938777</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" t="s">
+        <v>527</v>
+      </c>
+      <c r="C66">
+        <v>90</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="G66" s="3">
+        <f t="shared" si="4"/>
+        <v>0.9</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" si="5"/>
+        <v>0.02</v>
+      </c>
+      <c r="I66" s="3">
+        <f t="shared" si="6"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" t="s">
+        <v>528</v>
+      </c>
+      <c r="C67">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <f t="shared" ref="F67:F130" si="7">SUM(C67:E67)</f>
+        <v>26</v>
+      </c>
+      <c r="G67" s="3">
+        <f t="shared" ref="G67:G130" si="8">C67/$F67</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="H67" s="3">
+        <f t="shared" ref="H67:H130" si="9">D67/$F67</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="I67" s="3">
+        <f t="shared" ref="I67:I130" si="10">E67/$F67</f>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>191</v>
+      </c>
+      <c r="B68" t="s">
+        <v>517</v>
+      </c>
+      <c r="C68">
+        <v>674</v>
+      </c>
+      <c r="D68">
+        <v>250</v>
+      </c>
+      <c r="E68">
+        <v>306</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="7"/>
+        <v>1230</v>
+      </c>
+      <c r="G68" s="3">
+        <f t="shared" si="8"/>
+        <v>0.54796747967479675</v>
+      </c>
+      <c r="H68" s="3">
+        <f t="shared" si="9"/>
+        <v>0.2032520325203252</v>
+      </c>
+      <c r="I68" s="3">
+        <f t="shared" si="10"/>
+        <v>0.24878048780487805</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" t="s">
+        <v>518</v>
+      </c>
+      <c r="C69">
+        <v>1298</v>
+      </c>
+      <c r="D69">
+        <v>128</v>
+      </c>
+      <c r="E69">
+        <v>56</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="7"/>
+        <v>1482</v>
+      </c>
+      <c r="G69" s="3">
+        <f t="shared" si="8"/>
+        <v>0.87584345479082326</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" si="9"/>
+        <v>8.6369770580296892E-2</v>
+      </c>
+      <c r="I69" s="3">
+        <f t="shared" si="10"/>
+        <v>3.7786774628879895E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" t="s">
+        <v>510</v>
+      </c>
+      <c r="C70">
+        <v>854</v>
+      </c>
+      <c r="D70">
+        <v>441</v>
+      </c>
+      <c r="E70">
+        <v>598</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="7"/>
+        <v>1893</v>
+      </c>
+      <c r="G70" s="3">
+        <f t="shared" si="8"/>
+        <v>0.45113576333861594</v>
+      </c>
+      <c r="H70" s="3">
+        <f t="shared" si="9"/>
+        <v>0.23296354992076071</v>
+      </c>
+      <c r="I70" s="3">
+        <f t="shared" si="10"/>
+        <v>0.31590068674062333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" t="s">
+        <v>519</v>
+      </c>
+      <c r="C71">
+        <v>977</v>
+      </c>
+      <c r="D71">
+        <v>233</v>
+      </c>
+      <c r="E71">
+        <v>112</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="7"/>
+        <v>1322</v>
+      </c>
+      <c r="G71" s="3">
+        <f t="shared" si="8"/>
+        <v>0.73903177004538578</v>
+      </c>
+      <c r="H71" s="3">
+        <f t="shared" si="9"/>
+        <v>0.1762481089258699</v>
+      </c>
+      <c r="I71" s="3">
+        <f t="shared" si="10"/>
+        <v>8.4720121028744322E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" t="s">
+        <v>520</v>
+      </c>
+      <c r="C72">
+        <v>555</v>
+      </c>
+      <c r="D72">
+        <v>177</v>
+      </c>
+      <c r="E72">
+        <v>735</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="7"/>
+        <v>1467</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" si="8"/>
+        <v>0.3783231083844581</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" si="9"/>
+        <v>0.12065439672801637</v>
+      </c>
+      <c r="I72" s="3">
+        <f t="shared" si="10"/>
+        <v>0.50102249488752559</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>191</v>
+      </c>
+      <c r="B73" t="s">
+        <v>521</v>
+      </c>
+      <c r="C73">
+        <v>860</v>
+      </c>
+      <c r="D73">
+        <v>455</v>
+      </c>
+      <c r="E73">
+        <v>248</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="7"/>
+        <v>1563</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="8"/>
+        <v>0.55022392834293021</v>
+      </c>
+      <c r="H73" s="3">
+        <f t="shared" si="9"/>
+        <v>0.29110684580934099</v>
+      </c>
+      <c r="I73" s="3">
+        <f t="shared" si="10"/>
+        <v>0.15866922584772872</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s">
+        <v>522</v>
+      </c>
+      <c r="C74">
+        <v>1679</v>
+      </c>
+      <c r="D74">
+        <v>100</v>
+      </c>
+      <c r="E74">
+        <v>49</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="7"/>
+        <v>1828</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="8"/>
+        <v>0.91849015317286653</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" si="9"/>
+        <v>5.4704595185995623E-2</v>
+      </c>
+      <c r="I74" s="3">
+        <f t="shared" si="10"/>
+        <v>2.6805251641137857E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>191</v>
+      </c>
+      <c r="B75" t="s">
+        <v>523</v>
+      </c>
+      <c r="C75">
+        <v>119</v>
+      </c>
+      <c r="D75">
+        <v>61</v>
+      </c>
+      <c r="E75">
+        <v>260</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="7"/>
+        <v>440</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="8"/>
+        <v>0.27045454545454545</v>
+      </c>
+      <c r="H75" s="3">
+        <f t="shared" si="9"/>
+        <v>0.13863636363636364</v>
+      </c>
+      <c r="I75" s="3">
+        <f t="shared" si="10"/>
+        <v>0.59090909090909094</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>191</v>
+      </c>
+      <c r="B76" t="s">
+        <v>524</v>
+      </c>
+      <c r="C76">
+        <v>626</v>
+      </c>
+      <c r="D76">
+        <v>149</v>
+      </c>
+      <c r="E76">
+        <v>591</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="7"/>
+        <v>1366</v>
+      </c>
+      <c r="G76" s="3">
+        <f t="shared" si="8"/>
+        <v>0.45827232796486089</v>
+      </c>
+      <c r="H76" s="3">
+        <f t="shared" si="9"/>
+        <v>0.10907759882869693</v>
+      </c>
+      <c r="I76" s="3">
+        <f t="shared" si="10"/>
+        <v>0.43265007320644217</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" t="s">
+        <v>527</v>
+      </c>
+      <c r="C77">
+        <v>1301</v>
+      </c>
+      <c r="D77">
+        <v>52</v>
+      </c>
+      <c r="E77">
+        <v>78</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="7"/>
+        <v>1431</v>
+      </c>
+      <c r="G77" s="3">
+        <f t="shared" si="8"/>
+        <v>0.90915443745632429</v>
+      </c>
+      <c r="H77" s="3">
+        <f t="shared" si="9"/>
+        <v>3.6338225017470298E-2</v>
+      </c>
+      <c r="I77" s="3">
+        <f t="shared" si="10"/>
+        <v>5.450733752620545E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" t="s">
+        <v>528</v>
+      </c>
+      <c r="C78">
+        <v>575</v>
+      </c>
+      <c r="D78">
+        <v>86</v>
+      </c>
+      <c r="E78">
+        <v>53</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="7"/>
+        <v>714</v>
+      </c>
+      <c r="G78" s="3">
+        <f t="shared" si="8"/>
+        <v>0.80532212885154064</v>
+      </c>
+      <c r="H78" s="3">
+        <f t="shared" si="9"/>
+        <v>0.12044817927170869</v>
+      </c>
+      <c r="I78" s="3">
+        <f t="shared" si="10"/>
+        <v>7.42296918767507E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>253</v>
+      </c>
+      <c r="B79" t="s">
+        <v>517</v>
+      </c>
+      <c r="C79">
+        <v>41</v>
+      </c>
+      <c r="D79">
+        <v>12</v>
+      </c>
+      <c r="E79">
+        <v>9</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="7"/>
+        <v>62</v>
+      </c>
+      <c r="G79" s="3">
+        <f t="shared" si="8"/>
+        <v>0.66129032258064513</v>
+      </c>
+      <c r="H79" s="3">
+        <f t="shared" si="9"/>
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="I79" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14516129032258066</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>253</v>
+      </c>
+      <c r="B80" t="s">
+        <v>518</v>
+      </c>
+      <c r="C80">
+        <v>115</v>
+      </c>
+      <c r="D80">
+        <v>9</v>
+      </c>
+      <c r="E80">
+        <v>7</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="7"/>
+        <v>131</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="8"/>
+        <v>0.87786259541984735</v>
+      </c>
+      <c r="H80" s="3">
+        <f t="shared" si="9"/>
+        <v>6.8702290076335881E-2</v>
+      </c>
+      <c r="I80" s="3">
+        <f t="shared" si="10"/>
+        <v>5.3435114503816793E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>253</v>
+      </c>
+      <c r="B81" t="s">
+        <v>510</v>
+      </c>
+      <c r="C81">
+        <v>79</v>
+      </c>
+      <c r="D81">
+        <v>32</v>
+      </c>
+      <c r="E81">
+        <v>33</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="7"/>
+        <v>144</v>
+      </c>
+      <c r="G81" s="3">
+        <f t="shared" si="8"/>
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="H81" s="3">
+        <f t="shared" si="9"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="I81" s="3">
+        <f t="shared" si="10"/>
+        <v>0.22916666666666666</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>253</v>
+      </c>
+      <c r="B82" t="s">
+        <v>519</v>
+      </c>
+      <c r="C82">
+        <v>86</v>
+      </c>
+      <c r="D82">
+        <v>28</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="7"/>
+        <v>116</v>
+      </c>
+      <c r="G82" s="3">
+        <f t="shared" si="8"/>
+        <v>0.74137931034482762</v>
+      </c>
+      <c r="H82" s="3">
+        <f t="shared" si="9"/>
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="I82" s="3">
+        <f t="shared" si="10"/>
+        <v>1.7241379310344827E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>253</v>
+      </c>
+      <c r="B83" t="s">
+        <v>520</v>
+      </c>
+      <c r="C83">
+        <v>43</v>
+      </c>
+      <c r="D83">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>69</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="7"/>
+        <v>124</v>
+      </c>
+      <c r="G83" s="3">
+        <f t="shared" si="8"/>
+        <v>0.34677419354838712</v>
+      </c>
+      <c r="H83" s="3">
+        <f t="shared" si="9"/>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="I83" s="3">
+        <f t="shared" si="10"/>
+        <v>0.55645161290322576</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>253</v>
+      </c>
+      <c r="B84" t="s">
+        <v>521</v>
+      </c>
+      <c r="C84">
+        <v>107</v>
+      </c>
+      <c r="D84">
+        <v>38</v>
+      </c>
+      <c r="E84">
+        <v>49</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="7"/>
+        <v>194</v>
+      </c>
+      <c r="G84" s="3">
+        <f t="shared" si="8"/>
+        <v>0.55154639175257736</v>
+      </c>
+      <c r="H84" s="3">
+        <f t="shared" si="9"/>
+        <v>0.19587628865979381</v>
+      </c>
+      <c r="I84" s="3">
+        <f t="shared" si="10"/>
+        <v>0.25257731958762886</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>253</v>
+      </c>
+      <c r="B85" t="s">
+        <v>522</v>
+      </c>
+      <c r="C85">
+        <v>189</v>
+      </c>
+      <c r="D85">
+        <v>13</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="7"/>
+        <v>205</v>
+      </c>
+      <c r="G85" s="3">
+        <f t="shared" si="8"/>
+        <v>0.92195121951219516</v>
+      </c>
+      <c r="H85" s="3">
+        <f t="shared" si="9"/>
+        <v>6.3414634146341464E-2</v>
+      </c>
+      <c r="I85" s="3">
+        <f t="shared" si="10"/>
+        <v>1.4634146341463415E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>523</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86">
+        <v>13</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="G86" s="3">
+        <f t="shared" si="8"/>
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="H86" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I86" s="3">
+        <f t="shared" si="10"/>
+        <v>0.61904761904761907</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>253</v>
+      </c>
+      <c r="B87" t="s">
+        <v>524</v>
+      </c>
+      <c r="C87">
+        <v>61</v>
+      </c>
+      <c r="D87">
+        <v>9</v>
+      </c>
+      <c r="E87">
+        <v>48</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="7"/>
+        <v>118</v>
+      </c>
+      <c r="G87" s="3">
+        <f t="shared" si="8"/>
+        <v>0.51694915254237284</v>
+      </c>
+      <c r="H87" s="3">
+        <f t="shared" si="9"/>
+        <v>7.6271186440677971E-2</v>
+      </c>
+      <c r="I87" s="3">
+        <f t="shared" si="10"/>
+        <v>0.40677966101694918</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>253</v>
+      </c>
+      <c r="B88" t="s">
+        <v>527</v>
+      </c>
+      <c r="C88">
+        <v>113</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="7"/>
+        <v>118</v>
+      </c>
+      <c r="G88" s="3">
+        <f t="shared" si="8"/>
+        <v>0.9576271186440678</v>
+      </c>
+      <c r="H88" s="3">
+        <f t="shared" si="9"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="I88" s="3">
+        <f t="shared" si="10"/>
+        <v>2.5423728813559324E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>253</v>
+      </c>
+      <c r="B89" t="s">
+        <v>528</v>
+      </c>
+      <c r="C89">
+        <v>48</v>
+      </c>
+      <c r="D89">
+        <v>5</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="7"/>
+        <v>56</v>
+      </c>
+      <c r="G89" s="3">
+        <f t="shared" si="8"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H89" s="3">
+        <f t="shared" si="9"/>
+        <v>8.9285714285714288E-2</v>
+      </c>
+      <c r="I89" s="3">
+        <f t="shared" si="10"/>
+        <v>5.3571428571428568E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>333</v>
+      </c>
+      <c r="B90" t="s">
+        <v>517</v>
+      </c>
+      <c r="C90">
+        <v>21</v>
+      </c>
+      <c r="D90">
+        <v>8</v>
+      </c>
+      <c r="E90">
+        <v>9</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="G90" s="3">
+        <f t="shared" si="8"/>
+        <v>0.55263157894736847</v>
+      </c>
+      <c r="H90" s="3">
+        <f t="shared" si="9"/>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="I90" s="3">
+        <f t="shared" si="10"/>
+        <v>0.23684210526315788</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>333</v>
+      </c>
+      <c r="B91" t="s">
+        <v>518</v>
+      </c>
+      <c r="C91">
+        <v>50</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="7"/>
+        <v>55</v>
+      </c>
+      <c r="G91" s="3">
+        <f t="shared" si="8"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="H91" s="3">
+        <f t="shared" si="9"/>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="I91" s="3">
+        <f t="shared" si="10"/>
+        <v>5.4545454545454543E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>333</v>
+      </c>
+      <c r="B92" t="s">
+        <v>510</v>
+      </c>
+      <c r="C92">
+        <v>11</v>
+      </c>
+      <c r="D92">
+        <v>8</v>
+      </c>
+      <c r="E92">
+        <v>38</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="7"/>
+        <v>57</v>
+      </c>
+      <c r="G92" s="3">
+        <f t="shared" si="8"/>
+        <v>0.19298245614035087</v>
+      </c>
+      <c r="H92" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14035087719298245</v>
+      </c>
+      <c r="I92" s="3">
+        <f t="shared" si="10"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>333</v>
+      </c>
+      <c r="B93" t="s">
+        <v>519</v>
+      </c>
+      <c r="C93">
+        <v>39</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="7"/>
+        <v>47</v>
+      </c>
+      <c r="G93" s="3">
+        <f t="shared" si="8"/>
+        <v>0.82978723404255317</v>
+      </c>
+      <c r="H93" s="3">
+        <f t="shared" si="9"/>
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="I93" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2553191489361701E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>333</v>
+      </c>
+      <c r="B94" t="s">
+        <v>520</v>
+      </c>
+      <c r="C94">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>42</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="7"/>
+        <v>52</v>
+      </c>
+      <c r="G94" s="3">
+        <f t="shared" si="8"/>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="H94" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <f t="shared" si="10"/>
+        <v>0.80769230769230771</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>333</v>
+      </c>
+      <c r="B95" t="s">
+        <v>521</v>
+      </c>
+      <c r="C95">
+        <v>34</v>
+      </c>
+      <c r="D95">
+        <v>29</v>
+      </c>
+      <c r="E95">
+        <v>17</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="7"/>
+        <v>80</v>
+      </c>
+      <c r="G95" s="3">
+        <f t="shared" si="8"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="H95" s="3">
+        <f t="shared" si="9"/>
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="I95" s="3">
+        <f t="shared" si="10"/>
+        <v>0.21249999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>333</v>
+      </c>
+      <c r="B96" t="s">
+        <v>522</v>
+      </c>
+      <c r="C96">
+        <v>76</v>
+      </c>
+      <c r="D96">
+        <v>5</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="7"/>
+        <v>82</v>
+      </c>
+      <c r="G96" s="3">
+        <f t="shared" si="8"/>
+        <v>0.92682926829268297</v>
+      </c>
+      <c r="H96" s="3">
+        <f t="shared" si="9"/>
+        <v>6.097560975609756E-2</v>
+      </c>
+      <c r="I96" s="3">
+        <f t="shared" si="10"/>
+        <v>1.2195121951219513E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>333</v>
+      </c>
+      <c r="B97" t="s">
+        <v>523</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G97" s="3">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="H97" s="3">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="I97" s="3">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>333</v>
+      </c>
+      <c r="B98" t="s">
+        <v>524</v>
+      </c>
+      <c r="C98">
+        <v>11</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>38</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="7"/>
+        <v>49</v>
+      </c>
+      <c r="G98" s="3">
+        <f t="shared" si="8"/>
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="H98" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="3">
+        <f t="shared" si="10"/>
+        <v>0.77551020408163263</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>333</v>
+      </c>
+      <c r="B99" t="s">
+        <v>527</v>
+      </c>
+      <c r="C99">
+        <v>45</v>
+      </c>
+      <c r="D99">
+        <v>7</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="7"/>
+        <v>52</v>
+      </c>
+      <c r="G99" s="3">
+        <f t="shared" si="8"/>
+        <v>0.86538461538461542</v>
+      </c>
+      <c r="H99" s="3">
+        <f t="shared" si="9"/>
+        <v>0.13461538461538461</v>
+      </c>
+      <c r="I99" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>333</v>
+      </c>
+      <c r="B100" t="s">
+        <v>528</v>
+      </c>
+      <c r="C100">
+        <v>7</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="G100" s="3">
+        <f t="shared" si="8"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H100" s="3">
+        <f t="shared" si="9"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="I100" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>371</v>
+      </c>
+      <c r="B101" t="s">
+        <v>517</v>
+      </c>
+      <c r="C101">
+        <v>68</v>
+      </c>
+      <c r="D101">
+        <v>36</v>
+      </c>
+      <c r="E101">
+        <v>25</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="7"/>
+        <v>129</v>
+      </c>
+      <c r="G101" s="3">
+        <f t="shared" si="8"/>
+        <v>0.52713178294573648</v>
+      </c>
+      <c r="H101" s="3">
+        <f t="shared" si="9"/>
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="I101" s="3">
+        <f t="shared" si="10"/>
+        <v>0.19379844961240311</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>371</v>
+      </c>
+      <c r="B102" t="s">
+        <v>518</v>
+      </c>
+      <c r="C102">
+        <v>145</v>
+      </c>
+      <c r="D102">
+        <v>4</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="7"/>
+        <v>149</v>
+      </c>
+      <c r="G102" s="3">
+        <f t="shared" si="8"/>
+        <v>0.97315436241610742</v>
+      </c>
+      <c r="H102" s="3">
+        <f t="shared" si="9"/>
+        <v>2.6845637583892617E-2</v>
+      </c>
+      <c r="I102" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>371</v>
+      </c>
+      <c r="B103" t="s">
+        <v>510</v>
+      </c>
+      <c r="C103">
+        <v>48</v>
+      </c>
+      <c r="D103">
+        <v>18</v>
+      </c>
+      <c r="E103">
+        <v>87</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="7"/>
+        <v>153</v>
+      </c>
+      <c r="G103" s="3">
+        <f t="shared" si="8"/>
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="H103" s="3">
+        <f t="shared" si="9"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="I103" s="3">
+        <f t="shared" si="10"/>
+        <v>0.56862745098039214</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>371</v>
+      </c>
+      <c r="B104" t="s">
+        <v>519</v>
+      </c>
+      <c r="C104">
+        <v>81</v>
+      </c>
+      <c r="D104">
+        <v>33</v>
+      </c>
+      <c r="E104">
+        <v>21</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="7"/>
+        <v>135</v>
+      </c>
+      <c r="G104" s="3">
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
-      <c r="H2" s="3">
-        <f t="shared" ref="H2:I2" si="1">D2/$F2</f>
-        <v>0.3</v>
-      </c>
-      <c r="I2" s="3">
-        <f t="shared" si="1"/>
+      <c r="H104" s="3">
+        <f t="shared" si="9"/>
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="I104" s="3">
+        <f t="shared" si="10"/>
+        <v>0.15555555555555556</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>371</v>
+      </c>
+      <c r="B105" t="s">
+        <v>520</v>
+      </c>
+      <c r="C105">
+        <v>30</v>
+      </c>
+      <c r="D105">
+        <v>16</v>
+      </c>
+      <c r="E105">
+        <v>96</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="7"/>
+        <v>142</v>
+      </c>
+      <c r="G105" s="3">
+        <f t="shared" si="8"/>
+        <v>0.21126760563380281</v>
+      </c>
+      <c r="H105" s="3">
+        <f t="shared" si="9"/>
+        <v>0.11267605633802817</v>
+      </c>
+      <c r="I105" s="3">
+        <f t="shared" si="10"/>
+        <v>0.676056338028169</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>371</v>
+      </c>
+      <c r="B106" t="s">
+        <v>521</v>
+      </c>
+      <c r="C106">
+        <v>78</v>
+      </c>
+      <c r="D106">
+        <v>57</v>
+      </c>
+      <c r="E106">
+        <v>14</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="7"/>
+        <v>149</v>
+      </c>
+      <c r="G106" s="3">
+        <f t="shared" si="8"/>
+        <v>0.52348993288590606</v>
+      </c>
+      <c r="H106" s="3">
+        <f t="shared" si="9"/>
+        <v>0.3825503355704698</v>
+      </c>
+      <c r="I106" s="3">
+        <f t="shared" si="10"/>
+        <v>9.3959731543624164E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>371</v>
+      </c>
+      <c r="B107" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107">
+        <v>151</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="7"/>
+        <v>152</v>
+      </c>
+      <c r="G107" s="3">
+        <f t="shared" si="8"/>
+        <v>0.99342105263157898</v>
+      </c>
+      <c r="H107" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="3">
+        <f t="shared" si="10"/>
+        <v>6.5789473684210523E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>371</v>
+      </c>
+      <c r="B108" t="s">
+        <v>523</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>7</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="G108" s="3">
+        <f t="shared" si="8"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H108" s="3">
+        <f t="shared" si="9"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="I108" s="3">
+        <f t="shared" si="10"/>
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>371</v>
+      </c>
+      <c r="B109" t="s">
+        <v>524</v>
+      </c>
+      <c r="C109">
+        <v>54</v>
+      </c>
+      <c r="D109">
+        <v>6</v>
+      </c>
+      <c r="E109">
+        <v>77</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="7"/>
+        <v>137</v>
+      </c>
+      <c r="G109" s="3">
+        <f t="shared" si="8"/>
+        <v>0.39416058394160586</v>
+      </c>
+      <c r="H109" s="3">
+        <f t="shared" si="9"/>
+        <v>4.3795620437956206E-2</v>
+      </c>
+      <c r="I109" s="3">
+        <f t="shared" si="10"/>
+        <v>0.56204379562043794</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>371</v>
+      </c>
+      <c r="B110" t="s">
+        <v>527</v>
+      </c>
+      <c r="C110">
+        <v>139</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="7"/>
+        <v>142</v>
+      </c>
+      <c r="G110" s="3">
+        <f t="shared" si="8"/>
+        <v>0.97887323943661975</v>
+      </c>
+      <c r="H110" s="3">
+        <f t="shared" si="9"/>
+        <v>7.0422535211267607E-3</v>
+      </c>
+      <c r="I110" s="3">
+        <f t="shared" si="10"/>
+        <v>1.4084507042253521E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>371</v>
+      </c>
+      <c r="B111" t="s">
+        <v>528</v>
+      </c>
+      <c r="C111">
+        <v>13</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="G111" s="3">
+        <f t="shared" si="8"/>
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="H111" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="I111" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>402</v>
+      </c>
+      <c r="B112" t="s">
+        <v>517</v>
+      </c>
+      <c r="C112">
+        <v>20</v>
+      </c>
+      <c r="D112">
+        <v>4</v>
+      </c>
+      <c r="E112">
+        <v>4</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="G112" s="3">
+        <f t="shared" si="8"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H112" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I112" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>402</v>
+      </c>
+      <c r="B113" t="s">
+        <v>518</v>
+      </c>
+      <c r="C113">
+        <v>39</v>
+      </c>
+      <c r="D113">
+        <v>3</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="G113" s="3">
+        <f t="shared" si="8"/>
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="H113" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="I113" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>402</v>
+      </c>
+      <c r="B114" t="s">
+        <v>510</v>
+      </c>
+      <c r="C114">
+        <v>16</v>
+      </c>
+      <c r="D114">
+        <v>15</v>
+      </c>
+      <c r="E114">
+        <v>15</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="G114" s="3">
+        <f t="shared" si="8"/>
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="H114" s="3">
+        <f t="shared" si="9"/>
+        <v>0.32608695652173914</v>
+      </c>
+      <c r="I114" s="3">
+        <f t="shared" si="10"/>
+        <v>0.32608695652173914</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>402</v>
+      </c>
+      <c r="B115" t="s">
+        <v>519</v>
+      </c>
+      <c r="C115">
+        <v>30</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115">
+        <v>4</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="G115" s="3">
+        <f t="shared" si="8"/>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="H115" s="3">
+        <f t="shared" si="9"/>
+        <v>0.12820512820512819</v>
+      </c>
+      <c r="I115" s="3">
+        <f t="shared" si="10"/>
+        <v>0.10256410256410256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>402</v>
+      </c>
+      <c r="B116" t="s">
+        <v>520</v>
+      </c>
+      <c r="C116">
+        <v>18</v>
+      </c>
+      <c r="D116">
+        <v>5</v>
+      </c>
+      <c r="E116">
+        <v>20</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="7"/>
+        <v>43</v>
+      </c>
+      <c r="G116" s="3">
+        <f t="shared" si="8"/>
+        <v>0.41860465116279072</v>
+      </c>
+      <c r="H116" s="3">
+        <f t="shared" si="9"/>
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="I116" s="3">
+        <f t="shared" si="10"/>
+        <v>0.46511627906976744</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>402</v>
+      </c>
+      <c r="B117" t="s">
+        <v>521</v>
+      </c>
+      <c r="C117">
+        <v>37</v>
+      </c>
+      <c r="D117">
+        <v>6</v>
+      </c>
+      <c r="E117">
+        <v>3</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="G117" s="3">
+        <f t="shared" si="8"/>
+        <v>0.80434782608695654</v>
+      </c>
+      <c r="H117" s="3">
+        <f t="shared" si="9"/>
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="I117" s="3">
+        <f t="shared" si="10"/>
+        <v>6.5217391304347824E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>402</v>
+      </c>
+      <c r="B118" t="s">
+        <v>522</v>
+      </c>
+      <c r="C118">
+        <v>44</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="G118" s="3">
+        <f t="shared" si="8"/>
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="H118" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I118" s="3">
+        <f t="shared" si="10"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>402</v>
+      </c>
+      <c r="B119" t="s">
+        <v>523</v>
+      </c>
+      <c r="C119">
+        <v>3</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>6</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="G119" s="3">
+        <f t="shared" si="8"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H119" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I119" s="3">
+        <f t="shared" si="10"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>402</v>
+      </c>
+      <c r="B120" t="s">
+        <v>524</v>
+      </c>
+      <c r="C120">
+        <v>22</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120">
+        <v>18</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="G120" s="3">
+        <f t="shared" si="8"/>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="H120" s="3">
+        <f t="shared" si="9"/>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="I120" s="3">
+        <f t="shared" si="10"/>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>402</v>
+      </c>
+      <c r="B121" t="s">
+        <v>527</v>
+      </c>
+      <c r="C121">
+        <v>38</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <f t="shared" si="7"/>
+        <v>41</v>
+      </c>
+      <c r="G121" s="3">
+        <f t="shared" si="8"/>
+        <v>0.92682926829268297</v>
+      </c>
+      <c r="H121" s="3">
+        <f t="shared" si="9"/>
+        <v>4.878048780487805E-2</v>
+      </c>
+      <c r="I121" s="3">
+        <f t="shared" si="10"/>
+        <v>2.4390243902439025E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>402</v>
+      </c>
+      <c r="B122" t="s">
+        <v>528</v>
+      </c>
+      <c r="C122">
+        <v>11</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="G122" s="3">
+        <f t="shared" si="8"/>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H122" s="3">
+        <f t="shared" si="9"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="I122" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>420</v>
+      </c>
+      <c r="B123" t="s">
+        <v>517</v>
+      </c>
+      <c r="C123">
+        <v>75</v>
+      </c>
+      <c r="D123">
+        <v>27</v>
+      </c>
+      <c r="E123">
+        <v>26</v>
+      </c>
+      <c r="F123">
+        <f t="shared" si="7"/>
+        <v>128</v>
+      </c>
+      <c r="G123" s="3">
+        <f t="shared" si="8"/>
+        <v>0.5859375</v>
+      </c>
+      <c r="H123" s="3">
+        <f t="shared" si="9"/>
+        <v>0.2109375</v>
+      </c>
+      <c r="I123" s="3">
+        <f t="shared" si="10"/>
+        <v>0.203125</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>420</v>
+      </c>
+      <c r="B124" t="s">
+        <v>518</v>
+      </c>
+      <c r="C124">
+        <v>210</v>
+      </c>
+      <c r="D124">
+        <v>23</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124">
+        <f t="shared" si="7"/>
+        <v>234</v>
+      </c>
+      <c r="G124" s="3">
+        <f t="shared" si="8"/>
+        <v>0.89743589743589747</v>
+      </c>
+      <c r="H124" s="3">
+        <f t="shared" si="9"/>
+        <v>9.8290598290598288E-2</v>
+      </c>
+      <c r="I124" s="3">
+        <f t="shared" si="10"/>
+        <v>4.2735042735042739E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>420</v>
+      </c>
+      <c r="B125" t="s">
+        <v>510</v>
+      </c>
+      <c r="C125">
+        <v>125</v>
+      </c>
+      <c r="D125">
+        <v>58</v>
+      </c>
+      <c r="E125">
+        <v>70</v>
+      </c>
+      <c r="F125">
+        <f t="shared" si="7"/>
+        <v>253</v>
+      </c>
+      <c r="G125" s="3">
+        <f t="shared" si="8"/>
+        <v>0.49407114624505927</v>
+      </c>
+      <c r="H125" s="3">
+        <f t="shared" si="9"/>
+        <v>0.22924901185770752</v>
+      </c>
+      <c r="I125" s="3">
+        <f t="shared" si="10"/>
+        <v>0.27667984189723321</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>420</v>
+      </c>
+      <c r="B126" t="s">
+        <v>519</v>
+      </c>
+      <c r="C126">
+        <v>170</v>
+      </c>
+      <c r="D126">
+        <v>34</v>
+      </c>
+      <c r="E126">
+        <v>13</v>
+      </c>
+      <c r="F126">
+        <f t="shared" si="7"/>
+        <v>217</v>
+      </c>
+      <c r="G126" s="3">
+        <f t="shared" si="8"/>
+        <v>0.78341013824884798</v>
+      </c>
+      <c r="H126" s="3">
+        <f t="shared" si="9"/>
+        <v>0.15668202764976957</v>
+      </c>
+      <c r="I126" s="3">
+        <f t="shared" si="10"/>
+        <v>5.9907834101382486E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>420</v>
+      </c>
+      <c r="B127" t="s">
+        <v>520</v>
+      </c>
+      <c r="C127">
+        <v>89</v>
+      </c>
+      <c r="D127">
+        <v>33</v>
+      </c>
+      <c r="E127">
+        <v>110</v>
+      </c>
+      <c r="F127">
+        <f t="shared" si="7"/>
+        <v>232</v>
+      </c>
+      <c r="G127" s="3">
+        <f t="shared" si="8"/>
+        <v>0.38362068965517243</v>
+      </c>
+      <c r="H127" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14224137931034483</v>
+      </c>
+      <c r="I127" s="3">
+        <f t="shared" si="10"/>
+        <v>0.47413793103448276</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>420</v>
+      </c>
+      <c r="B128" t="s">
+        <v>521</v>
+      </c>
+      <c r="C128">
+        <v>139</v>
+      </c>
+      <c r="D128">
+        <v>85</v>
+      </c>
+      <c r="E128">
+        <v>66</v>
+      </c>
+      <c r="F128">
+        <f t="shared" si="7"/>
+        <v>290</v>
+      </c>
+      <c r="G128" s="3">
+        <f t="shared" si="8"/>
+        <v>0.47931034482758622</v>
+      </c>
+      <c r="H128" s="3">
+        <f t="shared" si="9"/>
+        <v>0.29310344827586204</v>
+      </c>
+      <c r="I128" s="3">
+        <f t="shared" si="10"/>
+        <v>0.22758620689655173</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>420</v>
+      </c>
+      <c r="B129" t="s">
+        <v>522</v>
+      </c>
+      <c r="C129">
+        <v>263</v>
+      </c>
+      <c r="D129">
+        <v>25</v>
+      </c>
+      <c r="E129">
+        <v>10</v>
+      </c>
+      <c r="F129">
+        <f t="shared" si="7"/>
+        <v>298</v>
+      </c>
+      <c r="G129" s="3">
+        <f t="shared" si="8"/>
+        <v>0.8825503355704698</v>
+      </c>
+      <c r="H129" s="3">
+        <f t="shared" si="9"/>
+        <v>8.3892617449664433E-2</v>
+      </c>
+      <c r="I129" s="3">
+        <f t="shared" si="10"/>
+        <v>3.3557046979865772E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>420</v>
+      </c>
+      <c r="B130" t="s">
+        <v>523</v>
+      </c>
+      <c r="C130">
+        <v>36</v>
+      </c>
+      <c r="D130">
+        <v>23</v>
+      </c>
+      <c r="E130">
+        <v>20</v>
+      </c>
+      <c r="F130">
+        <f t="shared" si="7"/>
+        <v>79</v>
+      </c>
+      <c r="G130" s="3">
+        <f t="shared" si="8"/>
+        <v>0.45569620253164556</v>
+      </c>
+      <c r="H130" s="3">
+        <f t="shared" si="9"/>
+        <v>0.29113924050632911</v>
+      </c>
+      <c r="I130" s="3">
+        <f t="shared" si="10"/>
+        <v>0.25316455696202533</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>420</v>
+      </c>
+      <c r="B131" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131">
+        <v>104</v>
+      </c>
+      <c r="D131">
+        <v>35</v>
+      </c>
+      <c r="E131">
+        <v>74</v>
+      </c>
+      <c r="F131">
+        <f t="shared" ref="F131:F144" si="11">SUM(C131:E131)</f>
+        <v>213</v>
+      </c>
+      <c r="G131" s="3">
+        <f t="shared" ref="G131:G144" si="12">C131/$F131</f>
+        <v>0.48826291079812206</v>
+      </c>
+      <c r="H131" s="3">
+        <f t="shared" ref="H131:H144" si="13">D131/$F131</f>
+        <v>0.16431924882629109</v>
+      </c>
+      <c r="I131" s="3">
+        <f t="shared" ref="I131:I144" si="14">E131/$F131</f>
+        <v>0.34741784037558687</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>420</v>
+      </c>
+      <c r="B132" t="s">
+        <v>527</v>
+      </c>
+      <c r="C132">
+        <v>203</v>
+      </c>
+      <c r="D132">
+        <v>5</v>
+      </c>
+      <c r="E132">
+        <v>8</v>
+      </c>
+      <c r="F132">
+        <f t="shared" si="11"/>
+        <v>216</v>
+      </c>
+      <c r="G132" s="3">
+        <f t="shared" si="12"/>
+        <v>0.93981481481481477</v>
+      </c>
+      <c r="H132" s="3">
+        <f t="shared" si="13"/>
+        <v>2.3148148148148147E-2</v>
+      </c>
+      <c r="I132" s="3">
+        <f t="shared" si="14"/>
+        <v>3.7037037037037035E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>420</v>
+      </c>
+      <c r="B133" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133">
+        <v>86</v>
+      </c>
+      <c r="D133">
+        <v>22</v>
+      </c>
+      <c r="E133">
+        <v>17</v>
+      </c>
+      <c r="F133">
+        <f t="shared" si="11"/>
+        <v>125</v>
+      </c>
+      <c r="G133" s="3">
+        <f t="shared" si="12"/>
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="H133" s="3">
+        <f t="shared" si="13"/>
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="I133" s="3">
+        <f t="shared" si="14"/>
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>491</v>
+      </c>
+      <c r="B134" t="s">
+        <v>517</v>
+      </c>
+      <c r="C134">
+        <v>10</v>
+      </c>
+      <c r="D134">
+        <v>7</v>
+      </c>
+      <c r="E134">
+        <v>5</v>
+      </c>
+      <c r="F134">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="G134" s="3">
+        <f t="shared" si="12"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="H134" s="3">
+        <f t="shared" si="13"/>
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="I134" s="3">
+        <f t="shared" si="14"/>
+        <v>0.22727272727272727</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>491</v>
+      </c>
+      <c r="B135" t="s">
+        <v>518</v>
+      </c>
+      <c r="C135">
+        <v>26</v>
+      </c>
+      <c r="D135">
+        <v>4</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="G135" s="3">
+        <f t="shared" si="12"/>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H135" s="3">
+        <f t="shared" si="13"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="I135" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>491</v>
+      </c>
+      <c r="B136" t="s">
+        <v>510</v>
+      </c>
+      <c r="C136">
+        <v>11</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="E136">
+        <v>18</v>
+      </c>
+      <c r="F136">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="G136" s="3">
+        <f t="shared" si="12"/>
+        <v>0.34375</v>
+      </c>
+      <c r="H136" s="3">
+        <f t="shared" si="13"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="I136" s="3">
+        <f t="shared" si="14"/>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>491</v>
+      </c>
+      <c r="B137" t="s">
+        <v>519</v>
+      </c>
+      <c r="C137">
+        <v>13</v>
+      </c>
+      <c r="D137">
+        <v>10</v>
+      </c>
+      <c r="E137">
+        <v>5</v>
+      </c>
+      <c r="F137">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="G137" s="3">
+        <f t="shared" si="12"/>
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="H137" s="3">
+        <f t="shared" si="13"/>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="I137" s="3">
+        <f t="shared" si="14"/>
+        <v>0.17857142857142858</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>491</v>
+      </c>
+      <c r="B138" t="s">
+        <v>520</v>
+      </c>
+      <c r="C138">
+        <v>8</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138">
+        <v>20</v>
+      </c>
+      <c r="F138">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="G138" s="3">
+        <f t="shared" si="12"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="H138" s="3">
+        <f t="shared" si="13"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I138" s="3">
+        <f t="shared" si="14"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>491</v>
+      </c>
+      <c r="B139" t="s">
+        <v>521</v>
+      </c>
+      <c r="C139">
+        <v>19</v>
+      </c>
+      <c r="D139">
+        <v>14</v>
+      </c>
+      <c r="E139">
+        <v>4</v>
+      </c>
+      <c r="F139">
+        <f t="shared" si="11"/>
+        <v>37</v>
+      </c>
+      <c r="G139" s="3">
+        <f t="shared" si="12"/>
+        <v>0.51351351351351349</v>
+      </c>
+      <c r="H139" s="3">
+        <f t="shared" si="13"/>
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="I139" s="3">
+        <f t="shared" si="14"/>
+        <v>0.10810810810810811</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>491</v>
+      </c>
+      <c r="B140" t="s">
+        <v>522</v>
+      </c>
+      <c r="C140">
+        <v>36</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="F140">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="G140" s="3">
+        <f t="shared" si="12"/>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="H140" s="3">
+        <f t="shared" si="13"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="I140" s="3">
+        <f t="shared" si="14"/>
+        <v>2.564102564102564E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>491</v>
+      </c>
+      <c r="B141" t="s">
+        <v>523</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="G141" s="3">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="H141" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I141" s="3">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>491</v>
+      </c>
+      <c r="B142" t="s">
+        <v>524</v>
+      </c>
+      <c r="C142">
+        <v>9</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>17</v>
+      </c>
+      <c r="F142">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="G142" s="3">
+        <f t="shared" si="12"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H142" s="3">
+        <f t="shared" si="13"/>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="I142" s="3">
+        <f t="shared" si="14"/>
+        <v>0.62962962962962965</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>491</v>
+      </c>
+      <c r="B143" t="s">
+        <v>527</v>
+      </c>
+      <c r="C143">
+        <v>23</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="G143" s="3">
+        <f t="shared" si="12"/>
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="H143" s="3">
+        <f t="shared" si="13"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="I143" s="3">
+        <f t="shared" si="14"/>
+        <v>3.8461538461538464E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>491</v>
+      </c>
+      <c r="B144" t="s">
+        <v>528</v>
+      </c>
+      <c r="C144">
+        <v>8</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="G144" s="3">
+        <f t="shared" si="12"/>
+        <v>0.8</v>
+      </c>
+      <c r="H144" s="3">
+        <f t="shared" si="13"/>
         <v>0.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C3">
-        <v>555</v>
-      </c>
-      <c r="D3">
-        <v>222</v>
-      </c>
-      <c r="E3">
-        <v>55</v>
-      </c>
-      <c r="F3">
-        <f>SUM(C3:E3)</f>
-        <v>832</v>
-      </c>
-      <c r="G3" s="3">
-        <f>C3/$F3</f>
-        <v>0.66706730769230771</v>
-      </c>
-      <c r="H3" s="3">
-        <f t="shared" ref="H3" si="2">D3/$F3</f>
-        <v>0.26682692307692307</v>
-      </c>
-      <c r="I3" s="3">
-        <f t="shared" ref="I3" si="3">E3/$F3</f>
-        <v>6.6105769230769232E-2</v>
+      <c r="I144" s="3">
+        <f t="shared" si="14"/>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/reportOKSanaliza.xlsx
+++ b/reportOKSanaliza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojan\Documents\GitHub\ReportOKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A274C62-E0A4-4B79-A1B2-8B961B2310DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C027AC-76C3-4026-948E-1BA8239ED2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId6"/>
-    <pivotCache cacheId="10" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56,8 +56,16 @@
 Comment:
     --statistike meritve (centili, cone) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
 --BL, 2026-04-01
---centili Slovenija
-SELECT 'Slovenija' as Regija,
+-- definicija baterij kot table variable
+DECLARE @Baterije TABLE (ID INT);
+INSERT INTO @Baterije (ID)
+VALUES (18), (19), (20), (21), (25), (26);
+-- =========================
+-- CENTILI
+-- =========================
+-- centili Slovenija
+SELECT 
+    'Slovenija' as Regija,
     t.Ime AS Test,
     AVG(r.CentilniRang1) AS CentilXA,
     COUNT(r.CentilniRang1) AS N
@@ -69,15 +77,15 @@
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
 JOIN Meritev me
-    ON me.ID = m.IdMeritev         -- &lt;--- dodano
+    ON me.ID = m.IdMeritev
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)   -- &lt;--- dodan pogoj
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
 GROUP BY 
     t.Ime
---ORDER BY     t.Ime
 UNION ALL
 -- centili regije
 SELECT
@@ -93,7 +101,7 @@
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
 JOIN Meritev me
-    ON me.ID = m.IdMeritev     -- &lt;--- dodan povezovalni JOIN
+    ON me.ID = m.IdMeritev
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 JOIN Uporabnik u
@@ -104,14 +112,71 @@
     ON rgn.ID = pc.RegionID
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND tv.IdBaterija IN (18, 19, 20, 21, 25, 26)    -- testi iz teh baterij
-  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26) -- meritve morajo biti v teh baterijah
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
 GROUP BY 
     rgn.Name,
     t.Ime
 ORDER BY 
-    Regija ASC,
-    t.Ime ASC;</t>
+    Regija,
+    Test;
+-- =========================
+-- CONE
+-- =========================
+-- cone Slovenija
+SELECT 
+    'Slovenija' as Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+  AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
+GROUP BY
+    te.Ime
+UNION ALL
+-- cone regije
+SELECT
+    rgn.Name AS Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = c.ID
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+  AND du.IdVloga = 10
+  AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
+GROUP BY
+    rgn.Name,
+    te.Ime
+ORDER BY
+    Regija,
+    TestIme;</t>
       </text>
     </comment>
   </commentList>
@@ -129,11 +194,80 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    SELECT 'Slovenija' as Regija,
+    -- definicija baterij kot table variable
+DECLARE @Baterije TABLE (ID INT);
+INSERT INTO @Baterije (ID)
+VALUES (18), (19), (20), (21), (25), (26);
+-- =========================
+-- CENTILI
+-- =========================
+-- centili Slovenija
+SELECT 
+    'Slovenija' as Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+GROUP BY 
+    t.Ime
+UNION ALL
+-- centili regije
+SELECT
+    rgn.Name AS Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+GROUP BY 
+    rgn.Name,
+    t.Ime
+ORDER BY 
+    Regija,
+    Test;
+-- =========================
+-- CONE
+-- =========================
+-- cone Slovenija
+SELECT 
+    'Slovenija' as Regija,
     te.Ime AS TestIme,
-    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
-    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
-    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
 FROM Rezultat r
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
@@ -143,18 +277,18 @@
     ON c.ID = m.IdClan
 JOIN Test te
     ON te.ID = r.IdTest
-WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
   AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
 GROUP BY
     te.Ime
---ORDER BY     te.Ime
 UNION ALL
+-- cone regije
 SELECT
     rgn.Name AS Regija,
     te.Ime AS TestIme,
-    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
-    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
-    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
 FROM Rezultat r
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
@@ -172,15 +306,15 @@
     ON rgn.ID = pc.RegionID
 JOIN Test te
     ON te.ID = r.IdTest
-WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
   AND du.IdVloga = 10
   AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
 GROUP BY
     rgn.Name,
     te.Ime
 ORDER BY
-    Regija ASC,
-    te.Ime ASC;</t>
+    Regija,
+    TestIme;</t>
       </text>
     </comment>
   </commentList>
@@ -1838,7 +1972,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1863,12 +1997,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1920,7 +2048,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1931,7 +2059,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1939,16 +2066,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{BDBFD1E4-62EC-41BE-B39B-390F134CCF6B}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
@@ -4476,8 +4594,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7361,7 +7479,7 @@
     <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -7387,7 +7505,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -7450,7 +7568,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED1F8AC9-8CC5-4E08-995C-C481136EF10E}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED1F8AC9-8CC5-4E08-995C-C481136EF10E}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="K4:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -7561,7 +7679,7 @@
     <dataField name="Average of Mejno%" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
@@ -7933,8 +8051,16 @@
   <threadedComment ref="A1" dT="2026-04-03T04:11:08.84" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{F4841313-2AC6-4AB8-9D8D-A918BDBEDA73}">
     <text>--statistike meritve (centili, cone) ločeno po testu za udeležence OKS projekta Zmigaj_se_do_vadbe (ZV) - regije in SLO
 --BL, 2026-04-01
---centili Slovenija
-SELECT 'Slovenija' as Regija,
+-- definicija baterij kot table variable
+DECLARE @Baterije TABLE (ID INT);
+INSERT INTO @Baterije (ID)
+VALUES (18), (19), (20), (21), (25), (26);
+-- =========================
+-- CENTILI
+-- =========================
+-- centili Slovenija
+SELECT 
+    'Slovenija' as Regija,
     t.Ime AS Test,
     AVG(r.CentilniRang1) AS CentilXA,
     COUNT(r.CentilniRang1) AS N
@@ -7946,15 +8072,15 @@
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
 JOIN Meritev me
-    ON me.ID = m.IdMeritev         -- &lt;--- dodano
+    ON me.ID = m.IdMeritev
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)   -- &lt;--- dodan pogoj
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
 GROUP BY 
     t.Ime
---ORDER BY     t.Ime
 UNION ALL
 -- centili regije
 SELECT
@@ -7970,7 +8096,7 @@
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
 JOIN Meritev me
-    ON me.ID = m.IdMeritev     -- &lt;--- dodan povezovalni JOIN
+    ON me.ID = m.IdMeritev
 JOIN DostopUporabnikaDoClana du
     ON du.IdClan = m.IdClan
 JOIN Uporabnik u
@@ -7981,26 +8107,24 @@
     ON rgn.ID = pc.RegionID
 WHERE du.IdVloga = 10
   AND r.CentilniRang1 IS NOT NULL
-  AND tv.IdBaterija IN (18, 19, 20, 21, 25, 26)    -- testi iz teh baterij
-  AND me.BaterijaTestov IN (18, 19, 20, 21, 25, 26) -- meritve morajo biti v teh baterijah
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
 GROUP BY 
     rgn.Name,
     t.Ime
 ORDER BY 
-    Regija ASC,
-    t.Ime ASC;</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A1" dT="2026-04-03T05:49:55.82" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{BFFC901B-821E-4A6C-8204-68AA98345E97}">
-    <text>SELECT 'Slovenija' as Regija,
+    Regija,
+    Test;
+-- =========================
+-- CONE
+-- =========================
+-- cone Slovenija
+SELECT 
+    'Slovenija' as Regija,
     te.Ime AS TestIme,
-    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
-    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
-    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
 FROM Rezultat r
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
@@ -8010,18 +8134,18 @@
     ON c.ID = m.IdClan
 JOIN Test te
     ON te.ID = r.IdTest
-WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
   AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
 GROUP BY
     te.Ime
---ORDER BY     te.Ime
 UNION ALL
+-- cone regije
 SELECT
     rgn.Name AS Regija,
     te.Ime AS TestIme,
-    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,   -- zelena
-    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,    -- rumena
-    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano   -- rdeča
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
 FROM Rezultat r
 JOIN Merjenec m 
     ON m.ID = r.IdMerjenec
@@ -8039,15 +8163,143 @@
     ON rgn.ID = pc.RegionID
 JOIN Test te
     ON te.ID = r.IdTest
-WHERE me.BaterijaTestov IN (18, 19, 20, 21, 25, 26)
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
   AND du.IdVloga = 10
   AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
 GROUP BY
     rgn.Name,
     te.Ime
 ORDER BY
-    Regija ASC,
-    te.Ime ASC;</text>
+    Regija,
+    TestIme;</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-04-03T05:49:55.82" personId="{B0A86080-3FF1-41DA-B9EB-1C8139C00CC1}" id="{BFFC901B-821E-4A6C-8204-68AA98345E97}">
+    <text>-- definicija baterij kot table variable
+DECLARE @Baterije TABLE (ID INT);
+INSERT INTO @Baterije (ID)
+VALUES (18), (19), (20), (21), (25), (26);
+-- =========================
+-- CENTILI
+-- =========================
+-- centili Slovenija
+SELECT 
+    'Slovenija' as Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+GROUP BY 
+    t.Ime
+UNION ALL
+-- centili regije
+SELECT
+    rgn.Name AS Regija,
+    t.Ime AS Test,
+    AVG(r.CentilniRang1) AS CentilXA,
+    COUNT(r.CentilniRang1) AS N
+FROM TestVbateriji tv
+JOIN Test t 
+    ON t.ID = tv.IdTest
+JOIN Rezultat r
+    ON r.IdTest = t.ID
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = m.IdClan
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+WHERE du.IdVloga = 10
+  AND r.CentilniRang1 IS NOT NULL
+  AND tv.IdBaterija IN (SELECT ID FROM @Baterije)
+  AND me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+GROUP BY 
+    rgn.Name,
+    t.Ime
+ORDER BY 
+    Regija,
+    Test;
+-- =========================
+-- CONE
+-- =========================
+-- cone Slovenija
+SELECT 
+    'Slovenija' as Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+  AND r.ConaBarva IN ('#9ac263', '#df3127', '#ffd54e')
+GROUP BY
+    te.Ime
+UNION ALL
+-- cone regije
+SELECT
+    rgn.Name AS Regija,
+    te.Ime AS TestIme,
+    SUM(CASE WHEN r.ConaBarva = '#9ac263' THEN 1 ELSE 0 END) AS Zdravo,
+    SUM(CASE WHEN r.ConaBarva = '#ffd54e' THEN 1 ELSE 0 END) AS Mejno,
+    SUM(CASE WHEN r.ConaBarva = '#df3127' THEN 1 ELSE 0 END) AS Tvegano
+FROM Rezultat r
+JOIN Merjenec m 
+    ON m.ID = r.IdMerjenec
+JOIN Meritev me
+    ON me.ID = m.IdMeritev
+JOIN Clan c
+    ON c.ID = m.IdClan
+JOIN DostopUporabnikaDoClana du
+    ON du.IdClan = c.ID
+JOIN Uporabnik u
+    ON u.ID = du.IdUporabnik
+JOIN PostalCodes pc
+    ON pc.ID = u.PostalCodeID
+JOIN fitnessMapRegions rgn
+    ON rgn.ID = pc.RegionID
+JOIN Test te
+    ON te.ID = r.IdTest
+WHERE me.BaterijaTestov IN (SELECT ID FROM @Baterije)
+  AND du.IdVloga = 10
+  AND r.ConaBarva IN ('#9ac263', '#ffd54e', '#df3127')
+GROUP BY
+    rgn.Name,
+    te.Ime
+ORDER BY
+    Regija,
+    TestIme;</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -10886,10 +11138,10 @@
       <c r="K5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>0.1864406779661017</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>0.16949152542372881</v>
       </c>
     </row>
@@ -10928,10 +11180,10 @@
       <c r="K6" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <v>0.21794871794871795</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="8">
         <v>0.17948717948717949</v>
       </c>
     </row>
@@ -10970,10 +11222,10 @@
       <c r="K7" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <v>0.25490196078431371</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>0.14705882352941177</v>
       </c>
     </row>
@@ -11012,10 +11264,10 @@
       <c r="K8" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>0.39473684210526316</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>0.15789473684210525</v>
       </c>
     </row>
@@ -11054,10 +11306,10 @@
       <c r="K9" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <v>0.32307692307692309</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <v>9.2307692307692313E-2</v>
       </c>
     </row>
@@ -11096,10 +11348,10 @@
       <c r="K10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="8">
         <v>0.24878048780487805</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <v>0.2032520325203252</v>
       </c>
     </row>
@@ -11138,10 +11390,10 @@
       <c r="K11" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <v>0.14516129032258066</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <v>0.19354838709677419</v>
       </c>
     </row>
@@ -11180,10 +11432,10 @@
       <c r="K12" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="8">
         <v>0.23684210526315788</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="8">
         <v>0.21052631578947367</v>
       </c>
     </row>
@@ -11222,10 +11474,10 @@
       <c r="K13" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <v>0.19379844961240311</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <v>0.27906976744186046</v>
       </c>
     </row>
@@ -11264,10 +11516,10 @@
       <c r="K14" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <v>0.14285714285714285</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <v>0.14285714285714285</v>
       </c>
     </row>
@@ -11306,10 +11558,10 @@
       <c r="K15" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <v>0.203125</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="8">
         <v>0.2109375</v>
       </c>
     </row>
@@ -11348,10 +11600,10 @@
       <c r="K16" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="8">
         <v>0.24783974862529459</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="8">
         <v>0.19285153181461115</v>
       </c>
     </row>
@@ -11390,10 +11642,10 @@
       <c r="K17" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <v>0.22727272727272727</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="8">
         <v>0.31818181818181818</v>
       </c>
     </row>
@@ -11432,10 +11684,10 @@
       <c r="K18" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18">
         <v>0.23252169797226951</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18">
         <v>0.19211265025324029</v>
       </c>
     </row>

--- a/reportOKSanaliza.xlsx
+++ b/reportOKSanaliza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojan\Documents\GitHub\ReportOKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C027AC-76C3-4026-948E-1BA8239ED2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970041D-47F6-466D-83D1-51CD7E8B0E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
   </bookViews>
   <sheets>
     <sheet name="Analize" sheetId="4" r:id="rId1"/>
@@ -18,11 +18,12 @@
     <sheet name="Cone" sheetId="7" r:id="rId3"/>
     <sheet name="Pošte" sheetId="1" r:id="rId4"/>
     <sheet name="Regije" sheetId="2" r:id="rId5"/>
+    <sheet name="Uvod" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -357,7 +358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="545">
   <si>
     <t>ID</t>
   </si>
@@ -1962,6 +1963,36 @@
   </si>
   <si>
     <t>Average of Tvegano%</t>
+  </si>
+  <si>
+    <t>Datum</t>
+  </si>
+  <si>
+    <t>IzvajalecNaziv</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>BaterijaTestovIme</t>
+  </si>
+  <si>
+    <t>RegijaName</t>
+  </si>
+  <si>
+    <t>Merjencev</t>
+  </si>
+  <si>
+    <t>13. 02. 2026 00:00:00</t>
+  </si>
+  <si>
+    <t>Fakulteta za šport, UL</t>
+  </si>
+  <si>
+    <t>Premelč Jerneja</t>
+  </si>
+  <si>
+    <t>Telesna zmogljivost odrasli + VZG in T600</t>
   </si>
 </sst>
 </file>
@@ -7479,7 +7510,7 @@
     <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -7505,7 +7536,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -26717,4 +26748,62 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75527AB1-8C0F-4349-B6A7-0DD57B989500}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/reportOKSanaliza.xlsx
+++ b/reportOKSanaliza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30019"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojan\Documents\GitHub\ReportOKS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7F521F1-22C6-457D-9708-53B651198F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A7ADBF7-FEED-4078-9ABB-B0F197399286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F13620D-0B35-4D77-9205-B40C0C733A79}"/>
   </bookViews>
   <sheets>
     <sheet name="Analize" sheetId="4" r:id="rId1"/>
@@ -22,8 +22,8 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId7"/>
-    <pivotCache cacheId="9" r:id="rId8"/>
+    <pivotCache cacheId="360" r:id="rId7"/>
+    <pivotCache cacheId="361" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -384,7 +384,7 @@
     <t>FŠ odrasli 13.2.2026</t>
   </si>
   <si>
-    <t>Table Grid</t>
+    <t>Light Shading Accent 3</t>
   </si>
   <si>
     <t>Geo_enota</t>
@@ -2099,9 +2099,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Navadno" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{BDBFD1E4-62EC-41BE-B39B-390F134CCF6B}"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Odstotek" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2123,7 +2123,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="sl-SI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2265,7 +2265,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Vsota</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2703,7 +2703,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="sl-SI"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7408,7 +7408,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F335978-D2AF-46A9-AAAA-E269CFBBC0BA}" name="PivotTable1" cacheId="360" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="H4:I18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -7516,7 +7516,7 @@
     <dataField name="Average of CentilXA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <conditionalFormats count="2">
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -7542,7 +7542,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -7605,7 +7605,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED1F8AC9-8CC5-4E08-995C-C481136EF10E}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED1F8AC9-8CC5-4E08-995C-C481136EF10E}" name="PivotTable1" cacheId="361" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="K4:M18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -8368,7 +8368,7 @@
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
